--- a/FullSeason5.xlsx
+++ b/FullSeason5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ianjpeck/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ianjpeck/Documents/GitHub/sbparser/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90069A84-1EE3-234C-A403-707E5930F6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8C2615-A059-1A4D-8A9F-F7A735B2A755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16480" xr2:uid="{786F1597-E4AA-4248-AD9D-56520FFD76E3}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{786F1597-E4AA-4248-AD9D-56520FFD76E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="320">
   <si>
     <t>Month 1</t>
   </si>
@@ -352,9 +352,6 @@
     <t>Meta Knight - W</t>
   </si>
   <si>
-    <t>Yoshi's Island</t>
-  </si>
-  <si>
     <t>Guest Apperance by Yoshi</t>
   </si>
   <si>
@@ -448,9 +445,6 @@
     <t>#1 contender Special</t>
   </si>
   <si>
-    <t>Warioware, Inc.</t>
-  </si>
-  <si>
     <t>If Sonic wins, he is added to Human championship</t>
   </si>
   <si>
@@ -509,9 +503,6 @@
   </si>
   <si>
     <t>Guest Appearance by Pit</t>
-  </si>
-  <si>
-    <t>Mario Bros</t>
   </si>
   <si>
     <t>Flat Zone 2</t>
@@ -846,12 +837,6 @@
     </r>
   </si>
   <si>
-    <t>Warioware Inc</t>
-  </si>
-  <si>
-    <t>75 m</t>
-  </si>
-  <si>
     <t>Special Guest by Ness</t>
   </si>
   <si>
@@ -876,9 +861,6 @@
     <t>Month 10</t>
   </si>
   <si>
-    <t>75 M</t>
-  </si>
-  <si>
     <t>Guest appearance by  DK</t>
   </si>
   <si>
@@ -889,9 +871,6 @@
   </si>
   <si>
     <t>Guest Appearance</t>
-  </si>
-  <si>
-    <t>Flatzone 2</t>
   </si>
   <si>
     <t>Good comeback. Saved match</t>
@@ -1152,22 +1131,31 @@
     <t>PL 80%</t>
   </si>
   <si>
-    <t>Final Destination  Tourney</t>
-  </si>
-  <si>
     <t>Need to outlaw hammers</t>
   </si>
   <si>
     <t>Low item drop next time</t>
   </si>
   <si>
-    <t>Brawl</t>
-  </si>
-  <si>
-    <t>Melee</t>
-  </si>
-  <si>
     <t>Ganondorf added into championship match</t>
+  </si>
+  <si>
+    <t>Yoshi's Island (Melee)</t>
+  </si>
+  <si>
+    <t>Yoshi's Island (Brawl)</t>
+  </si>
+  <si>
+    <t>Mario Bros.</t>
+  </si>
+  <si>
+    <t>WarioWare, Inc.</t>
+  </si>
+  <si>
+    <t>75m</t>
+  </si>
+  <si>
+    <t>Final Destination Tournament</t>
   </si>
 </sst>
 </file>
@@ -1504,9 +1492,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1544,7 +1532,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1650,7 +1638,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1792,7 +1780,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3635,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>99</v>
+        <v>315</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
@@ -3643,7 +3631,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B144" s="3">
         <v>1</v>
@@ -3727,13 +3715,13 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B150" s="3">
         <v>4</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>68</v>
@@ -3755,7 +3743,7 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B152" s="3">
         <v>5</v>
@@ -3793,7 +3781,7 @@
         <v>14</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D155" s="10"/>
       <c r="E155" s="10"/>
@@ -3805,7 +3793,7 @@
         <v>1</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D156" s="10" t="s">
         <v>58</v>
@@ -3879,7 +3867,7 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B162" s="7">
         <v>4</v>
@@ -3942,10 +3930,10 @@
     <row r="167" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A167" s="12"/>
       <c r="B167" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C167" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="C167" s="14" t="s">
-        <v>107</v>
       </c>
       <c r="D167" s="15"/>
       <c r="E167" s="15"/>
@@ -3959,7 +3947,7 @@
         <v>1</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D168" s="15" t="s">
         <v>86</v>
@@ -3969,7 +3957,7 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B169" s="12"/>
       <c r="C169" s="15">
@@ -4025,7 +4013,7 @@
         <v>3</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D172" s="15" t="s">
         <v>27</v>
@@ -4081,7 +4069,7 @@
         <v>5</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>40</v>
@@ -4091,21 +4079,21 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B177" s="12"/>
       <c r="C177" s="15">
         <v>0</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E177" s="15"/>
       <c r="F177" s="15"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B178" s="12">
         <v>6</v>
@@ -4117,7 +4105,7 @@
         <v>70</v>
       </c>
       <c r="E178" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F178" s="15" t="s">
         <v>12</v>
@@ -4125,7 +4113,7 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B179" s="12"/>
       <c r="C179" s="15">
@@ -4159,7 +4147,7 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B181" s="12"/>
       <c r="C181" s="15">
@@ -4201,7 +4189,7 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B184" s="12">
         <v>9</v>
@@ -4229,7 +4217,7 @@
     </row>
     <row r="186" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B186" s="1"/>
       <c r="C186" s="2"/>
@@ -4249,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D188" s="6"/>
       <c r="E188" s="6"/>
@@ -4257,13 +4245,13 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B189" s="3">
+        <v>1</v>
+      </c>
+      <c r="C189" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="B189" s="3">
-        <v>1</v>
-      </c>
-      <c r="C189" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>8</v>
@@ -4405,7 +4393,7 @@
         <v>14</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D200" s="10"/>
       <c r="E200" s="10"/>
@@ -4465,7 +4453,7 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B205" s="7">
         <v>3</v>
@@ -4529,7 +4517,7 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B209" s="7">
         <v>5</v>
@@ -4567,7 +4555,7 @@
         <v>1</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
@@ -4575,7 +4563,7 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B213" s="3">
         <v>1</v>
@@ -4629,7 +4617,7 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B217" s="3">
         <v>3</v>
@@ -4661,7 +4649,7 @@
         <v>4</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D219" s="6" t="s">
         <v>8</v>
@@ -4689,7 +4677,7 @@
         <v>5</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D221" s="6" t="s">
         <v>9</v>
@@ -4721,7 +4709,7 @@
         <v>14</v>
       </c>
       <c r="C224" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D224" s="10"/>
       <c r="E224" s="10"/>
@@ -4729,7 +4717,7 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B225" s="7">
         <v>1</v>
@@ -4835,7 +4823,7 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B233" s="7">
         <v>5</v>
@@ -4873,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>131</v>
+        <v>317</v>
       </c>
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
@@ -4881,16 +4869,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B237" s="3">
         <v>1</v>
       </c>
       <c r="C237" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E237" s="6" t="s">
         <v>94</v>
@@ -4991,7 +4979,7 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B245" s="3">
         <v>5</v>
@@ -5029,7 +5017,7 @@
         <v>14</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D248" s="10"/>
       <c r="E248" s="10"/>
@@ -5070,7 +5058,7 @@
         <v>48</v>
       </c>
       <c r="D251" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E251" s="10"/>
       <c r="F251" s="10"/>
@@ -5141,7 +5129,7 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B257" s="7">
         <v>5</v>
@@ -5176,10 +5164,10 @@
     <row r="260" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A260" s="12"/>
       <c r="B260" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D260" s="15"/>
       <c r="E260" s="15"/>
@@ -5193,7 +5181,7 @@
         <v>1</v>
       </c>
       <c r="C261" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D261" s="15" t="s">
         <v>32</v>
@@ -5203,7 +5191,7 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B262" s="12"/>
       <c r="C262" s="15">
@@ -5245,13 +5233,13 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A265" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B265" s="12">
         <v>3</v>
       </c>
       <c r="C265" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D265" s="16" t="s">
         <v>95</v>
@@ -5346,14 +5334,14 @@
         <v>33</v>
       </c>
       <c r="D271" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E271" s="15"/>
       <c r="F271" s="15"/>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B272" s="12"/>
       <c r="C272" s="15">
@@ -5395,7 +5383,7 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B275" s="12">
         <v>8</v>
@@ -5404,7 +5392,7 @@
         <v>82</v>
       </c>
       <c r="D275" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E275" s="15" t="s">
         <v>79</v>
@@ -5447,7 +5435,7 @@
     </row>
     <row r="279" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="2"/>
@@ -5467,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D281" s="6"/>
       <c r="E281" s="6"/>
@@ -5475,7 +5463,7 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B282" s="3">
         <v>1</v>
@@ -5484,7 +5472,7 @@
         <v>18</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E282" s="6"/>
       <c r="F282" s="6"/>
@@ -5629,7 +5617,7 @@
         <v>14</v>
       </c>
       <c r="C293" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D293" s="10"/>
       <c r="E293" s="10"/>
@@ -5637,7 +5625,7 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B294" s="7">
         <v>1</v>
@@ -5669,7 +5657,7 @@
         <v>2</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D296" s="10" t="s">
         <v>43</v>
@@ -5717,7 +5705,7 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B300" s="7">
         <v>4</v>
@@ -5745,7 +5733,7 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A302" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B302" s="7">
         <v>5</v>
@@ -5783,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D305" s="6"/>
       <c r="E305" s="6"/>
@@ -5791,7 +5779,7 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B306" s="3">
         <v>1</v>
@@ -5847,7 +5835,7 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B310" s="3">
         <v>3</v>
@@ -5875,7 +5863,7 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A312" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B312" s="3">
         <v>4</v>
@@ -5903,7 +5891,7 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B314" s="3">
         <v>5</v>
@@ -5941,7 +5929,7 @@
         <v>14</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>152</v>
+        <v>316</v>
       </c>
       <c r="D317" s="10"/>
       <c r="E317" s="10"/>
@@ -6055,7 +6043,7 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B326" s="7">
         <v>5</v>
@@ -6093,7 +6081,7 @@
         <v>1</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D329" s="6"/>
       <c r="E329" s="6"/>
@@ -6107,7 +6095,7 @@
         <v>1</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D330" s="6" t="s">
         <v>8</v>
@@ -6215,7 +6203,7 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B338" s="3">
         <v>5</v>
@@ -6224,7 +6212,7 @@
         <v>5</v>
       </c>
       <c r="D338" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E338" s="6"/>
       <c r="F338" s="6"/>
@@ -6253,7 +6241,7 @@
         <v>14</v>
       </c>
       <c r="C341" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D341" s="10"/>
       <c r="E341" s="10"/>
@@ -6322,7 +6310,7 @@
         <v>20</v>
       </c>
       <c r="D346" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E346" s="10"/>
       <c r="F346" s="10"/>
@@ -6341,7 +6329,7 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A348" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B348" s="7">
         <v>4</v>
@@ -6369,7 +6357,7 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A350" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B350" s="7">
         <v>5</v>
@@ -6404,10 +6392,10 @@
     <row r="353" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A353" s="12"/>
       <c r="B353" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C353" s="14" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D353" s="15"/>
       <c r="E353" s="15"/>
@@ -6449,7 +6437,7 @@
         <v>2</v>
       </c>
       <c r="C356" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D356" s="15" t="s">
         <v>30</v>
@@ -6516,14 +6504,14 @@
         <v>27</v>
       </c>
       <c r="D360" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E360" s="15"/>
       <c r="F360" s="15"/>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A361" s="12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B361" s="12"/>
       <c r="C361" s="15">
@@ -6565,7 +6553,7 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" s="12" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B364" s="12">
         <v>6</v>
@@ -6585,7 +6573,7 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A365" s="12" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B365" s="12"/>
       <c r="C365" s="15">
@@ -6603,7 +6591,7 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A366" s="12" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B366" s="12">
         <v>7</v>
@@ -6612,7 +6600,7 @@
         <v>13</v>
       </c>
       <c r="D366" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E366" s="15" t="s">
         <v>86</v>
@@ -6623,7 +6611,7 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A367" s="19" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B367" s="12"/>
       <c r="C367" s="15">
@@ -6650,7 +6638,7 @@
         <v>22</v>
       </c>
       <c r="D368" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E368" s="15"/>
       <c r="F368" s="15"/>
@@ -6675,7 +6663,7 @@
         <v>9</v>
       </c>
       <c r="C370" s="15" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D370" s="15" t="s">
         <v>9</v>
@@ -6685,7 +6673,7 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A371" s="12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B371" s="12"/>
       <c r="C371" s="15">
@@ -6699,7 +6687,7 @@
     </row>
     <row r="372" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B372" s="1"/>
       <c r="C372" s="2"/>
@@ -6719,7 +6707,7 @@
         <v>1</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D374" s="6"/>
       <c r="E374" s="6"/>
@@ -6760,7 +6748,7 @@
         <v>95</v>
       </c>
       <c r="D377" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E377" s="6"/>
       <c r="F377" s="6"/>
@@ -6805,7 +6793,7 @@
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A381" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B381" s="3">
         <v>4</v>
@@ -6821,7 +6809,7 @@
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A382" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B382" s="3"/>
       <c r="C382" s="6">
@@ -6835,7 +6823,7 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A383" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B383" s="3">
         <v>5</v>
@@ -6851,7 +6839,7 @@
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A384" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B384" s="3"/>
       <c r="C384" s="6">
@@ -6875,7 +6863,7 @@
         <v>14</v>
       </c>
       <c r="C386" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D386" s="10"/>
       <c r="E386" s="10"/>
@@ -6887,7 +6875,7 @@
         <v>1</v>
       </c>
       <c r="C387" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D387" s="10" t="s">
         <v>21</v>
@@ -6909,13 +6897,13 @@
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A389" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B389" s="7">
         <v>2</v>
       </c>
       <c r="C389" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D389" s="10" t="s">
         <v>90</v>
@@ -6941,7 +6929,7 @@
         <v>3</v>
       </c>
       <c r="C391" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D391" s="10" t="s">
         <v>76</v>
@@ -6963,7 +6951,7 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A393" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B393" s="7">
         <v>4</v>
@@ -7019,7 +7007,7 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A396" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B396" s="7"/>
       <c r="C396" s="10">
@@ -7047,7 +7035,7 @@
         <v>1</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D398" s="6"/>
       <c r="E398" s="6"/>
@@ -7201,7 +7189,7 @@
         <v>14</v>
       </c>
       <c r="C410" s="9" t="s">
-        <v>99</v>
+        <v>314</v>
       </c>
       <c r="D410" s="10"/>
       <c r="E410" s="10"/>
@@ -7265,7 +7253,7 @@
         <v>3</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D415" s="10" t="s">
         <v>20</v>
@@ -7351,7 +7339,7 @@
         <v>1</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D422" s="6"/>
       <c r="E422" s="6"/>
@@ -7415,7 +7403,7 @@
         <v>3</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D427" s="6" t="s">
         <v>68</v>
@@ -7499,7 +7487,7 @@
         <v>14</v>
       </c>
       <c r="C434" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D434" s="10"/>
       <c r="E434" s="10"/>
@@ -7585,13 +7573,13 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A441" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B441" s="7">
         <v>4</v>
       </c>
       <c r="C441" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D441" s="10" t="s">
         <v>70</v>
@@ -7601,7 +7589,7 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A442" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B442" s="7"/>
       <c r="C442" s="10">
@@ -7615,7 +7603,7 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A443" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B443" s="7">
         <v>5</v>
@@ -7631,7 +7619,7 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A444" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B444" s="7"/>
       <c r="C444" s="10">
@@ -7652,10 +7640,10 @@
     <row r="446" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A446" s="12"/>
       <c r="B446" s="13" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C446" s="14" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D446" s="15"/>
       <c r="E446" s="15"/>
@@ -7747,7 +7735,7 @@
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A452" s="12" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B452" s="12"/>
       <c r="C452" s="15">
@@ -7767,7 +7755,7 @@
         <v>4</v>
       </c>
       <c r="C453" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D453" s="15" t="s">
         <v>54</v>
@@ -7777,7 +7765,7 @@
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A454" s="12" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B454" s="12"/>
       <c r="C454" s="15">
@@ -7809,7 +7797,7 @@
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A456" s="12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B456" s="12"/>
       <c r="C456" s="15">
@@ -7834,7 +7822,7 @@
         <v>9</v>
       </c>
       <c r="D457" s="15" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E457" s="15"/>
       <c r="F457" s="15"/>
@@ -7869,7 +7857,7 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A460" s="19" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B460" s="12"/>
       <c r="C460" s="15">
@@ -7899,7 +7887,7 @@
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A462" s="12" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B462" s="12"/>
       <c r="C462" s="15">
@@ -7913,7 +7901,7 @@
     </row>
     <row r="463" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A463" s="22" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B463" s="1"/>
       <c r="C463" s="2"/>
@@ -7933,7 +7921,7 @@
         <v>1</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D465" s="6"/>
       <c r="E465" s="6"/>
@@ -7948,7 +7936,7 @@
         <v>70</v>
       </c>
       <c r="D466" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E466" s="6"/>
       <c r="F466" s="6"/>
@@ -8061,7 +8049,7 @@
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A475" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B475" s="3"/>
       <c r="C475" s="6">
@@ -8085,7 +8073,7 @@
         <v>14</v>
       </c>
       <c r="C477" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D477" s="10"/>
       <c r="E477" s="10"/>
@@ -8119,7 +8107,7 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A480" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B480" s="7">
         <v>2</v>
@@ -8173,7 +8161,7 @@
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A484" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B484" s="7">
         <v>4</v>
@@ -8189,7 +8177,7 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A485" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B485" s="7"/>
       <c r="C485" s="10">
@@ -8203,7 +8191,7 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A486" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B486" s="7">
         <v>5</v>
@@ -8241,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D489" s="6"/>
       <c r="E489" s="6"/>
@@ -8253,7 +8241,7 @@
         <v>1</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D490" s="6" t="s">
         <v>34</v>
@@ -8281,7 +8269,7 @@
         <v>2</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D492" s="6" t="s">
         <v>32</v>
@@ -8401,7 +8389,7 @@
         <v>14</v>
       </c>
       <c r="C501" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D501" s="10"/>
       <c r="E501" s="10"/>
@@ -8409,7 +8397,7 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A502" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B502" s="7">
         <v>1</v>
@@ -8553,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D513" s="6"/>
       <c r="E513" s="6"/>
@@ -8587,7 +8575,7 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A516" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B516" s="3">
         <v>2</v>
@@ -8596,7 +8584,7 @@
         <v>32</v>
       </c>
       <c r="D516" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E516" s="6"/>
       <c r="F516" s="6"/>
@@ -8791,7 +8779,7 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A532" s="7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B532" s="7">
         <v>4</v>
@@ -8807,7 +8795,7 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A533" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B533" s="7"/>
       <c r="C533" s="10">
@@ -8854,7 +8842,7 @@
     <row r="537" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A537" s="12"/>
       <c r="B537" s="13" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C537" s="14" t="s">
         <v>28</v>
@@ -8899,7 +8887,7 @@
         <v>2</v>
       </c>
       <c r="C540" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D540" s="15" t="s">
         <v>48</v>
@@ -8937,7 +8925,7 @@
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A543" s="12" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B543" s="12"/>
       <c r="C543" s="15">
@@ -8960,7 +8948,7 @@
         <v>73</v>
       </c>
       <c r="D544" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E544" s="15"/>
       <c r="F544" s="15"/>
@@ -8979,7 +8967,7 @@
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A546" s="12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B546" s="12">
         <v>5</v>
@@ -8999,7 +8987,7 @@
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A547" s="12" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B547" s="12"/>
       <c r="C547" s="15">
@@ -9026,7 +9014,7 @@
         <v>9</v>
       </c>
       <c r="D548" s="15" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E548" s="15"/>
       <c r="F548" s="15"/>
@@ -9061,7 +9049,7 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A551" s="19" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B551" s="12"/>
       <c r="C551" s="15">
@@ -9075,7 +9063,7 @@
     </row>
     <row r="552" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B552" s="1"/>
       <c r="C552" s="2"/>
@@ -9103,13 +9091,13 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A555" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B555" s="3">
         <v>1</v>
       </c>
       <c r="C555" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D555" s="6" t="s">
         <v>48</v>
@@ -9131,7 +9119,7 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A557" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B557" s="3">
         <v>2</v>
@@ -9255,7 +9243,7 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A567" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B567" s="7">
         <v>1</v>
@@ -9264,7 +9252,7 @@
         <v>20</v>
       </c>
       <c r="D567" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E567" s="10"/>
       <c r="F567" s="10"/>
@@ -9283,7 +9271,7 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A569" s="7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B569" s="7">
         <v>2</v>
@@ -9299,7 +9287,7 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A570" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B570" s="7"/>
       <c r="C570" s="10">
@@ -9313,7 +9301,7 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A571" s="7" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B571" s="7">
         <v>3</v>
@@ -9411,7 +9399,7 @@
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A579" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B579" s="3">
         <v>1</v>
@@ -9439,7 +9427,7 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A581" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B581" s="3">
         <v>2</v>
@@ -9467,7 +9455,7 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A583" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B583" s="3">
         <v>3</v>
@@ -9495,7 +9483,7 @@
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A585" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B585" s="3">
         <v>4</v>
@@ -9523,13 +9511,13 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A587" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B587" s="3">
         <v>5</v>
       </c>
       <c r="C587" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D587" s="6" t="s">
         <v>3</v>
@@ -9599,13 +9587,13 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A593" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B593" s="7">
         <v>2</v>
       </c>
       <c r="C593" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D593" s="10" t="s">
         <v>82</v>
@@ -9627,7 +9615,7 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A595" s="7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B595" s="7">
         <v>3</v>
@@ -9655,7 +9643,7 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A597" s="7" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B597" s="7">
         <v>4</v>
@@ -9683,7 +9671,7 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A599" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B599" s="7">
         <v>5</v>
@@ -9695,13 +9683,13 @@
         <v>76</v>
       </c>
       <c r="E599" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F599" s="10"/>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A600" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B600" s="7"/>
       <c r="C600" s="10">
@@ -9768,7 +9756,7 @@
         <v>54</v>
       </c>
       <c r="D605" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E605" s="6"/>
       <c r="F605" s="6"/>
@@ -9813,7 +9801,7 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A609" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B609" s="3">
         <v>4</v>
@@ -9822,7 +9810,7 @@
         <v>24</v>
       </c>
       <c r="D609" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E609" s="6"/>
       <c r="F609" s="6"/>
@@ -9841,7 +9829,7 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A611" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B611" s="3">
         <v>5</v>
@@ -9887,7 +9875,7 @@
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A615" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B615" s="7">
         <v>1</v>
@@ -9971,7 +9959,7 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A621" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B621" s="7">
         <v>4</v>
@@ -9999,7 +9987,7 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A623" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B623" s="7">
         <v>5</v>
@@ -10034,36 +10022,34 @@
     <row r="626" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A626" s="12"/>
       <c r="B626" s="13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C626" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D626" s="15"/>
       <c r="E626" s="15" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="F626" s="15" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A627" s="12" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B627" s="12">
         <v>1</v>
       </c>
       <c r="C627" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D627" s="15" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E627" s="15"/>
-      <c r="F627" s="25" t="s">
-        <v>321</v>
-      </c>
+      <c r="F627" s="25"/>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A628" s="12"/>
@@ -10079,7 +10065,7 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A629" s="12" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B629" s="12">
         <v>2</v>
@@ -10107,7 +10093,7 @@
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A631" s="12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B631" s="12">
         <v>3</v>
@@ -10135,7 +10121,7 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A633" s="12" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B633" s="12">
         <v>4</v>
@@ -10163,7 +10149,7 @@
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A635" s="12" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B635" s="12">
         <v>5</v>
@@ -10191,7 +10177,7 @@
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A637" s="12" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B637" s="12">
         <v>6</v>
@@ -10219,7 +10205,7 @@
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A639" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B639" s="12">
         <v>7</v>
@@ -10247,7 +10233,7 @@
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A641" s="12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B641" s="12">
         <v>8</v>
@@ -10275,7 +10261,7 @@
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A643" s="12" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B643" s="12">
         <v>9</v>
@@ -10303,7 +10289,7 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A645" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B645" s="12">
         <v>10</v>
@@ -10331,13 +10317,13 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A647" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B647" s="12">
         <v>11</v>
       </c>
       <c r="C647" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D647" s="15" t="s">
         <v>41</v>
@@ -10359,13 +10345,13 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A649" s="12" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B649" s="12">
         <v>12</v>
       </c>
       <c r="C649" s="15" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D649" s="15" t="s">
         <v>86</v>
@@ -10387,7 +10373,7 @@
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A651" s="12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B651" s="12">
         <v>13</v>
@@ -10415,7 +10401,7 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A653" s="12" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B653" s="12">
         <v>14</v>
@@ -10443,7 +10429,7 @@
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A655" s="12" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B655" s="12">
         <v>15</v>
@@ -10452,7 +10438,7 @@
         <v>24</v>
       </c>
       <c r="D655" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E655" s="12"/>
       <c r="F655" s="12"/>
@@ -10471,7 +10457,7 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A657" s="26" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B657" s="26">
         <v>1</v>
@@ -10483,9 +10469,7 @@
         <v>21</v>
       </c>
       <c r="E657" s="26"/>
-      <c r="F657" s="28" t="s">
-        <v>322</v>
-      </c>
+      <c r="F657" s="28"/>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A658" s="26"/>
@@ -10501,7 +10485,7 @@
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A659" s="26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B659" s="26">
         <v>2</v>
@@ -10529,7 +10513,7 @@
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A661" s="26" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B661" s="26">
         <v>3</v>
@@ -10557,7 +10541,7 @@
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A663" s="26" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B663" s="26">
         <v>4</v>
@@ -10585,7 +10569,7 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A665" s="26" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B665" s="26">
         <v>5</v>
@@ -10613,7 +10597,7 @@
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A667" s="26" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B667" s="26">
         <v>6</v>
@@ -10641,7 +10625,7 @@
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A669" s="26" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B669" s="26">
         <v>7</v>
@@ -10669,7 +10653,7 @@
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A671" s="26" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B671" s="26">
         <v>8</v>
@@ -10697,7 +10681,7 @@
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A673" s="26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B673" s="26">
         <v>9</v>
@@ -10725,7 +10709,7 @@
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A675" s="26" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B675" s="26">
         <v>10</v>
@@ -10753,13 +10737,13 @@
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A677" s="26" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B677" s="26">
         <v>11</v>
       </c>
       <c r="C677" s="27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D677" s="27" t="s">
         <v>27</v>
@@ -10781,7 +10765,7 @@
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A679" s="29" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B679" s="29">
         <v>12</v>
@@ -10809,7 +10793,7 @@
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A681" s="26" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B681" s="26">
         <v>13</v>
@@ -10837,7 +10821,7 @@
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A683" s="26" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B683" s="26">
         <v>14</v>
@@ -10865,7 +10849,7 @@
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A685" s="26" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B685" s="26">
         <v>15</v>
@@ -10893,7 +10877,7 @@
     </row>
     <row r="687" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="2"/>
@@ -10921,7 +10905,7 @@
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A690" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B690" s="3">
         <v>1</v>
@@ -11005,7 +10989,7 @@
         <v>4</v>
       </c>
       <c r="C696" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D696" s="6" t="s">
         <v>52</v>
@@ -11027,7 +11011,7 @@
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A698" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B698" s="3">
         <v>5</v>
@@ -11036,7 +11020,7 @@
         <v>31</v>
       </c>
       <c r="D698" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E698" s="6"/>
       <c r="F698" s="6"/>
@@ -11073,7 +11057,7 @@
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A702" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B702" s="7">
         <v>1</v>
@@ -11127,7 +11111,7 @@
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A706" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B706" s="7">
         <v>3</v>
@@ -11155,7 +11139,7 @@
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A708" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B708" s="7">
         <v>4</v>
@@ -11183,7 +11167,7 @@
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A710" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B710" s="7">
         <v>5</v>
@@ -11192,7 +11176,7 @@
         <v>22</v>
       </c>
       <c r="D710" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E710" s="10"/>
       <c r="F710" s="10"/>
@@ -11221,7 +11205,7 @@
         <v>1</v>
       </c>
       <c r="C713" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D713" s="6"/>
       <c r="E713" s="6"/>
@@ -11229,7 +11213,7 @@
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A714" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B714" s="3">
         <v>1</v>
@@ -11283,7 +11267,7 @@
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A718" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B718" s="3">
         <v>3</v>
@@ -11299,7 +11283,7 @@
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A719" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B719" s="3"/>
       <c r="C719" s="6">
@@ -11313,7 +11297,7 @@
     </row>
     <row r="720" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A720" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B720" s="3">
         <v>4</v>
@@ -11341,7 +11325,7 @@
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A722" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B722" s="3">
         <v>5</v>
@@ -11379,7 +11363,7 @@
         <v>14</v>
       </c>
       <c r="C725" s="9" t="s">
-        <v>99</v>
+        <v>315</v>
       </c>
       <c r="D725" s="10"/>
       <c r="E725" s="10"/>
@@ -11439,7 +11423,7 @@
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A730" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B730" s="7">
         <v>3</v>
@@ -11455,7 +11439,7 @@
     </row>
     <row r="731" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A731" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B731" s="7"/>
       <c r="C731" s="10">
@@ -11469,7 +11453,7 @@
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A732" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B732" s="7">
         <v>4</v>
@@ -11485,7 +11469,7 @@
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A733" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B733" s="7"/>
       <c r="C733" s="10">
@@ -11499,7 +11483,7 @@
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A734" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B734" s="7">
         <v>5</v>
@@ -11537,7 +11521,7 @@
         <v>1</v>
       </c>
       <c r="C737" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D737" s="6"/>
       <c r="E737" s="6"/>
@@ -11623,13 +11607,13 @@
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A744" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B744" s="3">
         <v>4</v>
       </c>
       <c r="C744" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D744" s="6" t="s">
         <v>30</v>
@@ -11651,7 +11635,7 @@
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A746" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B746" s="3">
         <v>5</v>
@@ -11689,7 +11673,7 @@
         <v>14</v>
       </c>
       <c r="C749" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D749" s="10"/>
       <c r="E749" s="10"/>
@@ -11733,7 +11717,7 @@
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A752" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B752" s="7">
         <v>2</v>
@@ -11787,7 +11771,7 @@
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A756" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B756" s="7">
         <v>4</v>
@@ -11815,7 +11799,7 @@
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A758" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B758" s="7">
         <v>5</v>
@@ -11833,7 +11817,7 @@
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A759" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B759" s="7"/>
       <c r="C759" s="10">
@@ -11856,10 +11840,10 @@
     <row r="761" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A761" s="12"/>
       <c r="B761" s="13" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C761" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D761" s="15"/>
       <c r="E761" s="15"/>
@@ -11909,7 +11893,7 @@
         <v>2</v>
       </c>
       <c r="C764" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D764" s="15" t="s">
         <v>48</v>
@@ -11953,7 +11937,7 @@
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A767" s="12" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B767" s="12"/>
       <c r="C767" s="15">
@@ -11978,18 +11962,18 @@
         <v>73</v>
       </c>
       <c r="D768" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E768" s="15" t="s">
         <v>13</v>
       </c>
       <c r="F768" s="15" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A769" s="12" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B769" s="12"/>
       <c r="C769" s="15">
@@ -12057,7 +12041,7 @@
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A773" s="12" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B773" s="12"/>
       <c r="C773" s="15">
@@ -12093,7 +12077,7 @@
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A775" s="19" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B775" s="12"/>
       <c r="C775" s="15">
@@ -12111,7 +12095,7 @@
     </row>
     <row r="776" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A776" s="31" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B776" s="31"/>
       <c r="C776" s="32"/>
@@ -12133,7 +12117,7 @@
         <v>1</v>
       </c>
       <c r="C778" s="36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D778" s="37"/>
       <c r="E778" s="37"/>
@@ -12282,10 +12266,10 @@
     <row r="790" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A790" s="38"/>
       <c r="B790" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C790" s="40" t="s">
-        <v>260</v>
+        <v>317</v>
       </c>
       <c r="D790" s="41"/>
       <c r="E790" s="41"/>
@@ -12345,7 +12329,7 @@
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A795" s="38" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B795" s="38">
         <v>3</v>
@@ -12439,7 +12423,7 @@
         <v>1</v>
       </c>
       <c r="C802" s="36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D802" s="37"/>
       <c r="E802" s="37"/>
@@ -12477,7 +12461,7 @@
         <v>2</v>
       </c>
       <c r="C805" s="37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D805" s="37" t="s">
         <v>62</v>
@@ -12534,7 +12518,7 @@
         <v>52</v>
       </c>
       <c r="D809" s="37" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E809" s="37"/>
       <c r="F809" s="37"/>
@@ -12590,10 +12574,10 @@
     <row r="814" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A814" s="38"/>
       <c r="B814" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C814" s="40" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D814" s="41"/>
       <c r="E814" s="41"/>
@@ -12653,13 +12637,13 @@
     </row>
     <row r="819" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A819" s="38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B819" s="38">
         <v>3</v>
       </c>
       <c r="C819" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D819" s="41" t="s">
         <v>82</v>
@@ -12709,7 +12693,7 @@
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A823" s="38" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B823" s="38">
         <v>5</v>
@@ -12749,7 +12733,7 @@
         <v>1</v>
       </c>
       <c r="C826" s="36" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D826" s="37"/>
       <c r="E826" s="37"/>
@@ -12763,7 +12747,7 @@
         <v>1</v>
       </c>
       <c r="C827" s="37" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D827" s="43" t="s">
         <v>94</v>
@@ -12852,7 +12836,7 @@
         <v>31</v>
       </c>
       <c r="D833" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E833" s="37"/>
       <c r="F833" s="37"/>
@@ -12875,7 +12859,7 @@
         <v>5</v>
       </c>
       <c r="C835" s="37" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D835" s="37" t="s">
         <v>7</v>
@@ -12906,10 +12890,10 @@
     <row r="838" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A838" s="38"/>
       <c r="B838" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C838" s="40" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="D838" s="41"/>
       <c r="E838" s="41"/>
@@ -12943,7 +12927,7 @@
     </row>
     <row r="841" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A841" s="38" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B841" s="38">
         <v>2</v>
@@ -13058,10 +13042,10 @@
     <row r="850" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A850" s="44"/>
       <c r="B850" s="45" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C850" s="46" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D850" s="47"/>
       <c r="E850" s="47"/>
@@ -13161,7 +13145,7 @@
         <v>4</v>
       </c>
       <c r="C857" s="47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D857" s="47" t="s">
         <v>8</v>
@@ -13235,7 +13219,7 @@
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A862" s="44" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B862" s="44"/>
       <c r="C862" s="47">
@@ -13258,14 +13242,14 @@
         <v>9</v>
       </c>
       <c r="D863" s="47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E863" s="47"/>
       <c r="F863" s="47"/>
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A864" s="49" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B864" s="44"/>
       <c r="C864" s="47">
@@ -13279,7 +13263,7 @@
     </row>
     <row r="865" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A865" s="50" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B865" s="50">
         <v>8</v>
@@ -13288,14 +13272,14 @@
         <v>86</v>
       </c>
       <c r="D865" s="51" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E865" s="51"/>
       <c r="F865" s="51"/>
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A866" s="12" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B866" s="12"/>
       <c r="C866" s="15">
@@ -13309,7 +13293,7 @@
     </row>
     <row r="867" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A867" s="31" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B867" s="31"/>
       <c r="C867" s="32"/>
@@ -13331,7 +13315,7 @@
         <v>1</v>
       </c>
       <c r="C869" s="36" t="s">
-        <v>270</v>
+        <v>318</v>
       </c>
       <c r="D869" s="37"/>
       <c r="E869" s="37"/>
@@ -13391,7 +13375,7 @@
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A874" s="34" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B874" s="34">
         <v>3</v>
@@ -13482,10 +13466,10 @@
     <row r="881" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A881" s="38"/>
       <c r="B881" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C881" s="40" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D881" s="41"/>
       <c r="E881" s="41"/>
@@ -13571,7 +13555,7 @@
     </row>
     <row r="888" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A888" s="38" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B888" s="38">
         <v>4</v>
@@ -13580,7 +13564,7 @@
         <v>27</v>
       </c>
       <c r="D888" s="52" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E888" s="41" t="s">
         <v>21</v>
@@ -13647,7 +13631,7 @@
         <v>1</v>
       </c>
       <c r="C893" s="36" t="s">
-        <v>152</v>
+        <v>316</v>
       </c>
       <c r="D893" s="37"/>
       <c r="E893" s="37"/>
@@ -13707,7 +13691,7 @@
     </row>
     <row r="898" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A898" s="34" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B898" s="34">
         <v>3</v>
@@ -13770,7 +13754,7 @@
         <v>9</v>
       </c>
       <c r="D902" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E902" s="37"/>
       <c r="F902" s="37"/>
@@ -13798,10 +13782,10 @@
     <row r="905" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A905" s="38"/>
       <c r="B905" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C905" s="40" t="s">
-        <v>275</v>
+        <v>150</v>
       </c>
       <c r="D905" s="41"/>
       <c r="E905" s="41"/>
@@ -13813,7 +13797,7 @@
         <v>1</v>
       </c>
       <c r="C906" s="41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D906" s="41" t="s">
         <v>46</v>
@@ -13861,7 +13845,7 @@
     </row>
     <row r="910" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A910" s="38" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B910" s="38">
         <v>3</v>
@@ -13877,7 +13861,7 @@
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A911" s="38" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="B911" s="38"/>
       <c r="C911" s="41">
@@ -13895,7 +13879,7 @@
         <v>4</v>
       </c>
       <c r="C912" s="41" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D912" s="41" t="s">
         <v>83</v>
@@ -13917,7 +13901,7 @@
     </row>
     <row r="914" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A914" s="38" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B914" s="38">
         <v>5</v>
@@ -13957,7 +13941,7 @@
         <v>1</v>
       </c>
       <c r="C917" s="36" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D917" s="37"/>
       <c r="E917" s="37"/>
@@ -13972,7 +13956,7 @@
         <v>34</v>
       </c>
       <c r="D918" s="37" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E918" s="37"/>
       <c r="F918" s="37"/>
@@ -14104,10 +14088,10 @@
     <row r="929" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A929" s="38"/>
       <c r="B929" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C929" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D929" s="41"/>
       <c r="E929" s="41"/>
@@ -14119,7 +14103,7 @@
         <v>1</v>
       </c>
       <c r="C930" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D930" s="41" t="s">
         <v>21</v>
@@ -14254,10 +14238,10 @@
     <row r="941" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A941" s="44"/>
       <c r="B941" s="45" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C941" s="46" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D941" s="47"/>
       <c r="E941" s="47"/>
@@ -14271,7 +14255,7 @@
         <v>1</v>
       </c>
       <c r="C942" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D942" s="47" t="s">
         <v>52</v>
@@ -14281,7 +14265,7 @@
     </row>
     <row r="943" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A943" s="44" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B943" s="44"/>
       <c r="C943" s="47">
@@ -14311,7 +14295,7 @@
     </row>
     <row r="945" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A945" s="44" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B945" s="44"/>
       <c r="C945" s="47">
@@ -14341,7 +14325,7 @@
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A947" s="44" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B947" s="44"/>
       <c r="C947" s="47">
@@ -14371,7 +14355,7 @@
     </row>
     <row r="949" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A949" s="44" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B949" s="44"/>
       <c r="C949" s="47">
@@ -14405,7 +14389,7 @@
     </row>
     <row r="951" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A951" s="44" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B951" s="44"/>
       <c r="C951" s="47">
@@ -14439,7 +14423,7 @@
     </row>
     <row r="953" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A953" s="44" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B953" s="44"/>
       <c r="C953" s="47">
@@ -14471,7 +14455,7 @@
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A955" s="49" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B955" s="44"/>
       <c r="C955" s="47">
@@ -14487,7 +14471,7 @@
     </row>
     <row r="956" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A956" s="44" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B956" s="44"/>
       <c r="C956" s="47"/>
@@ -14505,7 +14489,7 @@
     </row>
     <row r="958" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A958" s="31" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B958" s="31"/>
       <c r="C958" s="32"/>
@@ -14527,7 +14511,7 @@
         <v>1</v>
       </c>
       <c r="C960" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D960" s="37"/>
       <c r="E960" s="37"/>
@@ -14645,7 +14629,7 @@
         <v>5</v>
       </c>
       <c r="C969" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D969" s="37" t="s">
         <v>94</v>
@@ -14676,10 +14660,10 @@
     <row r="972" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A972" s="38"/>
       <c r="B972" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C972" s="40" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D972" s="41"/>
       <c r="E972" s="41"/>
@@ -14835,7 +14819,7 @@
         <v>1</v>
       </c>
       <c r="C984" s="36" t="s">
-        <v>99</v>
+        <v>314</v>
       </c>
       <c r="D984" s="37"/>
       <c r="E984" s="37"/>
@@ -14843,7 +14827,7 @@
     </row>
     <row r="985" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A985" s="34" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B985" s="34">
         <v>1</v>
@@ -14906,7 +14890,7 @@
         <v>94</v>
       </c>
       <c r="D989" s="43" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E989" s="37" t="s">
         <v>54</v>
@@ -14940,7 +14924,7 @@
         <v>41</v>
       </c>
       <c r="D991" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E991" s="37"/>
       <c r="F991" s="37"/>
@@ -14968,7 +14952,7 @@
         <v>8</v>
       </c>
       <c r="D993" s="37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E993" s="37" t="s">
         <v>62</v>
@@ -15000,10 +14984,10 @@
     <row r="996" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A996" s="38"/>
       <c r="B996" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C996" s="40" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D996" s="41"/>
       <c r="E996" s="41"/>
@@ -15011,7 +14995,7 @@
     </row>
     <row r="997" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A997" s="38" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B997" s="38">
         <v>1</v>
@@ -15091,13 +15075,13 @@
     </row>
     <row r="1003" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1003" s="38" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B1003" s="38">
         <v>4</v>
       </c>
       <c r="C1003" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D1003" s="41" t="s">
         <v>82</v>
@@ -15128,7 +15112,7 @@
         <v>27</v>
       </c>
       <c r="D1005" s="41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E1005" s="41"/>
       <c r="F1005" s="41"/>
@@ -15159,7 +15143,7 @@
         <v>1</v>
       </c>
       <c r="C1008" s="36" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D1008" s="37"/>
       <c r="E1008" s="37"/>
@@ -15200,7 +15184,7 @@
         <v>34</v>
       </c>
       <c r="D1011" s="37" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E1011" s="37"/>
       <c r="F1011" s="37"/>
@@ -15249,7 +15233,7 @@
         <v>4</v>
       </c>
       <c r="C1015" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D1015" s="37" t="s">
         <v>86</v>
@@ -15308,10 +15292,10 @@
     <row r="1020" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1020" s="38"/>
       <c r="B1020" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C1020" s="40" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D1020" s="41"/>
       <c r="E1020" s="41"/>
@@ -15319,7 +15303,7 @@
     </row>
     <row r="1021" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1021" s="38" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B1021" s="38">
         <v>1</v>
@@ -15347,7 +15331,7 @@
     </row>
     <row r="1023" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1023" s="38" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B1023" s="38">
         <v>2</v>
@@ -15379,7 +15363,7 @@
         <v>3</v>
       </c>
       <c r="C1025" s="41" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D1025" s="41" t="s">
         <v>20</v>
@@ -15427,7 +15411,7 @@
     </row>
     <row r="1029" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1029" s="38" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B1029" s="38">
         <v>5</v>
@@ -15464,10 +15448,10 @@
     <row r="1032" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1032" s="44"/>
       <c r="B1032" s="45" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C1032" s="46" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D1032" s="47"/>
       <c r="E1032" s="47"/>
@@ -15540,14 +15524,14 @@
         <v>26</v>
       </c>
       <c r="D1037" s="47" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E1037" s="47"/>
       <c r="F1037" s="47"/>
     </row>
     <row r="1038" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1038" s="44" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B1038" s="44"/>
       <c r="C1038" s="47">
@@ -15561,7 +15545,7 @@
     </row>
     <row r="1039" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1039" s="44" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B1039" s="44">
         <v>4</v>
@@ -15609,7 +15593,7 @@
     </row>
     <row r="1042" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1042" s="44" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B1042" s="44"/>
       <c r="C1042" s="47">
@@ -15664,14 +15648,14 @@
         <v>9</v>
       </c>
       <c r="D1045" s="47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E1045" s="47"/>
       <c r="F1045" s="47"/>
     </row>
     <row r="1046" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1046" s="49" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B1046" s="44"/>
       <c r="C1046" s="47">
@@ -15693,7 +15677,7 @@
     </row>
     <row r="1048" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A1048" s="31" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B1048" s="31"/>
       <c r="C1048" s="32"/>
@@ -15715,7 +15699,7 @@
         <v>1</v>
       </c>
       <c r="C1050" s="36" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D1050" s="37"/>
       <c r="E1050" s="37"/>
@@ -15782,7 +15766,7 @@
         <v>56</v>
       </c>
       <c r="D1055" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E1055" s="37"/>
       <c r="F1055" s="37"/>
@@ -15801,7 +15785,7 @@
     </row>
     <row r="1057" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1057" s="34" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B1057" s="38">
         <v>4</v>
@@ -15810,7 +15794,7 @@
         <v>77</v>
       </c>
       <c r="D1057" s="37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E1057" s="37"/>
       <c r="F1057" s="37"/>
@@ -15829,7 +15813,7 @@
     </row>
     <row r="1059" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1059" s="34" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B1059" s="38">
         <v>5</v>
@@ -15866,10 +15850,10 @@
     <row r="1062" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1062" s="38"/>
       <c r="B1062" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C1062" s="40" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D1062" s="41"/>
       <c r="E1062" s="41"/>
@@ -15907,7 +15891,7 @@
         <v>2</v>
       </c>
       <c r="C1065" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D1065" s="41" t="s">
         <v>20</v>
@@ -15929,7 +15913,7 @@
     </row>
     <row r="1067" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1067" s="38" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B1067" s="38">
         <v>3</v>
@@ -15983,7 +15967,7 @@
     </row>
     <row r="1071" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1071" s="38" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B1071" s="38">
         <v>5</v>
@@ -16023,7 +16007,7 @@
         <v>1</v>
       </c>
       <c r="C1074" s="36" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D1074" s="37"/>
       <c r="E1074" s="37"/>
@@ -16109,7 +16093,7 @@
     </row>
     <row r="1081" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1081" s="34" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B1081" s="34">
         <v>4</v>
@@ -16137,7 +16121,7 @@
     </row>
     <row r="1083" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1083" s="34" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B1083" s="34">
         <v>5</v>
@@ -16174,10 +16158,10 @@
     <row r="1086" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1086" s="38"/>
       <c r="B1086" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C1086" s="40" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D1086" s="41"/>
       <c r="E1086" s="41"/>
@@ -16185,13 +16169,13 @@
     </row>
     <row r="1087" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1087" s="38" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B1087" s="38">
         <v>1</v>
       </c>
       <c r="C1087" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D1087" s="41" t="s">
         <v>4</v>
@@ -16239,7 +16223,7 @@
     </row>
     <row r="1091" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1091" s="38" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B1091" s="38">
         <v>3</v>
@@ -16275,7 +16259,7 @@
     </row>
     <row r="1093" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1093" s="38" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B1093" s="38">
         <v>4</v>
@@ -16303,7 +16287,7 @@
     </row>
     <row r="1095" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1095" s="38" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B1095" s="38">
         <v>5</v>
@@ -16343,7 +16327,7 @@
         <v>1</v>
       </c>
       <c r="C1098" s="36" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="D1098" s="37"/>
       <c r="E1098" s="37"/>
@@ -16377,7 +16361,7 @@
     </row>
     <row r="1101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1101" s="34" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B1101" s="34">
         <v>2</v>
@@ -16405,7 +16389,7 @@
     </row>
     <row r="1103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1103" s="34" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B1103" s="34">
         <v>3</v>
@@ -16496,10 +16480,10 @@
     <row r="1110" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1110" s="38"/>
       <c r="B1110" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C1110" s="40" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="D1110" s="41"/>
       <c r="E1110" s="41"/>
@@ -16559,7 +16543,7 @@
     </row>
     <row r="1115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1115" s="38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B1115" s="38">
         <v>3</v>
@@ -16575,7 +16559,7 @@
     </row>
     <row r="1116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1116" s="38" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B1116" s="38"/>
       <c r="C1116" s="41">
@@ -16617,7 +16601,7 @@
     </row>
     <row r="1119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1119" s="38" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B1119" s="38">
         <v>5</v>
@@ -16654,10 +16638,10 @@
     <row r="1122" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1122" s="44"/>
       <c r="B1122" s="45" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C1122" s="46" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D1122" s="47"/>
       <c r="E1122" s="47"/>
@@ -16681,7 +16665,7 @@
     </row>
     <row r="1124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1124" s="44" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B1124" s="44"/>
       <c r="C1124" s="47">
@@ -16701,7 +16685,7 @@
         <v>2</v>
       </c>
       <c r="C1125" s="47" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D1125" s="47" t="s">
         <v>82</v>
@@ -16711,7 +16695,7 @@
     </row>
     <row r="1126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1126" s="44" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B1126" s="44"/>
       <c r="C1126" s="47">
@@ -16827,24 +16811,24 @@
         <v>6</v>
       </c>
       <c r="C1133" s="47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D1133" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E1133" s="47"/>
       <c r="F1133" s="47"/>
     </row>
     <row r="1134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1134" s="44" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B1134" s="44"/>
       <c r="C1134" s="53">
         <v>0.8</v>
       </c>
       <c r="D1134" s="47" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E1134" s="47"/>
       <c r="F1134" s="47"/>
@@ -16867,7 +16851,7 @@
       <c r="A1136" s="44"/>
       <c r="B1136" s="44"/>
       <c r="C1136" s="47" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D1136" s="53">
         <v>0.3</v>
@@ -16877,13 +16861,13 @@
     </row>
     <row r="1137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1137" s="44" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B1137" s="44">
         <v>8</v>
       </c>
       <c r="C1137" s="47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D1137" s="47" t="s">
         <v>41</v>
@@ -16895,7 +16879,7 @@
       <c r="A1138" s="44"/>
       <c r="B1138" s="44"/>
       <c r="C1138" s="47" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D1138" s="53">
         <v>0.6</v>
@@ -16909,7 +16893,7 @@
         <v>9</v>
       </c>
       <c r="C1139" s="47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D1139" s="47" t="s">
         <v>33</v>
@@ -16921,7 +16905,7 @@
       <c r="A1140" s="44"/>
       <c r="B1140" s="44"/>
       <c r="C1140" s="47" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D1140" s="47"/>
       <c r="E1140" s="47"/>
@@ -16945,11 +16929,11 @@
     </row>
     <row r="1142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1142" s="49" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B1142" s="44"/>
       <c r="C1142" s="47" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="D1142" s="53">
         <v>0</v>
@@ -16959,7 +16943,7 @@
     </row>
     <row r="1143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1143" s="44" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B1143" s="44">
         <v>11</v>
@@ -16977,7 +16961,7 @@
       <c r="A1144" s="44"/>
       <c r="B1144" s="44"/>
       <c r="C1144" s="47" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="D1144" s="47"/>
       <c r="E1144" s="47"/>
@@ -16989,7 +16973,7 @@
         <v>12</v>
       </c>
       <c r="C1145" s="47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D1145" s="47" t="s">
         <v>27</v>
@@ -17001,7 +16985,7 @@
       <c r="A1146" s="44"/>
       <c r="B1146" s="44"/>
       <c r="C1146" s="47" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D1146" s="53">
         <v>0</v>
@@ -17027,7 +17011,7 @@
       <c r="A1148" s="44"/>
       <c r="B1148" s="44"/>
       <c r="C1148" s="47" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D1148" s="47"/>
       <c r="E1148" s="47"/>

--- a/FullSeason5.xlsx
+++ b/FullSeason5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ianjpeck/Documents/GitHub/sbparser/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8C2615-A059-1A4D-8A9F-F7A735B2A755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78689B4E-A462-3549-B36B-1A22218BF116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{786F1597-E4AA-4248-AD9D-56520FFD76E3}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16480" xr2:uid="{786F1597-E4AA-4248-AD9D-56520FFD76E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="318">
   <si>
     <t>Month 1</t>
   </si>
@@ -422,9 +422,6 @@
   </si>
   <si>
     <t>Spear Pillar</t>
-  </si>
-  <si>
-    <t>#1 contender Unified Tag</t>
   </si>
   <si>
     <t>Spot in Smash Bros Match</t>
@@ -1047,9 +1044,6 @@
     <t>Guest Appearance by Diddy Kong</t>
   </si>
   <si>
-    <t>#1 contender special (coin match)</t>
-  </si>
-  <si>
     <t>Guest apperance</t>
   </si>
   <si>
@@ -1086,9 +1080,6 @@
     <t>Guest appearance by Pikachu</t>
   </si>
   <si>
-    <t>#1 contender Tag Team</t>
-  </si>
-  <si>
     <t>Disrespect</t>
   </si>
   <si>
@@ -1156,6 +1147,9 @@
   </si>
   <si>
     <t>Final Destination Tournament</t>
+  </si>
+  <si>
+    <t>#1 contender Tag+A827</t>
   </si>
 </sst>
 </file>
@@ -3623,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
@@ -4453,7 +4447,7 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" s="7" t="s">
-        <v>123</v>
+        <v>265</v>
       </c>
       <c r="B205" s="7">
         <v>3</v>
@@ -4517,7 +4511,7 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B209" s="7">
         <v>5</v>
@@ -4555,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
@@ -4617,7 +4611,7 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B217" s="3">
         <v>3</v>
@@ -4709,7 +4703,7 @@
         <v>14</v>
       </c>
       <c r="C224" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D224" s="10"/>
       <c r="E224" s="10"/>
@@ -4717,7 +4711,7 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B225" s="7">
         <v>1</v>
@@ -4823,7 +4817,7 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B233" s="7">
         <v>5</v>
@@ -4861,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
@@ -4869,7 +4863,7 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B237" s="3">
         <v>1</v>
@@ -4979,7 +4973,7 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B245" s="3">
         <v>5</v>
@@ -5017,7 +5011,7 @@
         <v>14</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D248" s="10"/>
       <c r="E248" s="10"/>
@@ -5058,7 +5052,7 @@
         <v>48</v>
       </c>
       <c r="D251" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E251" s="10"/>
       <c r="F251" s="10"/>
@@ -5129,7 +5123,7 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B257" s="7">
         <v>5</v>
@@ -5164,10 +5158,10 @@
     <row r="260" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A260" s="12"/>
       <c r="B260" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C260" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="C260" s="14" t="s">
-        <v>136</v>
       </c>
       <c r="D260" s="15"/>
       <c r="E260" s="15"/>
@@ -5191,7 +5185,7 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B262" s="12"/>
       <c r="C262" s="15">
@@ -5233,7 +5227,7 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A265" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B265" s="12">
         <v>3</v>
@@ -5341,7 +5335,7 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B272" s="12"/>
       <c r="C272" s="15">
@@ -5383,7 +5377,7 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B275" s="12">
         <v>8</v>
@@ -5435,7 +5429,7 @@
     </row>
     <row r="279" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="2"/>
@@ -5455,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D281" s="6"/>
       <c r="E281" s="6"/>
@@ -5463,7 +5457,7 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B282" s="3">
         <v>1</v>
@@ -5472,7 +5466,7 @@
         <v>18</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E282" s="6"/>
       <c r="F282" s="6"/>
@@ -5617,7 +5611,7 @@
         <v>14</v>
       </c>
       <c r="C293" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D293" s="10"/>
       <c r="E293" s="10"/>
@@ -5625,7 +5619,7 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B294" s="7">
         <v>1</v>
@@ -5705,7 +5699,7 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B300" s="7">
         <v>4</v>
@@ -5733,7 +5727,7 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A302" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B302" s="7">
         <v>5</v>
@@ -5771,7 +5765,7 @@
         <v>1</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D305" s="6"/>
       <c r="E305" s="6"/>
@@ -5779,7 +5773,7 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B306" s="3">
         <v>1</v>
@@ -5835,7 +5829,7 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B310" s="3">
         <v>3</v>
@@ -5863,7 +5857,7 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A312" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B312" s="3">
         <v>4</v>
@@ -5891,7 +5885,7 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B314" s="3">
         <v>5</v>
@@ -5929,7 +5923,7 @@
         <v>14</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D317" s="10"/>
       <c r="E317" s="10"/>
@@ -6043,7 +6037,7 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B326" s="7">
         <v>5</v>
@@ -6081,7 +6075,7 @@
         <v>1</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D329" s="6"/>
       <c r="E329" s="6"/>
@@ -6095,7 +6089,7 @@
         <v>1</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D330" s="6" t="s">
         <v>8</v>
@@ -6203,7 +6197,7 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B338" s="3">
         <v>5</v>
@@ -6241,7 +6235,7 @@
         <v>14</v>
       </c>
       <c r="C341" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D341" s="10"/>
       <c r="E341" s="10"/>
@@ -6329,7 +6323,7 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A348" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B348" s="7">
         <v>4</v>
@@ -6357,7 +6351,7 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A350" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B350" s="7">
         <v>5</v>
@@ -6392,10 +6386,10 @@
     <row r="353" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A353" s="12"/>
       <c r="B353" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C353" s="14" t="s">
         <v>153</v>
-      </c>
-      <c r="C353" s="14" t="s">
-        <v>154</v>
       </c>
       <c r="D353" s="15"/>
       <c r="E353" s="15"/>
@@ -6511,7 +6505,7 @@
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A361" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B361" s="12"/>
       <c r="C361" s="15">
@@ -6553,7 +6547,7 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B364" s="12">
         <v>6</v>
@@ -6573,7 +6567,7 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A365" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B365" s="12"/>
       <c r="C365" s="15">
@@ -6591,7 +6585,7 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A366" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B366" s="12">
         <v>7</v>
@@ -6611,7 +6605,7 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A367" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B367" s="12"/>
       <c r="C367" s="15">
@@ -6663,7 +6657,7 @@
         <v>9</v>
       </c>
       <c r="C370" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D370" s="15" t="s">
         <v>9</v>
@@ -6673,7 +6667,7 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A371" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B371" s="12"/>
       <c r="C371" s="15">
@@ -6687,7 +6681,7 @@
     </row>
     <row r="372" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B372" s="1"/>
       <c r="C372" s="2"/>
@@ -6707,7 +6701,7 @@
         <v>1</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D374" s="6"/>
       <c r="E374" s="6"/>
@@ -6793,7 +6787,7 @@
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A381" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B381" s="3">
         <v>4</v>
@@ -6809,7 +6803,7 @@
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A382" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B382" s="3"/>
       <c r="C382" s="6">
@@ -6823,7 +6817,7 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A383" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B383" s="3">
         <v>5</v>
@@ -6839,7 +6833,7 @@
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A384" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B384" s="3"/>
       <c r="C384" s="6">
@@ -6863,7 +6857,7 @@
         <v>14</v>
       </c>
       <c r="C386" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D386" s="10"/>
       <c r="E386" s="10"/>
@@ -6875,7 +6869,7 @@
         <v>1</v>
       </c>
       <c r="C387" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D387" s="10" t="s">
         <v>21</v>
@@ -6897,7 +6891,7 @@
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A389" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B389" s="7">
         <v>2</v>
@@ -6951,7 +6945,7 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A393" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B393" s="7">
         <v>4</v>
@@ -7007,7 +7001,7 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A396" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B396" s="7"/>
       <c r="C396" s="10">
@@ -7035,7 +7029,7 @@
         <v>1</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D398" s="6"/>
       <c r="E398" s="6"/>
@@ -7189,7 +7183,7 @@
         <v>14</v>
       </c>
       <c r="C410" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D410" s="10"/>
       <c r="E410" s="10"/>
@@ -7253,7 +7247,7 @@
         <v>3</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D415" s="10" t="s">
         <v>20</v>
@@ -7339,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D422" s="6"/>
       <c r="E422" s="6"/>
@@ -7487,7 +7481,7 @@
         <v>14</v>
       </c>
       <c r="C434" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D434" s="10"/>
       <c r="E434" s="10"/>
@@ -7573,13 +7567,13 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A441" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B441" s="7">
         <v>4</v>
       </c>
       <c r="C441" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D441" s="10" t="s">
         <v>70</v>
@@ -7589,7 +7583,7 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A442" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B442" s="7"/>
       <c r="C442" s="10">
@@ -7603,7 +7597,7 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A443" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B443" s="7">
         <v>5</v>
@@ -7619,7 +7613,7 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A444" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B444" s="7"/>
       <c r="C444" s="10">
@@ -7640,10 +7634,10 @@
     <row r="446" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A446" s="12"/>
       <c r="B446" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C446" s="14" t="s">
         <v>176</v>
-      </c>
-      <c r="C446" s="14" t="s">
-        <v>177</v>
       </c>
       <c r="D446" s="15"/>
       <c r="E446" s="15"/>
@@ -7735,7 +7729,7 @@
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A452" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B452" s="12"/>
       <c r="C452" s="15">
@@ -7765,7 +7759,7 @@
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A454" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B454" s="12"/>
       <c r="C454" s="15">
@@ -7797,7 +7791,7 @@
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A456" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B456" s="12"/>
       <c r="C456" s="15">
@@ -7822,7 +7816,7 @@
         <v>9</v>
       </c>
       <c r="D457" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E457" s="15"/>
       <c r="F457" s="15"/>
@@ -7857,7 +7851,7 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A460" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B460" s="12"/>
       <c r="C460" s="15">
@@ -7887,7 +7881,7 @@
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A462" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B462" s="12"/>
       <c r="C462" s="15">
@@ -7901,7 +7895,7 @@
     </row>
     <row r="463" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A463" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B463" s="1"/>
       <c r="C463" s="2"/>
@@ -7921,7 +7915,7 @@
         <v>1</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D465" s="6"/>
       <c r="E465" s="6"/>
@@ -7936,7 +7930,7 @@
         <v>70</v>
       </c>
       <c r="D466" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E466" s="6"/>
       <c r="F466" s="6"/>
@@ -8049,7 +8043,7 @@
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A475" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B475" s="3"/>
       <c r="C475" s="6">
@@ -8073,7 +8067,7 @@
         <v>14</v>
       </c>
       <c r="C477" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D477" s="10"/>
       <c r="E477" s="10"/>
@@ -8107,7 +8101,7 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A480" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B480" s="7">
         <v>2</v>
@@ -8161,7 +8155,7 @@
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A484" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B484" s="7">
         <v>4</v>
@@ -8177,7 +8171,7 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A485" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B485" s="7"/>
       <c r="C485" s="10">
@@ -8191,7 +8185,7 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A486" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B486" s="7">
         <v>5</v>
@@ -8229,7 +8223,7 @@
         <v>1</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D489" s="6"/>
       <c r="E489" s="6"/>
@@ -8241,7 +8235,7 @@
         <v>1</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D490" s="6" t="s">
         <v>34</v>
@@ -8269,7 +8263,7 @@
         <v>2</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D492" s="6" t="s">
         <v>32</v>
@@ -8389,7 +8383,7 @@
         <v>14</v>
       </c>
       <c r="C501" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D501" s="10"/>
       <c r="E501" s="10"/>
@@ -8397,7 +8391,7 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A502" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B502" s="7">
         <v>1</v>
@@ -8541,7 +8535,7 @@
         <v>1</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D513" s="6"/>
       <c r="E513" s="6"/>
@@ -8575,7 +8569,7 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A516" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B516" s="3">
         <v>2</v>
@@ -8584,7 +8578,7 @@
         <v>32</v>
       </c>
       <c r="D516" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E516" s="6"/>
       <c r="F516" s="6"/>
@@ -8779,7 +8773,7 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A532" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B532" s="7">
         <v>4</v>
@@ -8795,7 +8789,7 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A533" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B533" s="7"/>
       <c r="C533" s="10">
@@ -8842,7 +8836,7 @@
     <row r="537" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A537" s="12"/>
       <c r="B537" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C537" s="14" t="s">
         <v>28</v>
@@ -8925,7 +8919,7 @@
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A543" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B543" s="12"/>
       <c r="C543" s="15">
@@ -8967,7 +8961,7 @@
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A546" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B546" s="12">
         <v>5</v>
@@ -8987,7 +8981,7 @@
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A547" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B547" s="12"/>
       <c r="C547" s="15">
@@ -9014,7 +9008,7 @@
         <v>9</v>
       </c>
       <c r="D548" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E548" s="15"/>
       <c r="F548" s="15"/>
@@ -9049,7 +9043,7 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A551" s="19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B551" s="12"/>
       <c r="C551" s="15">
@@ -9063,7 +9057,7 @@
     </row>
     <row r="552" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B552" s="1"/>
       <c r="C552" s="2"/>
@@ -9091,13 +9085,13 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A555" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B555" s="3">
         <v>1</v>
       </c>
       <c r="C555" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D555" s="6" t="s">
         <v>48</v>
@@ -9119,7 +9113,7 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A557" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B557" s="3">
         <v>2</v>
@@ -9243,7 +9237,7 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A567" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B567" s="7">
         <v>1</v>
@@ -9271,7 +9265,7 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A569" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B569" s="7">
         <v>2</v>
@@ -9287,7 +9281,7 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A570" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B570" s="7"/>
       <c r="C570" s="10">
@@ -9301,7 +9295,7 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A571" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B571" s="7">
         <v>3</v>
@@ -9399,7 +9393,7 @@
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A579" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B579" s="3">
         <v>1</v>
@@ -9427,7 +9421,7 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A581" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B581" s="3">
         <v>2</v>
@@ -9455,7 +9449,7 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A583" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B583" s="3">
         <v>3</v>
@@ -9483,7 +9477,7 @@
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A585" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B585" s="3">
         <v>4</v>
@@ -9511,7 +9505,7 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A587" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B587" s="3">
         <v>5</v>
@@ -9587,13 +9581,13 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A593" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B593" s="7">
         <v>2</v>
       </c>
       <c r="C593" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D593" s="10" t="s">
         <v>82</v>
@@ -9615,7 +9609,7 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A595" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B595" s="7">
         <v>3</v>
@@ -9643,7 +9637,7 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A597" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B597" s="7">
         <v>4</v>
@@ -9671,7 +9665,7 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A599" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B599" s="7">
         <v>5</v>
@@ -9689,7 +9683,7 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A600" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B600" s="7"/>
       <c r="C600" s="10">
@@ -9756,7 +9750,7 @@
         <v>54</v>
       </c>
       <c r="D605" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E605" s="6"/>
       <c r="F605" s="6"/>
@@ -9801,7 +9795,7 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A609" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B609" s="3">
         <v>4</v>
@@ -9829,7 +9823,7 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A611" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B611" s="3">
         <v>5</v>
@@ -9875,7 +9869,7 @@
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A615" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B615" s="7">
         <v>1</v>
@@ -9959,7 +9953,7 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A621" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B621" s="7">
         <v>4</v>
@@ -9987,7 +9981,7 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A623" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B623" s="7">
         <v>5</v>
@@ -10022,22 +10016,22 @@
     <row r="626" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A626" s="12"/>
       <c r="B626" s="13" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C626" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D626" s="15"/>
       <c r="E626" s="15" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F626" s="15" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A627" s="12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B627" s="12">
         <v>1</v>
@@ -10046,7 +10040,7 @@
         <v>114</v>
       </c>
       <c r="D627" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E627" s="15"/>
       <c r="F627" s="25"/>
@@ -10065,7 +10059,7 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A629" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B629" s="12">
         <v>2</v>
@@ -10093,7 +10087,7 @@
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A631" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B631" s="12">
         <v>3</v>
@@ -10121,7 +10115,7 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A633" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B633" s="12">
         <v>4</v>
@@ -10149,7 +10143,7 @@
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A635" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B635" s="12">
         <v>5</v>
@@ -10177,7 +10171,7 @@
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A637" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B637" s="12">
         <v>6</v>
@@ -10205,7 +10199,7 @@
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A639" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B639" s="12">
         <v>7</v>
@@ -10233,7 +10227,7 @@
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A641" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B641" s="12">
         <v>8</v>
@@ -10261,7 +10255,7 @@
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A643" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B643" s="12">
         <v>9</v>
@@ -10289,7 +10283,7 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A645" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B645" s="12">
         <v>10</v>
@@ -10317,7 +10311,7 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A647" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B647" s="12">
         <v>11</v>
@@ -10345,13 +10339,13 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A649" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B649" s="12">
         <v>12</v>
       </c>
       <c r="C649" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D649" s="15" t="s">
         <v>86</v>
@@ -10373,7 +10367,7 @@
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A651" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B651" s="12">
         <v>13</v>
@@ -10401,7 +10395,7 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A653" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B653" s="12">
         <v>14</v>
@@ -10429,7 +10423,7 @@
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A655" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B655" s="12">
         <v>15</v>
@@ -10457,7 +10451,7 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A657" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B657" s="26">
         <v>1</v>
@@ -10485,7 +10479,7 @@
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A659" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B659" s="26">
         <v>2</v>
@@ -10513,7 +10507,7 @@
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A661" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B661" s="26">
         <v>3</v>
@@ -10541,7 +10535,7 @@
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A663" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B663" s="26">
         <v>4</v>
@@ -10569,7 +10563,7 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A665" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B665" s="26">
         <v>5</v>
@@ -10597,7 +10591,7 @@
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A667" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B667" s="26">
         <v>6</v>
@@ -10625,7 +10619,7 @@
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A669" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B669" s="26">
         <v>7</v>
@@ -10653,7 +10647,7 @@
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A671" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B671" s="26">
         <v>8</v>
@@ -10681,7 +10675,7 @@
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A673" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B673" s="26">
         <v>9</v>
@@ -10709,7 +10703,7 @@
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A675" s="26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B675" s="26">
         <v>10</v>
@@ -10737,7 +10731,7 @@
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A677" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B677" s="26">
         <v>11</v>
@@ -10765,7 +10759,7 @@
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A679" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B679" s="29">
         <v>12</v>
@@ -10793,7 +10787,7 @@
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A681" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B681" s="26">
         <v>13</v>
@@ -10821,7 +10815,7 @@
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A683" s="26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B683" s="26">
         <v>14</v>
@@ -10849,7 +10843,7 @@
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A685" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B685" s="26">
         <v>15</v>
@@ -10877,7 +10871,7 @@
     </row>
     <row r="687" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="2"/>
@@ -10905,7 +10899,7 @@
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A690" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B690" s="3">
         <v>1</v>
@@ -11011,7 +11005,7 @@
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A698" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B698" s="3">
         <v>5</v>
@@ -11020,7 +11014,7 @@
         <v>31</v>
       </c>
       <c r="D698" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E698" s="6"/>
       <c r="F698" s="6"/>
@@ -11057,7 +11051,7 @@
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A702" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B702" s="7">
         <v>1</v>
@@ -11111,7 +11105,7 @@
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A706" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B706" s="7">
         <v>3</v>
@@ -11139,7 +11133,7 @@
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A708" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B708" s="7">
         <v>4</v>
@@ -11167,7 +11161,7 @@
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A710" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B710" s="7">
         <v>5</v>
@@ -11213,7 +11207,7 @@
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A714" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B714" s="3">
         <v>1</v>
@@ -11267,7 +11261,7 @@
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A718" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B718" s="3">
         <v>3</v>
@@ -11283,7 +11277,7 @@
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A719" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B719" s="3"/>
       <c r="C719" s="6">
@@ -11297,7 +11291,7 @@
     </row>
     <row r="720" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A720" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B720" s="3">
         <v>4</v>
@@ -11325,7 +11319,7 @@
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A722" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B722" s="3">
         <v>5</v>
@@ -11363,7 +11357,7 @@
         <v>14</v>
       </c>
       <c r="C725" s="9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D725" s="10"/>
       <c r="E725" s="10"/>
@@ -11423,7 +11417,7 @@
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A730" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B730" s="7">
         <v>3</v>
@@ -11439,7 +11433,7 @@
     </row>
     <row r="731" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A731" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B731" s="7"/>
       <c r="C731" s="10">
@@ -11453,7 +11447,7 @@
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A732" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B732" s="7">
         <v>4</v>
@@ -11469,7 +11463,7 @@
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A733" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B733" s="7"/>
       <c r="C733" s="10">
@@ -11483,7 +11477,7 @@
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A734" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B734" s="7">
         <v>5</v>
@@ -11607,13 +11601,13 @@
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A744" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B744" s="3">
         <v>4</v>
       </c>
       <c r="C744" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D744" s="6" t="s">
         <v>30</v>
@@ -11635,7 +11629,7 @@
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A746" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B746" s="3">
         <v>5</v>
@@ -11717,7 +11711,7 @@
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A752" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B752" s="7">
         <v>2</v>
@@ -11771,7 +11765,7 @@
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A756" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B756" s="7">
         <v>4</v>
@@ -11799,7 +11793,7 @@
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A758" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B758" s="7">
         <v>5</v>
@@ -11817,7 +11811,7 @@
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A759" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B759" s="7"/>
       <c r="C759" s="10">
@@ -11840,10 +11834,10 @@
     <row r="761" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A761" s="12"/>
       <c r="B761" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C761" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D761" s="15"/>
       <c r="E761" s="15"/>
@@ -11937,7 +11931,7 @@
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A767" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B767" s="12"/>
       <c r="C767" s="15">
@@ -11968,12 +11962,12 @@
         <v>13</v>
       </c>
       <c r="F768" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A769" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B769" s="12"/>
       <c r="C769" s="15">
@@ -12041,7 +12035,7 @@
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A773" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B773" s="12"/>
       <c r="C773" s="15">
@@ -12077,7 +12071,7 @@
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A775" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B775" s="12"/>
       <c r="C775" s="15">
@@ -12095,7 +12089,7 @@
     </row>
     <row r="776" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A776" s="31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B776" s="31"/>
       <c r="C776" s="32"/>
@@ -12266,10 +12260,10 @@
     <row r="790" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A790" s="38"/>
       <c r="B790" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C790" s="40" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D790" s="41"/>
       <c r="E790" s="41"/>
@@ -12329,7 +12323,7 @@
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A795" s="38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B795" s="38">
         <v>3</v>
@@ -12423,7 +12417,7 @@
         <v>1</v>
       </c>
       <c r="C802" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D802" s="37"/>
       <c r="E802" s="37"/>
@@ -12518,7 +12512,7 @@
         <v>52</v>
       </c>
       <c r="D809" s="37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E809" s="37"/>
       <c r="F809" s="37"/>
@@ -12574,10 +12568,10 @@
     <row r="814" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A814" s="38"/>
       <c r="B814" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C814" s="40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D814" s="41"/>
       <c r="E814" s="41"/>
@@ -12637,13 +12631,13 @@
     </row>
     <row r="819" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A819" s="38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B819" s="38">
         <v>3</v>
       </c>
       <c r="C819" s="41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D819" s="41" t="s">
         <v>82</v>
@@ -12693,7 +12687,7 @@
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A823" s="38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B823" s="38">
         <v>5</v>
@@ -12733,7 +12727,7 @@
         <v>1</v>
       </c>
       <c r="C826" s="36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D826" s="37"/>
       <c r="E826" s="37"/>
@@ -12747,7 +12741,7 @@
         <v>1</v>
       </c>
       <c r="C827" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D827" s="43" t="s">
         <v>94</v>
@@ -12859,7 +12853,7 @@
         <v>5</v>
       </c>
       <c r="C835" s="37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D835" s="37" t="s">
         <v>7</v>
@@ -12890,10 +12884,10 @@
     <row r="838" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A838" s="38"/>
       <c r="B838" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C838" s="40" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D838" s="41"/>
       <c r="E838" s="41"/>
@@ -12927,7 +12921,7 @@
     </row>
     <row r="841" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A841" s="38" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B841" s="38">
         <v>2</v>
@@ -13042,10 +13036,10 @@
     <row r="850" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A850" s="44"/>
       <c r="B850" s="45" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C850" s="46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D850" s="47"/>
       <c r="E850" s="47"/>
@@ -13219,7 +13213,7 @@
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A862" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B862" s="44"/>
       <c r="C862" s="47">
@@ -13249,7 +13243,7 @@
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A864" s="49" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B864" s="44"/>
       <c r="C864" s="47">
@@ -13263,7 +13257,7 @@
     </row>
     <row r="865" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A865" s="50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B865" s="50">
         <v>8</v>
@@ -13272,14 +13266,14 @@
         <v>86</v>
       </c>
       <c r="D865" s="51" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E865" s="51"/>
       <c r="F865" s="51"/>
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A866" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B866" s="12"/>
       <c r="C866" s="15">
@@ -13293,7 +13287,7 @@
     </row>
     <row r="867" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A867" s="31" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B867" s="31"/>
       <c r="C867" s="32"/>
@@ -13315,7 +13309,7 @@
         <v>1</v>
       </c>
       <c r="C869" s="36" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D869" s="37"/>
       <c r="E869" s="37"/>
@@ -13375,7 +13369,7 @@
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A874" s="34" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B874" s="34">
         <v>3</v>
@@ -13466,10 +13460,10 @@
     <row r="881" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A881" s="38"/>
       <c r="B881" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C881" s="40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D881" s="41"/>
       <c r="E881" s="41"/>
@@ -13555,7 +13549,7 @@
     </row>
     <row r="888" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A888" s="38" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B888" s="38">
         <v>4</v>
@@ -13564,7 +13558,7 @@
         <v>27</v>
       </c>
       <c r="D888" s="52" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E888" s="41" t="s">
         <v>21</v>
@@ -13631,7 +13625,7 @@
         <v>1</v>
       </c>
       <c r="C893" s="36" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D893" s="37"/>
       <c r="E893" s="37"/>
@@ -13691,7 +13685,7 @@
     </row>
     <row r="898" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A898" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B898" s="34">
         <v>3</v>
@@ -13782,10 +13776,10 @@
     <row r="905" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A905" s="38"/>
       <c r="B905" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C905" s="40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D905" s="41"/>
       <c r="E905" s="41"/>
@@ -13845,7 +13839,7 @@
     </row>
     <row r="910" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A910" s="38" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B910" s="38">
         <v>3</v>
@@ -13861,7 +13855,7 @@
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A911" s="38" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B911" s="38"/>
       <c r="C911" s="41">
@@ -13879,7 +13873,7 @@
         <v>4</v>
       </c>
       <c r="C912" s="41" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D912" s="41" t="s">
         <v>83</v>
@@ -13901,7 +13895,7 @@
     </row>
     <row r="914" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A914" s="38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B914" s="38">
         <v>5</v>
@@ -13941,7 +13935,7 @@
         <v>1</v>
       </c>
       <c r="C917" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D917" s="37"/>
       <c r="E917" s="37"/>
@@ -13956,7 +13950,7 @@
         <v>34</v>
       </c>
       <c r="D918" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E918" s="37"/>
       <c r="F918" s="37"/>
@@ -14088,10 +14082,10 @@
     <row r="929" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A929" s="38"/>
       <c r="B929" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C929" s="40" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D929" s="41"/>
       <c r="E929" s="41"/>
@@ -14103,7 +14097,7 @@
         <v>1</v>
       </c>
       <c r="C930" s="41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D930" s="41" t="s">
         <v>21</v>
@@ -14238,10 +14232,10 @@
     <row r="941" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A941" s="44"/>
       <c r="B941" s="45" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C941" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D941" s="47"/>
       <c r="E941" s="47"/>
@@ -14265,7 +14259,7 @@
     </row>
     <row r="943" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A943" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B943" s="44"/>
       <c r="C943" s="47">
@@ -14295,7 +14289,7 @@
     </row>
     <row r="945" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A945" s="44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B945" s="44"/>
       <c r="C945" s="47">
@@ -14325,7 +14319,7 @@
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A947" s="44" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B947" s="44"/>
       <c r="C947" s="47">
@@ -14355,7 +14349,7 @@
     </row>
     <row r="949" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A949" s="44" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B949" s="44"/>
       <c r="C949" s="47">
@@ -14389,7 +14383,7 @@
     </row>
     <row r="951" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A951" s="44" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B951" s="44"/>
       <c r="C951" s="47">
@@ -14423,7 +14417,7 @@
     </row>
     <row r="953" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A953" s="44" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B953" s="44"/>
       <c r="C953" s="47">
@@ -14455,7 +14449,7 @@
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A955" s="49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B955" s="44"/>
       <c r="C955" s="47">
@@ -14471,7 +14465,7 @@
     </row>
     <row r="956" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A956" s="44" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B956" s="44"/>
       <c r="C956" s="47"/>
@@ -14489,7 +14483,7 @@
     </row>
     <row r="958" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A958" s="31" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B958" s="31"/>
       <c r="C958" s="32"/>
@@ -14511,7 +14505,7 @@
         <v>1</v>
       </c>
       <c r="C960" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D960" s="37"/>
       <c r="E960" s="37"/>
@@ -14660,10 +14654,10 @@
     <row r="972" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A972" s="38"/>
       <c r="B972" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C972" s="40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D972" s="41"/>
       <c r="E972" s="41"/>
@@ -14819,7 +14813,7 @@
         <v>1</v>
       </c>
       <c r="C984" s="36" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D984" s="37"/>
       <c r="E984" s="37"/>
@@ -14827,7 +14821,7 @@
     </row>
     <row r="985" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A985" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B985" s="34">
         <v>1</v>
@@ -14890,7 +14884,7 @@
         <v>94</v>
       </c>
       <c r="D989" s="43" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E989" s="37" t="s">
         <v>54</v>
@@ -14984,10 +14978,10 @@
     <row r="996" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A996" s="38"/>
       <c r="B996" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C996" s="40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D996" s="41"/>
       <c r="E996" s="41"/>
@@ -14995,7 +14989,7 @@
     </row>
     <row r="997" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A997" s="38" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B997" s="38">
         <v>1</v>
@@ -15075,13 +15069,13 @@
     </row>
     <row r="1003" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1003" s="38" t="s">
-        <v>283</v>
+        <v>128</v>
       </c>
       <c r="B1003" s="38">
         <v>4</v>
       </c>
       <c r="C1003" s="41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D1003" s="41" t="s">
         <v>82</v>
@@ -15143,7 +15137,7 @@
         <v>1</v>
       </c>
       <c r="C1008" s="36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D1008" s="37"/>
       <c r="E1008" s="37"/>
@@ -15184,7 +15178,7 @@
         <v>34</v>
       </c>
       <c r="D1011" s="37" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E1011" s="37"/>
       <c r="F1011" s="37"/>
@@ -15292,10 +15286,10 @@
     <row r="1020" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1020" s="38"/>
       <c r="B1020" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1020" s="40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D1020" s="41"/>
       <c r="E1020" s="41"/>
@@ -15303,7 +15297,7 @@
     </row>
     <row r="1021" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1021" s="38" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B1021" s="38">
         <v>1</v>
@@ -15331,7 +15325,7 @@
     </row>
     <row r="1023" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1023" s="38" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B1023" s="38">
         <v>2</v>
@@ -15363,7 +15357,7 @@
         <v>3</v>
       </c>
       <c r="C1025" s="41" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D1025" s="41" t="s">
         <v>20</v>
@@ -15411,7 +15405,7 @@
     </row>
     <row r="1029" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1029" s="38" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B1029" s="38">
         <v>5</v>
@@ -15448,10 +15442,10 @@
     <row r="1032" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1032" s="44"/>
       <c r="B1032" s="45" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C1032" s="46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D1032" s="47"/>
       <c r="E1032" s="47"/>
@@ -15524,14 +15518,14 @@
         <v>26</v>
       </c>
       <c r="D1037" s="47" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E1037" s="47"/>
       <c r="F1037" s="47"/>
     </row>
     <row r="1038" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1038" s="44" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B1038" s="44"/>
       <c r="C1038" s="47">
@@ -15545,7 +15539,7 @@
     </row>
     <row r="1039" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1039" s="44" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B1039" s="44">
         <v>4</v>
@@ -15593,7 +15587,7 @@
     </row>
     <row r="1042" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1042" s="44" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B1042" s="44"/>
       <c r="C1042" s="47">
@@ -15655,7 +15649,7 @@
     </row>
     <row r="1046" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1046" s="49" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B1046" s="44"/>
       <c r="C1046" s="47">
@@ -15677,7 +15671,7 @@
     </row>
     <row r="1048" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A1048" s="31" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B1048" s="31"/>
       <c r="C1048" s="32"/>
@@ -15699,7 +15693,7 @@
         <v>1</v>
       </c>
       <c r="C1050" s="36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D1050" s="37"/>
       <c r="E1050" s="37"/>
@@ -15785,7 +15779,7 @@
     </row>
     <row r="1057" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1057" s="34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B1057" s="38">
         <v>4</v>
@@ -15813,7 +15807,7 @@
     </row>
     <row r="1059" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1059" s="34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B1059" s="38">
         <v>5</v>
@@ -15850,10 +15844,10 @@
     <row r="1062" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1062" s="38"/>
       <c r="B1062" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1062" s="40" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D1062" s="41"/>
       <c r="E1062" s="41"/>
@@ -15891,7 +15885,7 @@
         <v>2</v>
       </c>
       <c r="C1065" s="41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D1065" s="41" t="s">
         <v>20</v>
@@ -15913,7 +15907,7 @@
     </row>
     <row r="1067" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1067" s="38" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B1067" s="38">
         <v>3</v>
@@ -15967,7 +15961,7 @@
     </row>
     <row r="1071" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1071" s="38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B1071" s="38">
         <v>5</v>
@@ -16007,7 +16001,7 @@
         <v>1</v>
       </c>
       <c r="C1074" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D1074" s="37"/>
       <c r="E1074" s="37"/>
@@ -16093,7 +16087,7 @@
     </row>
     <row r="1081" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1081" s="34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B1081" s="34">
         <v>4</v>
@@ -16121,7 +16115,7 @@
     </row>
     <row r="1083" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1083" s="34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B1083" s="34">
         <v>5</v>
@@ -16158,10 +16152,10 @@
     <row r="1086" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1086" s="38"/>
       <c r="B1086" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1086" s="40" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D1086" s="41"/>
       <c r="E1086" s="41"/>
@@ -16169,7 +16163,7 @@
     </row>
     <row r="1087" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1087" s="38" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B1087" s="38">
         <v>1</v>
@@ -16223,7 +16217,7 @@
     </row>
     <row r="1091" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1091" s="38" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="B1091" s="38">
         <v>3</v>
@@ -16259,7 +16253,7 @@
     </row>
     <row r="1093" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1093" s="38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B1093" s="38">
         <v>4</v>
@@ -16287,7 +16281,7 @@
     </row>
     <row r="1095" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1095" s="38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B1095" s="38">
         <v>5</v>
@@ -16327,7 +16321,7 @@
         <v>1</v>
       </c>
       <c r="C1098" s="36" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D1098" s="37"/>
       <c r="E1098" s="37"/>
@@ -16361,7 +16355,7 @@
     </row>
     <row r="1101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1101" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B1101" s="34">
         <v>2</v>
@@ -16389,7 +16383,7 @@
     </row>
     <row r="1103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1103" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B1103" s="34">
         <v>3</v>
@@ -16480,10 +16474,10 @@
     <row r="1110" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1110" s="38"/>
       <c r="B1110" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C1110" s="40" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D1110" s="41"/>
       <c r="E1110" s="41"/>
@@ -16543,7 +16537,7 @@
     </row>
     <row r="1115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1115" s="38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B1115" s="38">
         <v>3</v>
@@ -16559,7 +16553,7 @@
     </row>
     <row r="1116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1116" s="38" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B1116" s="38"/>
       <c r="C1116" s="41">
@@ -16601,7 +16595,7 @@
     </row>
     <row r="1119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1119" s="38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B1119" s="38">
         <v>5</v>
@@ -16638,10 +16632,10 @@
     <row r="1122" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1122" s="44"/>
       <c r="B1122" s="45" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C1122" s="46" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D1122" s="47"/>
       <c r="E1122" s="47"/>
@@ -16665,7 +16659,7 @@
     </row>
     <row r="1124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1124" s="44" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B1124" s="44"/>
       <c r="C1124" s="47">
@@ -16685,7 +16679,7 @@
         <v>2</v>
       </c>
       <c r="C1125" s="47" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D1125" s="47" t="s">
         <v>82</v>
@@ -16695,7 +16689,7 @@
     </row>
     <row r="1126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1126" s="44" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B1126" s="44"/>
       <c r="C1126" s="47">
@@ -16821,14 +16815,14 @@
     </row>
     <row r="1134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1134" s="44" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B1134" s="44"/>
       <c r="C1134" s="53">
         <v>0.8</v>
       </c>
       <c r="D1134" s="47" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E1134" s="47"/>
       <c r="F1134" s="47"/>
@@ -16851,7 +16845,7 @@
       <c r="A1136" s="44"/>
       <c r="B1136" s="44"/>
       <c r="C1136" s="47" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D1136" s="53">
         <v>0.3</v>
@@ -16861,7 +16855,7 @@
     </row>
     <row r="1137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1137" s="44" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B1137" s="44">
         <v>8</v>
@@ -16879,7 +16873,7 @@
       <c r="A1138" s="44"/>
       <c r="B1138" s="44"/>
       <c r="C1138" s="47" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D1138" s="53">
         <v>0.6</v>
@@ -16905,7 +16899,7 @@
       <c r="A1140" s="44"/>
       <c r="B1140" s="44"/>
       <c r="C1140" s="47" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D1140" s="47"/>
       <c r="E1140" s="47"/>
@@ -16929,11 +16923,11 @@
     </row>
     <row r="1142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1142" s="49" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B1142" s="44"/>
       <c r="C1142" s="47" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D1142" s="53">
         <v>0</v>
@@ -16943,7 +16937,7 @@
     </row>
     <row r="1143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1143" s="44" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B1143" s="44">
         <v>11</v>
@@ -16961,7 +16955,7 @@
       <c r="A1144" s="44"/>
       <c r="B1144" s="44"/>
       <c r="C1144" s="47" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D1144" s="47"/>
       <c r="E1144" s="47"/>
@@ -16985,7 +16979,7 @@
       <c r="A1146" s="44"/>
       <c r="B1146" s="44"/>
       <c r="C1146" s="47" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D1146" s="53">
         <v>0</v>
@@ -17011,7 +17005,7 @@
       <c r="A1148" s="44"/>
       <c r="B1148" s="44"/>
       <c r="C1148" s="47" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D1148" s="47"/>
       <c r="E1148" s="47"/>

--- a/FullSeason5.xlsx
+++ b/FullSeason5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ianjpeck/Documents/GitHub/sbparser/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78689B4E-A462-3549-B36B-1A22218BF116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E35CF5-F23C-9B40-9688-AE0C801C34A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16480" xr2:uid="{786F1597-E4AA-4248-AD9D-56520FFD76E3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="323">
   <si>
     <t>Month 1</t>
   </si>
@@ -1104,24 +1104,9 @@
     <t>Toon Link, ROB, Sonic, Pikachu, Diddy Kong</t>
   </si>
   <si>
-    <t>PL</t>
-  </si>
-  <si>
-    <t>Pikachu 10% Handicap from Tag Team Match</t>
-  </si>
-  <si>
     <t>Pit, Fox, Yoshi, Mr. Game &amp; Watch, Luigi</t>
   </si>
   <si>
-    <t>PL: Self Destruct</t>
-  </si>
-  <si>
-    <t>3,5,2,4,1</t>
-  </si>
-  <si>
-    <t>PL 80%</t>
-  </si>
-  <si>
     <t>Need to outlaw hammers</t>
   </si>
   <si>
@@ -1149,7 +1134,37 @@
     <t>Final Destination Tournament</t>
   </si>
   <si>
-    <t>#1 contender Tag+A827</t>
+    <t>Brawl Scramble</t>
+  </si>
+  <si>
+    <t>Sonic (PL)</t>
+  </si>
+  <si>
+    <t>ROB (PL)</t>
+  </si>
+  <si>
+    <t>Toon Link (PL)</t>
+  </si>
+  <si>
+    <t>Pikachu (PL)</t>
+  </si>
+  <si>
+    <t>Melee Scramble</t>
+  </si>
+  <si>
+    <t>Yoshi (PL)</t>
+  </si>
+  <si>
+    <t>Mr. Game &amp; Watch - W (PL)</t>
+  </si>
+  <si>
+    <t>Mr. Game &amp; Watch (PL)</t>
+  </si>
+  <si>
+    <t>Pit - W (PL)</t>
+  </si>
+  <si>
+    <t>Pikachu 10% Handicap</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1456,9 +1471,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3617,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
@@ -4855,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
@@ -5923,7 +5935,7 @@
         <v>14</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D317" s="10"/>
       <c r="E317" s="10"/>
@@ -7183,7 +7195,7 @@
         <v>14</v>
       </c>
       <c r="C410" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D410" s="10"/>
       <c r="E410" s="10"/>
@@ -10016,17 +10028,17 @@
     <row r="626" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A626" s="12"/>
       <c r="B626" s="13" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C626" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D626" s="15"/>
       <c r="E626" s="15" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F626" s="15" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.2">
@@ -10242,16 +10254,16 @@
       <c r="F641" s="15"/>
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A642" s="54"/>
-      <c r="B642" s="54"/>
-      <c r="C642" s="55">
-        <v>0</v>
-      </c>
-      <c r="D642" s="55">
-        <v>1</v>
-      </c>
-      <c r="E642" s="55"/>
-      <c r="F642" s="55"/>
+      <c r="A642" s="53"/>
+      <c r="B642" s="53"/>
+      <c r="C642" s="54">
+        <v>0</v>
+      </c>
+      <c r="D642" s="54">
+        <v>1</v>
+      </c>
+      <c r="E642" s="54"/>
+      <c r="F642" s="54"/>
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A643" s="12" t="s">
@@ -10354,16 +10366,16 @@
       <c r="F649" s="12"/>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A650" s="54"/>
-      <c r="B650" s="54"/>
-      <c r="C650" s="54">
-        <v>0</v>
-      </c>
-      <c r="D650" s="54">
-        <v>1</v>
-      </c>
-      <c r="E650" s="54"/>
-      <c r="F650" s="54"/>
+      <c r="A650" s="53"/>
+      <c r="B650" s="53"/>
+      <c r="C650" s="53">
+        <v>0</v>
+      </c>
+      <c r="D650" s="53">
+        <v>1</v>
+      </c>
+      <c r="E650" s="53"/>
+      <c r="F650" s="53"/>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A651" s="12" t="s">
@@ -10410,16 +10422,16 @@
       <c r="F653" s="12"/>
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A654" s="54"/>
-      <c r="B654" s="54"/>
-      <c r="C654" s="54">
-        <v>0</v>
-      </c>
-      <c r="D654" s="54">
-        <v>1</v>
-      </c>
-      <c r="E654" s="54"/>
-      <c r="F654" s="54"/>
+      <c r="A654" s="53"/>
+      <c r="B654" s="53"/>
+      <c r="C654" s="53">
+        <v>0</v>
+      </c>
+      <c r="D654" s="53">
+        <v>1</v>
+      </c>
+      <c r="E654" s="53"/>
+      <c r="F654" s="53"/>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A655" s="12" t="s">
@@ -10634,7 +10646,7 @@
       <c r="F669" s="26"/>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A670" s="56"/>
+      <c r="A670" s="55"/>
       <c r="B670" s="26"/>
       <c r="C670" s="26">
         <v>0</v>
@@ -11357,7 +11369,7 @@
         <v>14</v>
       </c>
       <c r="C725" s="9" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D725" s="10"/>
       <c r="E725" s="10"/>
@@ -12263,7 +12275,7 @@
         <v>255</v>
       </c>
       <c r="C790" s="40" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D790" s="41"/>
       <c r="E790" s="41"/>
@@ -12887,7 +12899,7 @@
         <v>255</v>
       </c>
       <c r="C838" s="40" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D838" s="41"/>
       <c r="E838" s="41"/>
@@ -13309,7 +13321,7 @@
         <v>1</v>
       </c>
       <c r="C869" s="36" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D869" s="37"/>
       <c r="E869" s="37"/>
@@ -13625,7 +13637,7 @@
         <v>1</v>
       </c>
       <c r="C893" s="36" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D893" s="37"/>
       <c r="E893" s="37"/>
@@ -13855,7 +13867,7 @@
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A911" s="38" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B911" s="38"/>
       <c r="C911" s="41">
@@ -14813,7 +14825,7 @@
         <v>1</v>
       </c>
       <c r="C984" s="36" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D984" s="37"/>
       <c r="E984" s="37"/>
@@ -16217,7 +16229,7 @@
     </row>
     <row r="1091" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1091" s="38" t="s">
-        <v>317</v>
+        <v>265</v>
       </c>
       <c r="B1091" s="38">
         <v>3</v>
@@ -16799,7 +16811,7 @@
     </row>
     <row r="1133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1133" s="44" t="s">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="B1133" s="44">
         <v>6</v>
@@ -16808,7 +16820,7 @@
         <v>121</v>
       </c>
       <c r="D1133" s="47" t="s">
-        <v>107</v>
+        <v>313</v>
       </c>
       <c r="E1133" s="47"/>
       <c r="F1133" s="47"/>
@@ -16818,11 +16830,11 @@
         <v>301</v>
       </c>
       <c r="B1134" s="44"/>
-      <c r="C1134" s="53">
-        <v>0.8</v>
-      </c>
-      <c r="D1134" s="47" t="s">
-        <v>302</v>
+      <c r="C1134" s="47">
+        <v>1</v>
+      </c>
+      <c r="D1134" s="47">
+        <v>0</v>
       </c>
       <c r="E1134" s="47"/>
       <c r="F1134" s="47"/>
@@ -16833,7 +16845,7 @@
         <v>7</v>
       </c>
       <c r="C1135" s="47" t="s">
-        <v>3</v>
+        <v>314</v>
       </c>
       <c r="D1135" s="47" t="s">
         <v>9</v>
@@ -16844,24 +16856,24 @@
     <row r="1136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1136" s="44"/>
       <c r="B1136" s="44"/>
-      <c r="C1136" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="D1136" s="53">
-        <v>0.3</v>
+      <c r="C1136" s="47">
+        <v>0</v>
+      </c>
+      <c r="D1136" s="47">
+        <v>1</v>
       </c>
       <c r="E1136" s="47"/>
       <c r="F1136" s="47"/>
     </row>
     <row r="1137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1137" s="44" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="B1137" s="44">
         <v>8</v>
       </c>
       <c r="C1137" s="47" t="s">
-        <v>114</v>
+        <v>315</v>
       </c>
       <c r="D1137" s="47" t="s">
         <v>41</v>
@@ -16872,22 +16884,24 @@
     <row r="1138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1138" s="44"/>
       <c r="B1138" s="44"/>
-      <c r="C1138" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="D1138" s="53">
-        <v>0.6</v>
+      <c r="C1138" s="47">
+        <v>0</v>
+      </c>
+      <c r="D1138" s="47">
+        <v>1</v>
       </c>
       <c r="E1138" s="47"/>
       <c r="F1138" s="47"/>
     </row>
     <row r="1139" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1139" s="44"/>
+      <c r="A1139" s="44" t="s">
+        <v>78</v>
+      </c>
       <c r="B1139" s="44">
         <v>9</v>
       </c>
       <c r="C1139" s="47" t="s">
-        <v>109</v>
+        <v>316</v>
       </c>
       <c r="D1139" s="47" t="s">
         <v>33</v>
@@ -16898,22 +16912,24 @@
     <row r="1140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1140" s="44"/>
       <c r="B1140" s="44"/>
-      <c r="C1140" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="D1140" s="47"/>
+      <c r="C1140" s="47">
+        <v>0</v>
+      </c>
+      <c r="D1140" s="47">
+        <v>1</v>
+      </c>
       <c r="E1140" s="47"/>
       <c r="F1140" s="47"/>
     </row>
     <row r="1141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1141" s="44" t="s">
-        <v>75</v>
+        <v>317</v>
       </c>
       <c r="B1141" s="44">
         <v>10</v>
       </c>
       <c r="C1141" s="47" t="s">
-        <v>26</v>
+        <v>318</v>
       </c>
       <c r="D1141" s="47" t="s">
         <v>17</v>
@@ -16923,27 +16939,25 @@
     </row>
     <row r="1142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1142" s="49" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B1142" s="44"/>
-      <c r="C1142" s="47" t="s">
-        <v>305</v>
-      </c>
-      <c r="D1142" s="53">
-        <v>0</v>
+      <c r="C1142" s="47">
+        <v>0</v>
+      </c>
+      <c r="D1142" s="47">
+        <v>1</v>
       </c>
       <c r="E1142" s="47"/>
       <c r="F1142" s="47"/>
     </row>
     <row r="1143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1143" s="44" t="s">
-        <v>306</v>
-      </c>
+      <c r="A1143" s="44"/>
       <c r="B1143" s="44">
         <v>11</v>
       </c>
       <c r="C1143" s="47" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
       <c r="D1143" s="47" t="s">
         <v>43</v>
@@ -16954,10 +16968,12 @@
     <row r="1144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1144" s="44"/>
       <c r="B1144" s="44"/>
-      <c r="C1144" s="47" t="s">
-        <v>307</v>
-      </c>
-      <c r="D1144" s="47"/>
+      <c r="C1144" s="47">
+        <v>1</v>
+      </c>
+      <c r="D1144" s="47">
+        <v>0</v>
+      </c>
       <c r="E1144" s="47"/>
       <c r="F1144" s="47"/>
     </row>
@@ -16967,7 +16983,7 @@
         <v>12</v>
       </c>
       <c r="C1145" s="47" t="s">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="D1145" s="47" t="s">
         <v>27</v>
@@ -16978,22 +16994,24 @@
     <row r="1146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1146" s="44"/>
       <c r="B1146" s="44"/>
-      <c r="C1146" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="D1146" s="53">
-        <v>0</v>
+      <c r="C1146" s="47">
+        <v>0</v>
+      </c>
+      <c r="D1146" s="47">
+        <v>1</v>
       </c>
       <c r="E1146" s="47"/>
       <c r="F1146" s="47"/>
     </row>
     <row r="1147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1147" s="44"/>
+      <c r="A1147" s="44" t="s">
+        <v>75</v>
+      </c>
       <c r="B1147" s="44">
         <v>13</v>
       </c>
       <c r="C1147" s="47" t="s">
-        <v>27</v>
+        <v>321</v>
       </c>
       <c r="D1147" s="47" t="s">
         <v>83</v>
@@ -17004,10 +17022,12 @@
     <row r="1148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1148" s="44"/>
       <c r="B1148" s="44"/>
-      <c r="C1148" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="D1148" s="47"/>
+      <c r="C1148" s="47">
+        <v>1</v>
+      </c>
+      <c r="D1148" s="47">
+        <v>0</v>
+      </c>
       <c r="E1148" s="47"/>
       <c r="F1148" s="47"/>
     </row>

--- a/FullSeason5.xlsx
+++ b/FullSeason5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ianjpeck/Documents/GitHub/sbparser/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835D1831-37CA-F247-9A7C-1053CF574247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A10C61B-7DBC-6446-978B-42E710A2B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{C96D0F46-2D53-AF4F-A06C-8FE540EC6340}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16500" xr2:uid="{C96D0F46-2D53-AF4F-A06C-8FE540EC6340}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="324">
   <si>
     <t>Month 1</t>
   </si>
@@ -1081,9 +1081,6 @@
   </si>
   <si>
     <t>Coin Match, 1st time champion has lost at Championship Cruise</t>
-  </si>
-  <si>
-    <t>Hardcore Chamionship</t>
   </si>
   <si>
     <t>Wolf 140% Handicap</t>
@@ -15574,7 +15571,7 @@
     </row>
     <row r="1038" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1038" s="46" t="s">
-        <v>295</v>
+        <v>72</v>
       </c>
       <c r="B1038" s="46">
         <v>4</v>
@@ -15622,7 +15619,7 @@
     </row>
     <row r="1041" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1041" s="46" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B1041" s="46"/>
       <c r="C1041" s="49">
@@ -15684,7 +15681,7 @@
     </row>
     <row r="1045" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1045" s="51" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B1045" s="46"/>
       <c r="C1045" s="49">
@@ -15698,7 +15695,7 @@
     </row>
     <row r="1046" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A1046" s="33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B1046" s="33"/>
       <c r="C1046" s="34"/>
@@ -15934,7 +15931,7 @@
     </row>
     <row r="1065" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1065" s="40" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B1065" s="40">
         <v>3</v>
@@ -16190,7 +16187,7 @@
     </row>
     <row r="1085" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1085" s="40" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B1085" s="40">
         <v>1</v>
@@ -16348,7 +16345,7 @@
         <v>1</v>
       </c>
       <c r="C1096" s="38" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D1096" s="39"/>
       <c r="E1096" s="39"/>
@@ -16504,7 +16501,7 @@
         <v>262</v>
       </c>
       <c r="C1108" s="42" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D1108" s="43"/>
       <c r="E1108" s="43"/>
@@ -16580,7 +16577,7 @@
     </row>
     <row r="1114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1114" s="40" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B1114" s="40"/>
       <c r="C1114" s="43">
@@ -16659,10 +16656,10 @@
     <row r="1120" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1120" s="46"/>
       <c r="B1120" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1120" s="48" t="s">
         <v>304</v>
-      </c>
-      <c r="C1120" s="48" t="s">
-        <v>305</v>
       </c>
       <c r="D1120" s="49"/>
       <c r="E1120" s="49"/>
@@ -16686,7 +16683,7 @@
     </row>
     <row r="1122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1122" s="46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1122" s="46"/>
       <c r="C1122" s="49">
@@ -16716,7 +16713,7 @@
     </row>
     <row r="1124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1124" s="46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1124" s="46"/>
       <c r="C1124" s="49">
@@ -16826,7 +16823,7 @@
     </row>
     <row r="1131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1131" s="46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B1131" s="46">
         <v>6</v>
@@ -16835,14 +16832,14 @@
         <v>122</v>
       </c>
       <c r="D1131" s="49" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E1131" s="49"/>
       <c r="F1131" s="49"/>
     </row>
     <row r="1132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1132" s="46" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B1132" s="46"/>
       <c r="C1132" s="49">
@@ -16856,13 +16853,13 @@
     </row>
     <row r="1133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1133" s="51" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1133" s="46">
         <v>7</v>
       </c>
       <c r="C1133" s="49" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D1133" s="49" t="s">
         <v>9</v>
@@ -16884,13 +16881,13 @@
     </row>
     <row r="1135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1135" s="46" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B1135" s="46">
         <v>8</v>
       </c>
       <c r="C1135" s="49" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D1135" s="49" t="s">
         <v>41</v>
@@ -16912,13 +16909,13 @@
     </row>
     <row r="1137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1137" s="46" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B1137" s="46">
         <v>10</v>
       </c>
       <c r="C1137" s="49" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D1137" s="49" t="s">
         <v>33</v>
@@ -16940,13 +16937,13 @@
     </row>
     <row r="1139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1139" s="46" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B1139" s="46">
         <v>11</v>
       </c>
       <c r="C1139" s="49" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D1139" s="49" t="s">
         <v>17</v>
@@ -16956,7 +16953,7 @@
     </row>
     <row r="1140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1140" s="51" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B1140" s="46"/>
       <c r="C1140" s="49">
@@ -16970,13 +16967,13 @@
     </row>
     <row r="1141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1141" s="46" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B1141" s="46">
         <v>12</v>
       </c>
       <c r="C1141" s="49" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D1141" s="49" t="s">
         <v>43</v>
@@ -16998,13 +16995,13 @@
     </row>
     <row r="1143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1143" s="46" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B1143" s="46">
         <v>13</v>
       </c>
       <c r="C1143" s="49" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D1143" s="49" t="s">
         <v>27</v>
@@ -17026,13 +17023,13 @@
     </row>
     <row r="1145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1145" s="46" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B1145" s="46">
         <v>14</v>
       </c>
       <c r="C1145" s="49" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D1145" s="49" t="s">
         <v>83</v>

--- a/FullSeason5.xlsx
+++ b/FullSeason5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ianjpeck/Documents/GitHub/sbparser/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A10C61B-7DBC-6446-978B-42E710A2B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA659EB-E770-D449-A597-B41991FA4E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16500" xr2:uid="{C96D0F46-2D53-AF4F-A06C-8FE540EC6340}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{C96D0F46-2D53-AF4F-A06C-8FE540EC6340}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="328">
   <si>
     <t>Month 1</t>
   </si>
@@ -1128,9 +1128,6 @@
     <t>ROB (PL)</t>
   </si>
   <si>
-    <t>Toon Link (PL)</t>
-  </si>
-  <si>
     <t>Pikachu (PL)</t>
   </si>
   <si>
@@ -1146,9 +1143,6 @@
     <t>Mr. Game &amp; Watch (PL)</t>
   </si>
   <si>
-    <t>Pit - W (PL)</t>
-  </si>
-  <si>
     <t>1 vs. 1 - Melee Scramble</t>
   </si>
   <si>
@@ -1168,6 +1162,24 @@
   </si>
   <si>
     <t>3 vs. 4 - Brawl Championship</t>
+  </si>
+  <si>
+    <t>Toon Link - W (Defending)</t>
+  </si>
+  <si>
+    <t>Toon Link (PL) (Defending)</t>
+  </si>
+  <si>
+    <t>Pit - W (PL) (Defending)</t>
+  </si>
+  <si>
+    <t>Toon Link (Defending)</t>
+  </si>
+  <si>
+    <t>Luigi - W (Defending)</t>
+  </si>
+  <si>
+    <t>Luigi (Defending)</t>
   </si>
 </sst>
 </file>
@@ -10073,7 +10085,7 @@
         <v>1</v>
       </c>
       <c r="C627" s="15" t="s">
-        <v>115</v>
+        <v>325</v>
       </c>
       <c r="D627" s="15" t="s">
         <v>193</v>
@@ -10495,7 +10507,7 @@
         <v>1</v>
       </c>
       <c r="C657" s="28" t="s">
-        <v>22</v>
+        <v>326</v>
       </c>
       <c r="D657" s="28" t="s">
         <v>21</v>
@@ -10721,7 +10733,7 @@
         <v>9</v>
       </c>
       <c r="C673" s="28" t="s">
-        <v>22</v>
+        <v>326</v>
       </c>
       <c r="D673" s="28" t="s">
         <v>66</v>
@@ -10833,7 +10845,7 @@
         <v>13</v>
       </c>
       <c r="C681" s="28" t="s">
-        <v>43</v>
+        <v>327</v>
       </c>
       <c r="D681" s="28" t="s">
         <v>38</v>
@@ -16823,7 +16835,7 @@
     </row>
     <row r="1131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1131" s="46" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B1131" s="46">
         <v>6</v>
@@ -16853,7 +16865,7 @@
     </row>
     <row r="1133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1133" s="51" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B1133" s="46">
         <v>7</v>
@@ -16862,7 +16874,7 @@
         <v>309</v>
       </c>
       <c r="D1133" s="49" t="s">
-        <v>9</v>
+        <v>322</v>
       </c>
       <c r="E1133" s="49"/>
       <c r="F1133" s="49"/>
@@ -16881,13 +16893,13 @@
     </row>
     <row r="1135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1135" s="46" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B1135" s="46">
         <v>8</v>
       </c>
       <c r="C1135" s="49" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="D1135" s="49" t="s">
         <v>41</v>
@@ -16909,13 +16921,13 @@
     </row>
     <row r="1137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1137" s="46" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B1137" s="46">
         <v>10</v>
       </c>
       <c r="C1137" s="49" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D1137" s="49" t="s">
         <v>33</v>
@@ -16937,13 +16949,13 @@
     </row>
     <row r="1139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1139" s="46" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B1139" s="46">
         <v>11</v>
       </c>
       <c r="C1139" s="49" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D1139" s="49" t="s">
         <v>17</v>
@@ -16953,7 +16965,7 @@
     </row>
     <row r="1140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1140" s="51" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B1140" s="46"/>
       <c r="C1140" s="49">
@@ -16967,13 +16979,13 @@
     </row>
     <row r="1141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1141" s="46" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B1141" s="46">
         <v>12</v>
       </c>
       <c r="C1141" s="49" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D1141" s="49" t="s">
         <v>43</v>
@@ -16995,13 +17007,13 @@
     </row>
     <row r="1143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1143" s="46" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B1143" s="46">
         <v>13</v>
       </c>
       <c r="C1143" s="49" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D1143" s="49" t="s">
         <v>27</v>
@@ -17023,13 +17035,13 @@
     </row>
     <row r="1145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1145" s="46" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B1145" s="46">
         <v>14</v>
       </c>
       <c r="C1145" s="49" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="D1145" s="49" t="s">
         <v>83</v>

--- a/FullSeason5.xlsx
+++ b/FullSeason5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ianjpeck/Documents/GitHub/sbparser/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA659EB-E770-D449-A597-B41991FA4E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E30657E-F07A-F84F-B900-3B8B4C3907C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{C96D0F46-2D53-AF4F-A06C-8FE540EC6340}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16500" xr2:uid="{C96D0F46-2D53-AF4F-A06C-8FE540EC6340}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="323">
   <si>
     <t>Month 1</t>
   </si>
@@ -250,9 +250,6 @@
     <t>Zelda - W</t>
   </si>
   <si>
-    <t>Ganandorf</t>
-  </si>
-  <si>
     <t>Link</t>
   </si>
   <si>
@@ -361,18 +358,12 @@
     <t>Spot in Pokeball match</t>
   </si>
   <si>
-    <t>Toon Link- W</t>
-  </si>
-  <si>
     <t>Halberd</t>
   </si>
   <si>
     <t>King Dedede - W</t>
   </si>
   <si>
-    <t>Good comeback to stay undefeated (Down 3-1)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pokeslam </t>
   </si>
   <si>
@@ -595,9 +586,6 @@
     <t>Corneria</t>
   </si>
   <si>
-    <t>MoTY candidate: ROB down 2-1(109%), gets 2 finishers then a bazooka for the win)</t>
-  </si>
-  <si>
     <t>All fighters died at same time (bomb), Mario wins because he had 2 lives</t>
   </si>
   <si>
@@ -698,9 +686,6 @@
   </si>
   <si>
     <t>Mario has 5 Kos</t>
-  </si>
-  <si>
-    <t>Marth- W</t>
   </si>
   <si>
     <t>#6 &amp; #5</t>
@@ -877,12 +862,6 @@
   </si>
   <si>
     <t>Month 10</t>
-  </si>
-  <si>
-    <t>Guest appearance by  DK</t>
-  </si>
-  <si>
-    <t>Lucaro - W</t>
   </si>
   <si>
     <t>Guest Appearance</t>
@@ -1071,12 +1050,6 @@
     <t>Guest appearance by Falco</t>
   </si>
   <si>
-    <t>Meta Kinght - W</t>
-  </si>
-  <si>
-    <t>Great match, good comeback by Luigi down 2-1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Championship Cruise </t>
   </si>
   <si>
@@ -1116,9 +1089,6 @@
     <t>Samus killed Kirby at buzzer but didn’t count</t>
   </si>
   <si>
-    <t>300% Match // comeback from 3-1</t>
-  </si>
-  <si>
     <t>Sonic (PL)</t>
   </si>
   <si>
@@ -1180,6 +1150,21 @@
   </si>
   <si>
     <t>Luigi (Defending)</t>
+  </si>
+  <si>
+    <t>Good comeback to stay undefeated (Down 3 -1)</t>
+  </si>
+  <si>
+    <t>MoTY candidate: ROB down 2 -1(109%), gets 2 finishers then a bazooka for the win)</t>
+  </si>
+  <si>
+    <t>Great match, good comeback by Luigi down 2 -1</t>
+  </si>
+  <si>
+    <t>300% Match // comeback from 3 -1</t>
+  </si>
+  <si>
+    <t>Guest appearance by DK</t>
   </si>
 </sst>
 </file>
@@ -2815,10 +2800,10 @@
         <v>64</v>
       </c>
       <c r="E79" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F79" s="15" t="s">
         <v>65</v>
-      </c>
-      <c r="F79" s="15" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
@@ -2839,7 +2824,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B81" s="12">
         <v>3</v>
@@ -2848,7 +2833,7 @@
         <v>33</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="12"/>
@@ -2867,13 +2852,13 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B83" s="12">
         <v>4</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D83" s="15" t="s">
         <v>17</v>
@@ -2883,7 +2868,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B84" s="12"/>
       <c r="C84" s="15">
@@ -2897,16 +2882,16 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B85" s="12">
         <v>5</v>
       </c>
       <c r="C85" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D85" s="15" t="s">
         <v>73</v>
-      </c>
-      <c r="D85" s="15" t="s">
-        <v>74</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="12"/>
@@ -2925,16 +2910,16 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B87" s="12">
         <v>6</v>
       </c>
       <c r="C87" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D87" s="15" t="s">
         <v>76</v>
-      </c>
-      <c r="D87" s="15" t="s">
-        <v>77</v>
       </c>
       <c r="E87" s="12"/>
       <c r="F87" s="12"/>
@@ -2953,7 +2938,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B89" s="12">
         <v>7</v>
@@ -2962,14 +2947,14 @@
         <v>33</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="12"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B90" s="12"/>
       <c r="C90" s="15">
@@ -2983,16 +2968,16 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B91" s="12">
         <v>8</v>
       </c>
       <c r="C91" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D91" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="D91" s="15" t="s">
-        <v>83</v>
       </c>
       <c r="E91" s="15" t="s">
         <v>39</v>
@@ -3019,7 +3004,7 @@
     </row>
     <row r="93" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="2"/>
@@ -3039,7 +3024,7 @@
         <v>1</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
@@ -3077,7 +3062,7 @@
         <v>2</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>30</v>
@@ -3125,7 +3110,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B102" s="3">
         <v>4</v>
@@ -3134,7 +3119,7 @@
         <v>7</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -3153,13 +3138,13 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B104" s="3">
         <v>5</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>3</v>
@@ -3195,7 +3180,7 @@
         <v>14</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D107" s="10"/>
       <c r="E107" s="10"/>
@@ -3281,7 +3266,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B114" s="7">
         <v>4</v>
@@ -3290,7 +3275,7 @@
         <v>48</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E114" s="10"/>
       <c r="F114" s="10"/>
@@ -3309,7 +3294,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B116" s="7">
         <v>5</v>
@@ -3347,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
@@ -3387,7 +3372,7 @@
         <v>2</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>34</v>
@@ -3421,10 +3406,10 @@
         <v>13</v>
       </c>
       <c r="E124" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F124" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
@@ -3449,10 +3434,10 @@
         <v>4</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -3477,7 +3462,7 @@
         <v>5</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>7</v>
@@ -3509,7 +3494,7 @@
         <v>14</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D131" s="10"/>
       <c r="E131" s="10"/>
@@ -3573,7 +3558,7 @@
         <v>3</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D136" s="10" t="s">
         <v>48</v>
@@ -3611,7 +3596,7 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B139" s="7"/>
       <c r="C139" s="10">
@@ -3625,7 +3610,7 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B140" s="7">
         <v>5</v>
@@ -3634,7 +3619,7 @@
         <v>21</v>
       </c>
       <c r="D140" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E140" s="10"/>
       <c r="F140" s="10"/>
@@ -3663,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
@@ -3671,7 +3656,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B144" s="3">
         <v>1</v>
@@ -3705,10 +3690,10 @@
         <v>2</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
@@ -3727,7 +3712,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B148" s="3">
         <v>3</v>
@@ -3755,16 +3740,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B150" s="3">
         <v>4</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
@@ -3783,13 +3768,13 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B152" s="3">
         <v>5</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>12</v>
@@ -3821,7 +3806,7 @@
         <v>14</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D155" s="10"/>
       <c r="E155" s="10"/>
@@ -3833,7 +3818,7 @@
         <v>1</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D156" s="10" t="s">
         <v>58</v>
@@ -3859,10 +3844,10 @@
         <v>2</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E158" s="10"/>
       <c r="F158" s="10"/>
@@ -3907,7 +3892,7 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" s="7" t="s">
-        <v>105</v>
+        <v>318</v>
       </c>
       <c r="B162" s="7">
         <v>4</v>
@@ -3944,7 +3929,7 @@
         <v>24</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E164" s="10"/>
       <c r="F164" s="10"/>
@@ -3970,10 +3955,10 @@
     <row r="167" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A167" s="12"/>
       <c r="B167" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D167" s="15"/>
       <c r="E167" s="15"/>
@@ -3981,23 +3966,23 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B168" s="12">
         <v>1</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E168" s="15"/>
       <c r="F168" s="15"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B169" s="12"/>
       <c r="C169" s="15">
@@ -4053,7 +4038,7 @@
         <v>3</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D172" s="15" t="s">
         <v>27</v>
@@ -4075,7 +4060,7 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B174" s="12">
         <v>4</v>
@@ -4103,13 +4088,13 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B176" s="12">
         <v>5</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>40</v>
@@ -4119,21 +4104,21 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" s="12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B177" s="12"/>
       <c r="C177" s="15">
         <v>0</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E177" s="15"/>
       <c r="F177" s="15"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" s="12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B178" s="12">
         <v>6</v>
@@ -4142,10 +4127,10 @@
         <v>23</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E178" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F178" s="15" t="s">
         <v>12</v>
@@ -4153,7 +4138,7 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B179" s="12"/>
       <c r="C179" s="15">
@@ -4171,7 +4156,7 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B180" s="12">
         <v>7</v>
@@ -4180,14 +4165,14 @@
         <v>33</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E180" s="15"/>
       <c r="F180" s="15"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" s="19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B181" s="12"/>
       <c r="C181" s="15">
@@ -4201,7 +4186,7 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B182" s="12">
         <v>8</v>
@@ -4229,23 +4214,23 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B184" s="12">
         <v>9</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D184" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E184" s="15"/>
       <c r="F184" s="15"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B185" s="12"/>
       <c r="C185" s="15">
@@ -4259,7 +4244,7 @@
     </row>
     <row r="186" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B186" s="1"/>
       <c r="C186" s="2"/>
@@ -4279,7 +4264,7 @@
         <v>1</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D188" s="6"/>
       <c r="E188" s="6"/>
@@ -4287,13 +4272,13 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B189" s="3">
         <v>1</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>8</v>
@@ -4319,7 +4304,7 @@
         <v>2</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D191" s="6" t="s">
         <v>64</v>
@@ -4345,7 +4330,7 @@
         <v>3</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D193" s="6" t="s">
         <v>30</v>
@@ -4399,13 +4384,13 @@
         <v>5</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D197" s="6" t="s">
         <v>51</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F197" s="6"/>
     </row>
@@ -4435,7 +4420,7 @@
         <v>14</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D200" s="10"/>
       <c r="E200" s="10"/>
@@ -4473,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="C203" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D203" s="10" t="s">
         <v>18</v>
@@ -4495,7 +4480,7 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B205" s="7">
         <v>3</v>
@@ -4531,7 +4516,7 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B207" s="7">
         <v>4</v>
@@ -4559,7 +4544,7 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B209" s="7">
         <v>5</v>
@@ -4597,7 +4582,7 @@
         <v>1</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
@@ -4605,7 +4590,7 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B213" s="3">
         <v>1</v>
@@ -4614,7 +4599,7 @@
         <v>54</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E213" s="6"/>
       <c r="F213" s="6"/>
@@ -4659,7 +4644,7 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B217" s="3">
         <v>3</v>
@@ -4691,7 +4676,7 @@
         <v>4</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D219" s="6" t="s">
         <v>8</v>
@@ -4719,7 +4704,7 @@
         <v>5</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D221" s="6" t="s">
         <v>9</v>
@@ -4751,7 +4736,7 @@
         <v>14</v>
       </c>
       <c r="C224" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D224" s="10"/>
       <c r="E224" s="10"/>
@@ -4759,7 +4744,7 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B225" s="7">
         <v>1</v>
@@ -4768,7 +4753,7 @@
         <v>21</v>
       </c>
       <c r="D225" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E225" s="10"/>
       <c r="F225" s="10"/>
@@ -4865,13 +4850,13 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B233" s="7">
         <v>5</v>
       </c>
       <c r="C233" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D233" s="10" t="s">
         <v>56</v>
@@ -4903,7 +4888,7 @@
         <v>1</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
@@ -4911,19 +4896,19 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B237" s="3">
         <v>1</v>
       </c>
       <c r="C237" s="20" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E237" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F237" s="6"/>
     </row>
@@ -4973,7 +4958,7 @@
         <v>3</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D241" s="6" t="s">
         <v>30</v>
@@ -5021,7 +5006,7 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B245" s="3">
         <v>5</v>
@@ -5030,7 +5015,7 @@
         <v>12</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E245" s="6"/>
       <c r="F245" s="6"/>
@@ -5059,7 +5044,7 @@
         <v>14</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D248" s="10"/>
       <c r="E248" s="10"/>
@@ -5071,7 +5056,7 @@
         <v>1</v>
       </c>
       <c r="C249" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D249" s="10" t="s">
         <v>21</v>
@@ -5100,7 +5085,7 @@
         <v>48</v>
       </c>
       <c r="D251" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E251" s="10"/>
       <c r="F251" s="10"/>
@@ -5149,7 +5134,7 @@
         <v>4</v>
       </c>
       <c r="C255" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D255" s="10" t="s">
         <v>41</v>
@@ -5171,7 +5156,7 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B257" s="7">
         <v>5</v>
@@ -5206,10 +5191,10 @@
     <row r="260" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A260" s="12"/>
       <c r="B260" s="13" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D260" s="15"/>
       <c r="E260" s="15"/>
@@ -5217,13 +5202,13 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A261" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B261" s="12">
         <v>1</v>
       </c>
       <c r="C261" s="15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D261" s="15" t="s">
         <v>32</v>
@@ -5233,7 +5218,7 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262" s="12" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B262" s="12"/>
       <c r="C262" s="15">
@@ -5256,7 +5241,7 @@
         <v>27</v>
       </c>
       <c r="D263" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E263" s="15"/>
       <c r="F263" s="15"/>
@@ -5281,10 +5266,10 @@
         <v>3</v>
       </c>
       <c r="C265" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D265" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E265" s="15" t="s">
         <v>38</v>
@@ -5311,7 +5296,7 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A267" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B267" s="12">
         <v>4</v>
@@ -5339,7 +5324,7 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A269" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B269" s="12">
         <v>5</v>
@@ -5367,7 +5352,7 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A271" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B271" s="12">
         <v>6</v>
@@ -5376,14 +5361,14 @@
         <v>33</v>
       </c>
       <c r="D271" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E271" s="15"/>
       <c r="F271" s="15"/>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272" s="12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B272" s="12"/>
       <c r="C272" s="15">
@@ -5397,7 +5382,7 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B273" s="12">
         <v>7</v>
@@ -5425,19 +5410,19 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B275" s="12">
         <v>8</v>
       </c>
       <c r="C275" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D275" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E275" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F275" s="15" t="s">
         <v>24</v>
@@ -5477,7 +5462,7 @@
     </row>
     <row r="279" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="2"/>
@@ -5497,7 +5482,7 @@
         <v>1</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D281" s="6"/>
       <c r="E281" s="6"/>
@@ -5505,7 +5490,7 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B282" s="3">
         <v>1</v>
@@ -5514,7 +5499,7 @@
         <v>18</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E282" s="6"/>
       <c r="F282" s="6"/>
@@ -5545,10 +5530,10 @@
         <v>31</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F284" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.2">
@@ -5576,7 +5561,7 @@
         <v>51</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E286" s="6"/>
       <c r="F286" s="6"/>
@@ -5602,7 +5587,7 @@
         <v>34</v>
       </c>
       <c r="D288" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E288" s="6"/>
       <c r="F288" s="6"/>
@@ -5630,7 +5615,7 @@
         <v>9</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E290" s="6"/>
       <c r="F290" s="6"/>
@@ -5659,7 +5644,7 @@
         <v>14</v>
       </c>
       <c r="C293" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D293" s="10"/>
       <c r="E293" s="10"/>
@@ -5667,7 +5652,7 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B294" s="7">
         <v>1</v>
@@ -5699,7 +5684,7 @@
         <v>2</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D296" s="10" t="s">
         <v>43</v>
@@ -5747,7 +5732,7 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B300" s="7">
         <v>4</v>
@@ -5775,13 +5760,13 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A302" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B302" s="7">
         <v>5</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D302" s="10" t="s">
         <v>37</v>
@@ -5813,7 +5798,7 @@
         <v>1</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D305" s="6"/>
       <c r="E305" s="6"/>
@@ -5821,7 +5806,7 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B306" s="3">
         <v>1</v>
@@ -5855,10 +5840,10 @@
         <v>2</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D308" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E308" s="6"/>
       <c r="F308" s="6"/>
@@ -5877,7 +5862,7 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B310" s="3">
         <v>3</v>
@@ -5886,7 +5871,7 @@
         <v>52</v>
       </c>
       <c r="D310" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E310" s="6"/>
       <c r="F310" s="6"/>
@@ -5905,16 +5890,16 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A312" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B312" s="3">
         <v>4</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D312" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E312" s="6"/>
       <c r="F312" s="6"/>
@@ -5933,16 +5918,16 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B314" s="3">
         <v>5</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D314" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E314" s="6"/>
       <c r="F314" s="6"/>
@@ -5971,7 +5956,7 @@
         <v>14</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D317" s="10"/>
       <c r="E317" s="10"/>
@@ -5983,7 +5968,7 @@
         <v>1</v>
       </c>
       <c r="C318" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D318" s="10" t="s">
         <v>20</v>
@@ -6085,13 +6070,13 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B326" s="7">
         <v>5</v>
       </c>
       <c r="C326" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D326" s="10" t="s">
         <v>27</v>
@@ -6123,7 +6108,7 @@
         <v>1</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D329" s="6"/>
       <c r="E329" s="6"/>
@@ -6137,7 +6122,7 @@
         <v>1</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D330" s="6" t="s">
         <v>8</v>
@@ -6198,7 +6183,7 @@
         <v>54</v>
       </c>
       <c r="F334" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.2">
@@ -6245,7 +6230,7 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B338" s="3">
         <v>5</v>
@@ -6254,7 +6239,7 @@
         <v>5</v>
       </c>
       <c r="D338" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E338" s="6"/>
       <c r="F338" s="6"/>
@@ -6283,7 +6268,7 @@
         <v>14</v>
       </c>
       <c r="C341" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D341" s="10"/>
       <c r="E341" s="10"/>
@@ -6295,10 +6280,10 @@
         <v>1</v>
       </c>
       <c r="C342" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D342" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E342" s="10"/>
       <c r="F342" s="10"/>
@@ -6352,7 +6337,7 @@
         <v>20</v>
       </c>
       <c r="D346" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E346" s="10"/>
       <c r="F346" s="10"/>
@@ -6371,7 +6356,7 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A348" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B348" s="7">
         <v>4</v>
@@ -6380,7 +6365,7 @@
         <v>38</v>
       </c>
       <c r="D348" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E348" s="10"/>
       <c r="F348" s="10"/>
@@ -6399,7 +6384,7 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A350" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B350" s="7">
         <v>5</v>
@@ -6434,10 +6419,10 @@
     <row r="353" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A353" s="12"/>
       <c r="B353" s="13" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C353" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D353" s="15"/>
       <c r="E353" s="15"/>
@@ -6445,7 +6430,7 @@
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A354" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B354" s="12">
         <v>1</v>
@@ -6473,13 +6458,13 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A356" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B356" s="12">
         <v>2</v>
       </c>
       <c r="C356" s="15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D356" s="15" t="s">
         <v>30</v>
@@ -6513,7 +6498,7 @@
         <v>38</v>
       </c>
       <c r="E358" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F358" s="15" t="s">
         <v>54</v>
@@ -6546,14 +6531,14 @@
         <v>27</v>
       </c>
       <c r="D360" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E360" s="15"/>
       <c r="F360" s="15"/>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A361" s="12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B361" s="12"/>
       <c r="C361" s="15">
@@ -6567,7 +6552,7 @@
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A362" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B362" s="12">
         <v>5</v>
@@ -6595,7 +6580,7 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" s="12" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B364" s="12">
         <v>6</v>
@@ -6604,7 +6589,7 @@
         <v>62</v>
       </c>
       <c r="D364" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E364" s="15" t="s">
         <v>39</v>
@@ -6615,7 +6600,7 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A365" s="12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B365" s="12"/>
       <c r="C365" s="15">
@@ -6633,7 +6618,7 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A366" s="12" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B366" s="12">
         <v>7</v>
@@ -6642,10 +6627,10 @@
         <v>13</v>
       </c>
       <c r="D366" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E366" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F366" s="15" t="s">
         <v>3</v>
@@ -6653,7 +6638,7 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A367" s="19" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B367" s="12"/>
       <c r="C367" s="15">
@@ -6671,7 +6656,7 @@
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A368" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B368" s="12">
         <v>8</v>
@@ -6680,7 +6665,7 @@
         <v>22</v>
       </c>
       <c r="D368" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E368" s="15"/>
       <c r="F368" s="15"/>
@@ -6699,13 +6684,13 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A370" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B370" s="12">
         <v>9</v>
       </c>
       <c r="C370" s="15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D370" s="15" t="s">
         <v>9</v>
@@ -6715,7 +6700,7 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A371" s="12" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B371" s="12"/>
       <c r="C371" s="15">
@@ -6729,7 +6714,7 @@
     </row>
     <row r="372" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B372" s="1"/>
       <c r="C372" s="2"/>
@@ -6749,7 +6734,7 @@
         <v>1</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D374" s="6"/>
       <c r="E374" s="6"/>
@@ -6761,10 +6746,10 @@
         <v>1</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D375" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E375" s="6"/>
       <c r="F375" s="6"/>
@@ -6787,10 +6772,10 @@
         <v>2</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D377" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E377" s="6"/>
       <c r="F377" s="6"/>
@@ -6835,13 +6820,13 @@
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A381" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B381" s="3">
         <v>4</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D381" s="6" t="s">
         <v>12</v>
@@ -6851,7 +6836,7 @@
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A382" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B382" s="3"/>
       <c r="C382" s="6">
@@ -6865,23 +6850,23 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A383" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B383" s="3">
         <v>5</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D383" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E383" s="6"/>
       <c r="F383" s="6"/>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A384" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B384" s="3"/>
       <c r="C384" s="6">
@@ -6905,7 +6890,7 @@
         <v>14</v>
       </c>
       <c r="C386" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D386" s="10"/>
       <c r="E386" s="10"/>
@@ -6917,7 +6902,7 @@
         <v>1</v>
       </c>
       <c r="C387" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D387" s="10" t="s">
         <v>21</v>
@@ -6939,16 +6924,16 @@
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A389" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B389" s="7">
         <v>2</v>
       </c>
       <c r="C389" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D389" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E389" s="10"/>
       <c r="F389" s="10"/>
@@ -6971,10 +6956,10 @@
         <v>3</v>
       </c>
       <c r="C391" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D391" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E391" s="10"/>
       <c r="F391" s="10"/>
@@ -6993,7 +6978,7 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A393" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B393" s="7">
         <v>4</v>
@@ -7035,10 +7020,10 @@
         <v>5</v>
       </c>
       <c r="C395" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D395" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E395" s="10" t="s">
         <v>23</v>
@@ -7049,7 +7034,7 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A396" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B396" s="7"/>
       <c r="C396" s="10">
@@ -7077,7 +7062,7 @@
         <v>1</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D398" s="6"/>
       <c r="E398" s="6"/>
@@ -7118,7 +7103,7 @@
         <v>34</v>
       </c>
       <c r="D401" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E401" s="6"/>
       <c r="F401" s="6"/>
@@ -7170,7 +7155,7 @@
         <v>51</v>
       </c>
       <c r="D405" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E405" s="6"/>
       <c r="F405" s="6"/>
@@ -7231,7 +7216,7 @@
         <v>14</v>
       </c>
       <c r="C410" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D410" s="10"/>
       <c r="E410" s="10"/>
@@ -7269,7 +7254,7 @@
         <v>2</v>
       </c>
       <c r="C413" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D413" s="10" t="s">
         <v>46</v>
@@ -7295,7 +7280,7 @@
         <v>3</v>
       </c>
       <c r="C415" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D415" s="10" t="s">
         <v>20</v>
@@ -7343,7 +7328,7 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A419" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B419" s="7">
         <v>5</v>
@@ -7381,7 +7366,7 @@
         <v>1</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D422" s="6"/>
       <c r="E422" s="6"/>
@@ -7396,7 +7381,7 @@
         <v>34</v>
       </c>
       <c r="D423" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E423" s="6"/>
       <c r="F423" s="6"/>
@@ -7419,7 +7404,7 @@
         <v>2</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D425" s="6" t="s">
         <v>7</v>
@@ -7445,10 +7430,10 @@
         <v>3</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D427" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E427" s="6"/>
       <c r="F427" s="6"/>
@@ -7471,7 +7456,7 @@
         <v>4</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D429" s="6" t="s">
         <v>12</v>
@@ -7529,7 +7514,7 @@
         <v>14</v>
       </c>
       <c r="C434" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D434" s="10"/>
       <c r="E434" s="10"/>
@@ -7615,23 +7600,23 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A441" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B441" s="7">
         <v>4</v>
       </c>
       <c r="C441" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D441" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E441" s="10"/>
       <c r="F441" s="10"/>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A442" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B442" s="7"/>
       <c r="C442" s="10">
@@ -7645,13 +7630,13 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A443" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B443" s="7">
         <v>5</v>
       </c>
       <c r="C443" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D443" s="10" t="s">
         <v>62</v>
@@ -7661,7 +7646,7 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A444" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B444" s="7"/>
       <c r="C444" s="10">
@@ -7682,10 +7667,10 @@
     <row r="446" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A446" s="12"/>
       <c r="B446" s="13" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C446" s="14" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D446" s="15"/>
       <c r="E446" s="15"/>
@@ -7705,7 +7690,7 @@
         <v>38</v>
       </c>
       <c r="E447" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F447" s="15" t="s">
         <v>37</v>
@@ -7729,7 +7714,7 @@
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A449" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B449" s="12">
         <v>2</v>
@@ -7738,10 +7723,10 @@
         <v>5</v>
       </c>
       <c r="D449" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E449" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F449" s="15"/>
     </row>
@@ -7761,7 +7746,7 @@
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A451" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B451" s="12">
         <v>3</v>
@@ -7777,7 +7762,7 @@
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A452" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B452" s="12"/>
       <c r="C452" s="15">
@@ -7791,13 +7776,13 @@
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A453" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B453" s="12">
         <v>4</v>
       </c>
       <c r="C453" s="15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D453" s="15" t="s">
         <v>54</v>
@@ -7807,7 +7792,7 @@
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A454" s="12" t="s">
-        <v>180</v>
+        <v>319</v>
       </c>
       <c r="B454" s="12"/>
       <c r="C454" s="15">
@@ -7833,13 +7818,13 @@
         <v>62</v>
       </c>
       <c r="E455" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F455" s="15"/>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A456" s="12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B456" s="12"/>
       <c r="C456" s="15">
@@ -7855,7 +7840,7 @@
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A457" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B457" s="12">
         <v>6</v>
@@ -7864,7 +7849,7 @@
         <v>9</v>
       </c>
       <c r="D457" s="15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E457" s="15"/>
       <c r="F457" s="15"/>
@@ -7883,7 +7868,7 @@
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A459" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B459" s="12">
         <v>7</v>
@@ -7899,7 +7884,7 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A460" s="19" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B460" s="12"/>
       <c r="C460" s="15">
@@ -7913,7 +7898,7 @@
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A461" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B461" s="12">
         <v>8</v>
@@ -7929,7 +7914,7 @@
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A462" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B462" s="12"/>
       <c r="C462" s="15">
@@ -7943,7 +7928,7 @@
     </row>
     <row r="463" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B463" s="1"/>
       <c r="C463" s="2"/>
@@ -7963,7 +7948,7 @@
         <v>1</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D465" s="6"/>
       <c r="E465" s="6"/>
@@ -7975,10 +7960,10 @@
         <v>1</v>
       </c>
       <c r="C466" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D466" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E466" s="6"/>
       <c r="F466" s="6"/>
@@ -8084,14 +8069,14 @@
         <v>41</v>
       </c>
       <c r="D474" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E474" s="6"/>
       <c r="F474" s="6"/>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A475" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B475" s="3"/>
       <c r="C475" s="6">
@@ -8115,7 +8100,7 @@
         <v>14</v>
       </c>
       <c r="C477" s="9" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D477" s="10"/>
       <c r="E477" s="10"/>
@@ -8127,7 +8112,7 @@
         <v>1</v>
       </c>
       <c r="C478" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D478" s="10" t="s">
         <v>45</v>
@@ -8149,7 +8134,7 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A480" s="7" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B480" s="7">
         <v>2</v>
@@ -8158,7 +8143,7 @@
         <v>24</v>
       </c>
       <c r="D480" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E480" s="10"/>
       <c r="F480" s="10"/>
@@ -8203,13 +8188,13 @@
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A484" s="7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B484" s="7">
         <v>4</v>
       </c>
       <c r="C484" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D484" s="10" t="s">
         <v>46</v>
@@ -8219,7 +8204,7 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A485" s="7" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B485" s="7"/>
       <c r="C485" s="10">
@@ -8233,7 +8218,7 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A486" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B486" s="7">
         <v>5</v>
@@ -8242,7 +8227,7 @@
         <v>58</v>
       </c>
       <c r="D486" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E486" s="10"/>
       <c r="F486" s="10"/>
@@ -8271,7 +8256,7 @@
         <v>1</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D489" s="6"/>
       <c r="E489" s="6"/>
@@ -8283,7 +8268,7 @@
         <v>1</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D490" s="6" t="s">
         <v>34</v>
@@ -8311,7 +8296,7 @@
         <v>2</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D492" s="6" t="s">
         <v>32</v>
@@ -8337,10 +8322,10 @@
         <v>3</v>
       </c>
       <c r="C494" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D494" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E494" s="6"/>
       <c r="F494" s="6"/>
@@ -8431,7 +8416,7 @@
         <v>14</v>
       </c>
       <c r="C501" s="9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D501" s="10"/>
       <c r="E501" s="10"/>
@@ -8439,7 +8424,7 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A502" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B502" s="7">
         <v>1</v>
@@ -8500,7 +8485,7 @@
         <v>40</v>
       </c>
       <c r="D506" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E506" s="10"/>
       <c r="F506" s="10"/>
@@ -8545,13 +8530,13 @@
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A510" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B510" s="7">
         <v>5</v>
       </c>
       <c r="C510" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D510" s="10" t="s">
         <v>46</v>
@@ -8583,7 +8568,7 @@
         <v>1</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D513" s="6"/>
       <c r="E513" s="6"/>
@@ -8617,7 +8602,7 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A516" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B516" s="3">
         <v>2</v>
@@ -8626,7 +8611,7 @@
         <v>32</v>
       </c>
       <c r="D516" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E516" s="6"/>
       <c r="F516" s="6"/>
@@ -8675,7 +8660,7 @@
         <v>4</v>
       </c>
       <c r="C520" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D520" s="6" t="s">
         <v>37</v>
@@ -8821,7 +8806,7 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A532" s="7" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B532" s="7">
         <v>4</v>
@@ -8837,7 +8822,7 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A533" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B533" s="7"/>
       <c r="C533" s="10">
@@ -8884,7 +8869,7 @@
     <row r="537" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A537" s="12"/>
       <c r="B537" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C537" s="14" t="s">
         <v>28</v>
@@ -8901,10 +8886,10 @@
         <v>1</v>
       </c>
       <c r="C538" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D538" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E538" s="15"/>
       <c r="F538" s="15"/>
@@ -8923,13 +8908,13 @@
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A540" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B540" s="12">
         <v>2</v>
       </c>
       <c r="C540" s="15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D540" s="15" t="s">
         <v>48</v>
@@ -8951,7 +8936,7 @@
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A542" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B542" s="12">
         <v>3</v>
@@ -8960,14 +8945,14 @@
         <v>40</v>
       </c>
       <c r="D542" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E542" s="15"/>
       <c r="F542" s="15"/>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A543" s="12" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B543" s="12"/>
       <c r="C543" s="15">
@@ -8981,16 +8966,16 @@
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A544" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B544" s="12">
         <v>4</v>
       </c>
       <c r="C544" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D544" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E544" s="15"/>
       <c r="F544" s="15"/>
@@ -9024,12 +9009,12 @@
         <v>54</v>
       </c>
       <c r="F546" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A547" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B547" s="12"/>
       <c r="C547" s="15">
@@ -9047,7 +9032,7 @@
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A548" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B548" s="12">
         <v>6</v>
@@ -9056,7 +9041,7 @@
         <v>9</v>
       </c>
       <c r="D548" s="15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E548" s="15"/>
       <c r="F548" s="15"/>
@@ -9075,7 +9060,7 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A550" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B550" s="12">
         <v>7</v>
@@ -9091,7 +9076,7 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A551" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B551" s="12"/>
       <c r="C551" s="15">
@@ -9105,7 +9090,7 @@
     </row>
     <row r="552" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B552" s="1"/>
       <c r="C552" s="2"/>
@@ -9133,13 +9118,13 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A555" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B555" s="3">
         <v>1</v>
       </c>
       <c r="C555" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D555" s="6" t="s">
         <v>48</v>
@@ -9161,7 +9146,7 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A557" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B557" s="3">
         <v>2</v>
@@ -9196,7 +9181,7 @@
         <v>34</v>
       </c>
       <c r="D559" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E559" s="6"/>
       <c r="F559" s="6"/>
@@ -9222,7 +9207,7 @@
         <v>19</v>
       </c>
       <c r="D561" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E561" s="6"/>
       <c r="F561" s="6"/>
@@ -9285,7 +9270,7 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A567" s="7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B567" s="7">
         <v>1</v>
@@ -9294,7 +9279,7 @@
         <v>20</v>
       </c>
       <c r="D567" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E567" s="10"/>
       <c r="F567" s="10"/>
@@ -9313,7 +9298,7 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A569" s="7" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B569" s="7">
         <v>2</v>
@@ -9329,7 +9314,7 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A570" s="7" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B570" s="7"/>
       <c r="C570" s="10">
@@ -9343,16 +9328,16 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A571" s="7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B571" s="7">
         <v>3</v>
       </c>
       <c r="C571" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D571" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E571" s="10"/>
       <c r="F571" s="10"/>
@@ -9375,7 +9360,7 @@
         <v>4</v>
       </c>
       <c r="C573" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D573" s="10" t="s">
         <v>38</v>
@@ -9401,10 +9386,10 @@
         <v>5</v>
       </c>
       <c r="C575" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D575" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E575" s="10"/>
       <c r="F575" s="10"/>
@@ -9441,13 +9426,13 @@
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A579" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B579" s="3">
         <v>1</v>
       </c>
       <c r="C579" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D579" s="6" t="s">
         <v>30</v>
@@ -9469,7 +9454,7 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A581" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B581" s="3">
         <v>2</v>
@@ -9497,7 +9482,7 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A583" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B583" s="3">
         <v>3</v>
@@ -9506,7 +9491,7 @@
         <v>31</v>
       </c>
       <c r="D583" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E583" s="6"/>
       <c r="F583" s="6"/>
@@ -9525,7 +9510,7 @@
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A585" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B585" s="3">
         <v>4</v>
@@ -9534,7 +9519,7 @@
         <v>62</v>
       </c>
       <c r="D585" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E585" s="6"/>
       <c r="F585" s="6"/>
@@ -9553,13 +9538,13 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A587" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B587" s="3">
         <v>5</v>
       </c>
       <c r="C587" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D587" s="6" t="s">
         <v>3</v>
@@ -9629,16 +9614,16 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A593" s="7" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B593" s="7">
         <v>2</v>
       </c>
       <c r="C593" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D593" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E593" s="10"/>
       <c r="F593" s="10"/>
@@ -9657,13 +9642,13 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A595" s="7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B595" s="7">
         <v>3</v>
       </c>
       <c r="C595" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D595" s="10" t="s">
         <v>46</v>
@@ -9685,7 +9670,7 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A597" s="7" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B597" s="7">
         <v>4</v>
@@ -9713,7 +9698,7 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A599" s="7" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B599" s="7">
         <v>5</v>
@@ -9722,16 +9707,16 @@
         <v>26</v>
       </c>
       <c r="D599" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E599" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F599" s="10"/>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A600" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B600" s="7"/>
       <c r="C600" s="10">
@@ -9757,7 +9742,7 @@
         <v>1</v>
       </c>
       <c r="C602" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D602" s="6"/>
       <c r="E602" s="6"/>
@@ -9772,7 +9757,7 @@
         <v>9</v>
       </c>
       <c r="D603" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E603" s="6"/>
       <c r="F603" s="6"/>
@@ -9798,7 +9783,7 @@
         <v>54</v>
       </c>
       <c r="D605" s="6" t="s">
-        <v>215</v>
+        <v>85</v>
       </c>
       <c r="E605" s="6"/>
       <c r="F605" s="6"/>
@@ -9843,7 +9828,7 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A609" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B609" s="3">
         <v>4</v>
@@ -9852,7 +9837,7 @@
         <v>24</v>
       </c>
       <c r="D609" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E609" s="6"/>
       <c r="F609" s="6"/>
@@ -9871,7 +9856,7 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A611" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B611" s="3">
         <v>5</v>
@@ -9880,7 +9865,7 @@
         <v>3</v>
       </c>
       <c r="D611" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E611" s="6"/>
       <c r="F611" s="6"/>
@@ -9909,7 +9894,7 @@
         <v>14</v>
       </c>
       <c r="C614" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D614" s="10"/>
       <c r="E614" s="10"/>
@@ -9917,7 +9902,7 @@
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A615" s="7" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B615" s="7">
         <v>1</v>
@@ -9979,10 +9964,10 @@
         <v>3</v>
       </c>
       <c r="C619" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D619" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E619" s="10"/>
       <c r="F619" s="10"/>
@@ -10001,7 +9986,7 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A621" s="7" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B621" s="7">
         <v>4</v>
@@ -10029,7 +10014,7 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A623" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B623" s="7">
         <v>5</v>
@@ -10064,35 +10049,35 @@
     <row r="626" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A626" s="12"/>
       <c r="B626" s="13" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C626" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D626" s="15"/>
       <c r="E626" s="15" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F626" s="15" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A627" s="12" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B627" s="12">
         <v>1</v>
       </c>
       <c r="C627" s="15" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D627" s="15" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E627" s="15"/>
       <c r="F627" s="24" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.2">
@@ -10109,7 +10094,7 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A629" s="12" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B629" s="12">
         <v>2</v>
@@ -10137,13 +10122,13 @@
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A631" s="12" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B631" s="12">
         <v>3</v>
       </c>
       <c r="C631" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D631" s="15" t="s">
         <v>32</v>
@@ -10165,7 +10150,7 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A633" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B633" s="12">
         <v>4</v>
@@ -10193,7 +10178,7 @@
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A635" s="12" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B635" s="12">
         <v>5</v>
@@ -10221,7 +10206,7 @@
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A637" s="12" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B637" s="12">
         <v>6</v>
@@ -10249,16 +10234,16 @@
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A639" s="12" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B639" s="12">
         <v>7</v>
       </c>
       <c r="C639" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D639" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E639" s="15"/>
       <c r="F639" s="15"/>
@@ -10277,7 +10262,7 @@
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A641" s="12" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B641" s="12">
         <v>8</v>
@@ -10305,7 +10290,7 @@
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A643" s="12" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B643" s="12">
         <v>9</v>
@@ -10333,7 +10318,7 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A645" s="12" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B645" s="12">
         <v>10</v>
@@ -10361,13 +10346,13 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A647" s="12" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B647" s="12">
         <v>11</v>
       </c>
       <c r="C647" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D647" s="15" t="s">
         <v>41</v>
@@ -10389,16 +10374,16 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A649" s="12" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B649" s="12">
         <v>12</v>
       </c>
       <c r="C649" s="15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D649" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E649" s="12"/>
       <c r="F649" s="12"/>
@@ -10417,7 +10402,7 @@
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A651" s="12" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B651" s="12">
         <v>13</v>
@@ -10445,7 +10430,7 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A653" s="12" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B653" s="12">
         <v>14</v>
@@ -10473,7 +10458,7 @@
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A655" s="12" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B655" s="12">
         <v>15</v>
@@ -10482,7 +10467,7 @@
         <v>24</v>
       </c>
       <c r="D655" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E655" s="12"/>
       <c r="F655" s="12"/>
@@ -10501,20 +10486,20 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A657" s="27" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B657" s="27">
         <v>1</v>
       </c>
       <c r="C657" s="28" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="D657" s="28" t="s">
         <v>21</v>
       </c>
       <c r="E657" s="27"/>
       <c r="F657" s="29" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.2">
@@ -10531,16 +10516,16 @@
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A659" s="27" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B659" s="27">
         <v>2</v>
       </c>
       <c r="C659" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D659" s="28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E659" s="27"/>
       <c r="F659" s="27"/>
@@ -10559,7 +10544,7 @@
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A661" s="27" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B661" s="27">
         <v>3</v>
@@ -10568,7 +10553,7 @@
         <v>17</v>
       </c>
       <c r="D661" s="28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E661" s="27"/>
       <c r="F661" s="27"/>
@@ -10587,7 +10572,7 @@
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A663" s="27" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B663" s="27">
         <v>4</v>
@@ -10596,7 +10581,7 @@
         <v>26</v>
       </c>
       <c r="D663" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E663" s="27"/>
       <c r="F663" s="27"/>
@@ -10615,7 +10600,7 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A665" s="27" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B665" s="27">
         <v>5</v>
@@ -10624,7 +10609,7 @@
         <v>38</v>
       </c>
       <c r="D665" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E665" s="27"/>
       <c r="F665" s="27"/>
@@ -10643,7 +10628,7 @@
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A667" s="27" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B667" s="27">
         <v>6</v>
@@ -10671,13 +10656,13 @@
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A669" s="27" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B669" s="27">
         <v>7</v>
       </c>
       <c r="C669" s="28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D669" s="28" t="s">
         <v>6</v>
@@ -10699,7 +10684,7 @@
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A671" s="27" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B671" s="27">
         <v>8</v>
@@ -10727,16 +10712,16 @@
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A673" s="27" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B673" s="27">
         <v>9</v>
       </c>
       <c r="C673" s="28" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="D673" s="28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E673" s="27"/>
       <c r="F673" s="27"/>
@@ -10755,7 +10740,7 @@
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A675" s="27" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B675" s="27">
         <v>10</v>
@@ -10783,13 +10768,13 @@
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A677" s="27" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B677" s="27">
         <v>11</v>
       </c>
       <c r="C677" s="28" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D677" s="28" t="s">
         <v>27</v>
@@ -10811,16 +10796,16 @@
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A679" s="31" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B679" s="31">
         <v>12</v>
       </c>
       <c r="C679" s="32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D679" s="32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E679" s="31"/>
       <c r="F679" s="31"/>
@@ -10839,13 +10824,13 @@
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A681" s="27" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B681" s="27">
         <v>13</v>
       </c>
       <c r="C681" s="28" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="D681" s="28" t="s">
         <v>38</v>
@@ -10867,13 +10852,13 @@
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A683" s="27" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B683" s="27">
         <v>14</v>
       </c>
       <c r="C683" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D683" s="28" t="s">
         <v>39</v>
@@ -10895,7 +10880,7 @@
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A685" s="27" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B685" s="27">
         <v>15</v>
@@ -10904,7 +10889,7 @@
         <v>58</v>
       </c>
       <c r="D685" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E685" s="27"/>
       <c r="F685" s="27"/>
@@ -10923,7 +10908,7 @@
     </row>
     <row r="687" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="2"/>
@@ -10943,7 +10928,7 @@
         <v>1</v>
       </c>
       <c r="C689" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D689" s="6"/>
       <c r="E689" s="6"/>
@@ -10951,7 +10936,7 @@
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A690" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B690" s="3">
         <v>1</v>
@@ -11009,7 +10994,7 @@
         <v>3</v>
       </c>
       <c r="C694" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D694" s="6" t="s">
         <v>34</v>
@@ -11035,7 +11020,7 @@
         <v>4</v>
       </c>
       <c r="C696" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D696" s="6" t="s">
         <v>52</v>
@@ -11057,7 +11042,7 @@
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A698" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B698" s="3">
         <v>5</v>
@@ -11066,7 +11051,7 @@
         <v>31</v>
       </c>
       <c r="D698" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E698" s="6"/>
       <c r="F698" s="6"/>
@@ -11095,7 +11080,7 @@
         <v>14</v>
       </c>
       <c r="C701" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D701" s="10"/>
       <c r="E701" s="10"/>
@@ -11103,7 +11088,7 @@
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A702" s="7" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B702" s="7">
         <v>1</v>
@@ -11112,7 +11097,7 @@
         <v>52</v>
       </c>
       <c r="D702" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E702" s="10"/>
       <c r="F702" s="10"/>
@@ -11157,7 +11142,7 @@
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A706" s="7" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B706" s="7">
         <v>3</v>
@@ -11166,7 +11151,7 @@
         <v>12</v>
       </c>
       <c r="D706" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E706" s="10"/>
       <c r="F706" s="10"/>
@@ -11185,13 +11170,13 @@
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A708" s="7" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B708" s="7">
         <v>4</v>
       </c>
       <c r="C708" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D708" s="10" t="s">
         <v>5</v>
@@ -11213,7 +11198,7 @@
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A710" s="7" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B710" s="7">
         <v>5</v>
@@ -11222,7 +11207,7 @@
         <v>22</v>
       </c>
       <c r="D710" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E710" s="10"/>
       <c r="F710" s="10"/>
@@ -11251,7 +11236,7 @@
         <v>1</v>
       </c>
       <c r="C713" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D713" s="6"/>
       <c r="E713" s="6"/>
@@ -11259,13 +11244,13 @@
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A714" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B714" s="3">
         <v>1</v>
       </c>
       <c r="C714" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D714" s="6" t="s">
         <v>30</v>
@@ -11313,7 +11298,7 @@
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A718" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B718" s="3">
         <v>3</v>
@@ -11329,7 +11314,7 @@
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A719" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B719" s="3"/>
       <c r="C719" s="6">
@@ -11343,13 +11328,13 @@
     </row>
     <row r="720" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A720" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B720" s="3">
         <v>4</v>
       </c>
       <c r="C720" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D720" s="6" t="s">
         <v>41</v>
@@ -11371,7 +11356,7 @@
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A722" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B722" s="3">
         <v>5</v>
@@ -11409,7 +11394,7 @@
         <v>14</v>
       </c>
       <c r="C725" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D725" s="10"/>
       <c r="E725" s="10"/>
@@ -11421,10 +11406,10 @@
         <v>1</v>
       </c>
       <c r="C726" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D726" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E726" s="10"/>
       <c r="F726" s="10"/>
@@ -11450,7 +11435,7 @@
         <v>40</v>
       </c>
       <c r="D728" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E728" s="10"/>
       <c r="F728" s="10"/>
@@ -11469,7 +11454,7 @@
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A730" s="7" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B730" s="7">
         <v>3</v>
@@ -11485,7 +11470,7 @@
     </row>
     <row r="731" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A731" s="7" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B731" s="7"/>
       <c r="C731" s="10">
@@ -11499,7 +11484,7 @@
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A732" s="7" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B732" s="7">
         <v>4</v>
@@ -11515,7 +11500,7 @@
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A733" s="7" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B733" s="7"/>
       <c r="C733" s="10">
@@ -11529,7 +11514,7 @@
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A734" s="7" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B734" s="7">
         <v>5</v>
@@ -11567,7 +11552,7 @@
         <v>1</v>
       </c>
       <c r="C737" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D737" s="6"/>
       <c r="E737" s="6"/>
@@ -11579,7 +11564,7 @@
         <v>1</v>
       </c>
       <c r="C738" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D738" s="6" t="s">
         <v>34</v>
@@ -11605,7 +11590,7 @@
         <v>2</v>
       </c>
       <c r="C740" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D740" s="6" t="s">
         <v>3</v>
@@ -11631,7 +11616,7 @@
         <v>3</v>
       </c>
       <c r="C742" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D742" s="6" t="s">
         <v>37</v>
@@ -11653,13 +11638,13 @@
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A744" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B744" s="3">
         <v>4</v>
       </c>
       <c r="C744" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D744" s="6" t="s">
         <v>30</v>
@@ -11681,7 +11666,7 @@
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A746" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B746" s="3">
         <v>5</v>
@@ -11690,7 +11675,7 @@
         <v>62</v>
       </c>
       <c r="D746" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E746" s="6"/>
       <c r="F746" s="6"/>
@@ -11719,7 +11704,7 @@
         <v>14</v>
       </c>
       <c r="C749" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D749" s="10"/>
       <c r="E749" s="10"/>
@@ -11763,16 +11748,16 @@
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A752" s="7" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B752" s="7">
         <v>2</v>
       </c>
       <c r="C752" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D752" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E752" s="10"/>
       <c r="F752" s="10"/>
@@ -11798,7 +11783,7 @@
         <v>46</v>
       </c>
       <c r="D754" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E754" s="10"/>
       <c r="F754" s="10"/>
@@ -11817,7 +11802,7 @@
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A756" s="7" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B756" s="7">
         <v>4</v>
@@ -11845,7 +11830,7 @@
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A758" s="7" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B758" s="7">
         <v>5</v>
@@ -11857,13 +11842,13 @@
         <v>45</v>
       </c>
       <c r="E758" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F758" s="10"/>
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A759" s="7" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B759" s="7"/>
       <c r="C759" s="10">
@@ -11886,10 +11871,10 @@
     <row r="761" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A761" s="12"/>
       <c r="B761" s="13" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C761" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D761" s="15"/>
       <c r="E761" s="15"/>
@@ -11909,7 +11894,7 @@
         <v>38</v>
       </c>
       <c r="E762" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F762" s="15" t="s">
         <v>37</v>
@@ -11933,13 +11918,13 @@
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A764" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B764" s="12">
         <v>2</v>
       </c>
       <c r="C764" s="15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D764" s="15" t="s">
         <v>48</v>
@@ -11965,7 +11950,7 @@
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A766" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B766" s="12">
         <v>3</v>
@@ -11977,13 +11962,13 @@
         <v>20</v>
       </c>
       <c r="E766" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F766" s="15"/>
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A767" s="12" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B767" s="12"/>
       <c r="C767" s="15">
@@ -11999,27 +11984,27 @@
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A768" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B768" s="12">
         <v>4</v>
       </c>
       <c r="C768" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D768" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E768" s="15" t="s">
         <v>13</v>
       </c>
       <c r="F768" s="15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A769" s="12" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B769" s="12"/>
       <c r="C769" s="15">
@@ -12043,10 +12028,10 @@
         <v>5</v>
       </c>
       <c r="C770" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D770" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E770" s="15" t="s">
         <v>23</v>
@@ -12069,13 +12054,13 @@
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A772" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B772" s="12">
         <v>6</v>
       </c>
       <c r="C772" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D772" s="15" t="s">
         <v>9</v>
@@ -12087,7 +12072,7 @@
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A773" s="12" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B773" s="12"/>
       <c r="C773" s="15">
@@ -12103,7 +12088,7 @@
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A774" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B774" s="12">
         <v>7</v>
@@ -12123,7 +12108,7 @@
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A775" s="19" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B775" s="12"/>
       <c r="C775" s="15">
@@ -12141,7 +12126,7 @@
     </row>
     <row r="776" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A776" s="33" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B776" s="33"/>
       <c r="C776" s="34"/>
@@ -12163,7 +12148,7 @@
         <v>1</v>
       </c>
       <c r="C778" s="38" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D778" s="39"/>
       <c r="E778" s="39"/>
@@ -12227,7 +12212,7 @@
         <v>3</v>
       </c>
       <c r="C783" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D783" s="39" t="s">
         <v>52</v>
@@ -12255,7 +12240,7 @@
         <v>4</v>
       </c>
       <c r="C785" s="39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D785" s="39" t="s">
         <v>62</v>
@@ -12312,10 +12297,10 @@
     <row r="790" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A790" s="40"/>
       <c r="B790" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C790" s="42" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D790" s="43"/>
       <c r="E790" s="43"/>
@@ -12327,7 +12312,7 @@
         <v>1</v>
       </c>
       <c r="C791" s="43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D791" s="43" t="s">
         <v>51</v>
@@ -12375,7 +12360,7 @@
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A795" s="40" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B795" s="40">
         <v>3</v>
@@ -12384,7 +12369,7 @@
         <v>46</v>
       </c>
       <c r="D795" s="43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E795" s="43"/>
       <c r="F795" s="43"/>
@@ -12403,7 +12388,7 @@
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A797" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B797" s="40">
         <v>4</v>
@@ -12469,7 +12454,7 @@
         <v>1</v>
       </c>
       <c r="C802" s="38" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D802" s="39"/>
       <c r="E802" s="39"/>
@@ -12484,7 +12469,7 @@
         <v>37</v>
       </c>
       <c r="D803" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E803" s="39"/>
       <c r="F803" s="39"/>
@@ -12507,7 +12492,7 @@
         <v>2</v>
       </c>
       <c r="C805" s="39" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D805" s="39" t="s">
         <v>62</v>
@@ -12533,10 +12518,10 @@
         <v>3</v>
       </c>
       <c r="C807" s="39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D807" s="44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E807" s="39"/>
       <c r="F807" s="39"/>
@@ -12564,7 +12549,7 @@
         <v>52</v>
       </c>
       <c r="D809" s="39" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E809" s="39"/>
       <c r="F809" s="39"/>
@@ -12620,10 +12605,10 @@
     <row r="814" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A814" s="40"/>
       <c r="B814" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C814" s="42" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D814" s="43"/>
       <c r="E814" s="43"/>
@@ -12638,7 +12623,7 @@
         <v>27</v>
       </c>
       <c r="D815" s="43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E815" s="43"/>
       <c r="F815" s="43"/>
@@ -12683,23 +12668,23 @@
     </row>
     <row r="819" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A819" s="40" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B819" s="40">
         <v>3</v>
       </c>
       <c r="C819" s="43" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D819" s="43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E819" s="43"/>
       <c r="F819" s="43"/>
     </row>
     <row r="820" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A820" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B820" s="40"/>
       <c r="C820" s="43">
@@ -12739,7 +12724,7 @@
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A823" s="40" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B823" s="40">
         <v>5</v>
@@ -12748,7 +12733,7 @@
         <v>43</v>
       </c>
       <c r="D823" s="43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E823" s="43"/>
       <c r="F823" s="43"/>
@@ -12779,7 +12764,7 @@
         <v>1</v>
       </c>
       <c r="C826" s="38" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D826" s="39"/>
       <c r="E826" s="39"/>
@@ -12793,13 +12778,13 @@
         <v>1</v>
       </c>
       <c r="C827" s="39" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D827" s="45" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E827" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F827" s="39" t="s">
         <v>34</v>
@@ -12827,7 +12812,7 @@
         <v>2</v>
       </c>
       <c r="C829" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D829" s="39" t="s">
         <v>30</v>
@@ -12882,7 +12867,7 @@
         <v>31</v>
       </c>
       <c r="D833" s="39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E833" s="39"/>
       <c r="F833" s="39"/>
@@ -12905,7 +12890,7 @@
         <v>5</v>
       </c>
       <c r="C835" s="39" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D835" s="39" t="s">
         <v>7</v>
@@ -12936,10 +12921,10 @@
     <row r="838" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A838" s="40"/>
       <c r="B838" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C838" s="42" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D838" s="43"/>
       <c r="E838" s="43"/>
@@ -12954,7 +12939,7 @@
         <v>51</v>
       </c>
       <c r="D839" s="43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E839" s="43"/>
       <c r="F839" s="43"/>
@@ -12973,7 +12958,7 @@
     </row>
     <row r="841" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A841" s="40" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B841" s="40">
         <v>2</v>
@@ -13057,7 +13042,7 @@
         <v>5</v>
       </c>
       <c r="C847" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D847" s="43" t="s">
         <v>38</v>
@@ -13088,10 +13073,10 @@
     <row r="850" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A850" s="46"/>
       <c r="B850" s="47" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C850" s="48" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D850" s="49"/>
       <c r="E850" s="49"/>
@@ -13127,13 +13112,13 @@
     </row>
     <row r="853" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A853" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="B853" s="46">
+        <v>2</v>
+      </c>
+      <c r="C853" s="49" t="s">
         <v>72</v>
-      </c>
-      <c r="B853" s="46">
-        <v>2</v>
-      </c>
-      <c r="C853" s="49" t="s">
-        <v>73</v>
       </c>
       <c r="D853" s="49" t="s">
         <v>13</v>
@@ -13155,7 +13140,7 @@
     </row>
     <row r="855" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A855" s="46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B855" s="46">
         <v>3</v>
@@ -13171,7 +13156,7 @@
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A856" s="46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B856" s="46"/>
       <c r="C856" s="49">
@@ -13185,13 +13170,13 @@
     </row>
     <row r="857" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A857" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B857" s="46">
         <v>4</v>
       </c>
       <c r="C857" s="49" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D857" s="49" t="s">
         <v>8</v>
@@ -13249,7 +13234,7 @@
     </row>
     <row r="861" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A861" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B861" s="46">
         <v>6</v>
@@ -13265,7 +13250,7 @@
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A862" s="46" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B862" s="46"/>
       <c r="C862" s="49">
@@ -13279,7 +13264,7 @@
     </row>
     <row r="863" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A863" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B863" s="46">
         <v>7</v>
@@ -13288,14 +13273,14 @@
         <v>9</v>
       </c>
       <c r="D863" s="49" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E863" s="49"/>
       <c r="F863" s="49"/>
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A864" s="51" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B864" s="46"/>
       <c r="C864" s="49">
@@ -13309,23 +13294,23 @@
     </row>
     <row r="865" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A865" s="52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B865" s="52">
         <v>8</v>
       </c>
       <c r="C865" s="53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D865" s="53" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E865" s="53"/>
       <c r="F865" s="53"/>
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A866" s="12" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B866" s="12"/>
       <c r="C866" s="15">
@@ -13339,7 +13324,7 @@
     </row>
     <row r="867" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A867" s="33" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B867" s="33"/>
       <c r="C867" s="34"/>
@@ -13361,7 +13346,7 @@
         <v>1</v>
       </c>
       <c r="C869" s="38" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D869" s="39"/>
       <c r="E869" s="39"/>
@@ -13373,7 +13358,7 @@
         <v>1</v>
       </c>
       <c r="C870" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D870" s="39" t="s">
         <v>8</v>
@@ -13399,10 +13384,10 @@
         <v>2</v>
       </c>
       <c r="C872" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D872" s="39" t="s">
         <v>73</v>
-      </c>
-      <c r="D872" s="39" t="s">
-        <v>74</v>
       </c>
       <c r="E872" s="39"/>
       <c r="F872" s="39"/>
@@ -13421,7 +13406,7 @@
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A874" s="36" t="s">
-        <v>271</v>
+        <v>322</v>
       </c>
       <c r="B874" s="36">
         <v>3</v>
@@ -13430,7 +13415,7 @@
         <v>51</v>
       </c>
       <c r="D874" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E874" s="39"/>
       <c r="F874" s="39"/>
@@ -13456,7 +13441,7 @@
         <v>30</v>
       </c>
       <c r="D876" s="39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E876" s="39"/>
       <c r="F876" s="39"/>
@@ -13512,10 +13497,10 @@
     <row r="881" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A881" s="40"/>
       <c r="B881" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C881" s="42" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D881" s="43"/>
       <c r="E881" s="43"/>
@@ -13582,7 +13567,7 @@
         <v>22</v>
       </c>
       <c r="D886" s="43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E886" s="43"/>
       <c r="F886" s="43"/>
@@ -13601,7 +13586,7 @@
     </row>
     <row r="888" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A888" s="40" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B888" s="40">
         <v>4</v>
@@ -13610,7 +13595,7 @@
         <v>27</v>
       </c>
       <c r="D888" s="54" t="s">
-        <v>272</v>
+        <v>4</v>
       </c>
       <c r="E888" s="43" t="s">
         <v>21</v>
@@ -13637,13 +13622,13 @@
     </row>
     <row r="890" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A890" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B890" s="40">
         <v>5</v>
       </c>
       <c r="C890" s="43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D890" s="43" t="s">
         <v>51</v>
@@ -13677,7 +13662,7 @@
         <v>1</v>
       </c>
       <c r="C893" s="38" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D893" s="39"/>
       <c r="E893" s="39"/>
@@ -13715,10 +13700,10 @@
         <v>2</v>
       </c>
       <c r="C896" s="39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D896" s="39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E896" s="39"/>
       <c r="F896" s="39"/>
@@ -13737,13 +13722,13 @@
     </row>
     <row r="898" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A898" s="36" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B898" s="36">
         <v>3</v>
       </c>
       <c r="C898" s="39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D898" s="39" t="s">
         <v>30</v>
@@ -13800,7 +13785,7 @@
         <v>9</v>
       </c>
       <c r="D902" s="39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E902" s="39"/>
       <c r="F902" s="39"/>
@@ -13828,10 +13813,10 @@
     <row r="905" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A905" s="40"/>
       <c r="B905" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C905" s="42" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D905" s="43"/>
       <c r="E905" s="43"/>
@@ -13843,7 +13828,7 @@
         <v>1</v>
       </c>
       <c r="C906" s="43" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D906" s="43" t="s">
         <v>46</v>
@@ -13872,7 +13857,7 @@
         <v>4</v>
       </c>
       <c r="D908" s="43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E908" s="43"/>
       <c r="F908" s="43"/>
@@ -13891,7 +13876,7 @@
     </row>
     <row r="910" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A910" s="40" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B910" s="40">
         <v>3</v>
@@ -13907,7 +13892,7 @@
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A911" s="40" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B911" s="40"/>
       <c r="C911" s="43">
@@ -13925,10 +13910,10 @@
         <v>4</v>
       </c>
       <c r="C912" s="43" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="D912" s="43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E912" s="43"/>
       <c r="F912" s="43"/>
@@ -13947,13 +13932,13 @@
     </row>
     <row r="914" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A914" s="40" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B914" s="40">
         <v>5</v>
       </c>
       <c r="C914" s="43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D914" s="43" t="s">
         <v>58</v>
@@ -13987,7 +13972,7 @@
         <v>1</v>
       </c>
       <c r="C917" s="38" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D917" s="39"/>
       <c r="E917" s="39"/>
@@ -14002,7 +13987,7 @@
         <v>34</v>
       </c>
       <c r="D918" s="39" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E918" s="39"/>
       <c r="F918" s="39"/>
@@ -14051,7 +14036,7 @@
         <v>3</v>
       </c>
       <c r="C922" s="39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D922" s="39" t="s">
         <v>33</v>
@@ -14080,7 +14065,7 @@
         <v>41</v>
       </c>
       <c r="D924" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E924" s="39"/>
       <c r="F924" s="39"/>
@@ -14134,10 +14119,10 @@
     <row r="929" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A929" s="40"/>
       <c r="B929" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C929" s="42" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D929" s="43"/>
       <c r="E929" s="43"/>
@@ -14149,7 +14134,7 @@
         <v>1</v>
       </c>
       <c r="C930" s="43" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D930" s="43" t="s">
         <v>21</v>
@@ -14175,7 +14160,7 @@
         <v>2</v>
       </c>
       <c r="C932" s="43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D932" s="43" t="s">
         <v>17</v>
@@ -14201,7 +14186,7 @@
         <v>3</v>
       </c>
       <c r="C934" s="43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D934" s="43" t="s">
         <v>40</v>
@@ -14227,10 +14212,10 @@
         <v>4</v>
       </c>
       <c r="C936" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D936" s="43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E936" s="43"/>
       <c r="F936" s="43"/>
@@ -14284,10 +14269,10 @@
     <row r="941" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A941" s="46"/>
       <c r="B941" s="47" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C941" s="48" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D941" s="49"/>
       <c r="E941" s="49"/>
@@ -14295,13 +14280,13 @@
     </row>
     <row r="942" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A942" s="46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B942" s="46">
         <v>1</v>
       </c>
       <c r="C942" s="49" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D942" s="49" t="s">
         <v>52</v>
@@ -14311,7 +14296,7 @@
     </row>
     <row r="943" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A943" s="46" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B943" s="46"/>
       <c r="C943" s="49">
@@ -14341,7 +14326,7 @@
     </row>
     <row r="945" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A945" s="46" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B945" s="46"/>
       <c r="C945" s="49">
@@ -14355,7 +14340,7 @@
     </row>
     <row r="946" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A946" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B946" s="46">
         <v>3</v>
@@ -14371,7 +14356,7 @@
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A947" s="46" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B947" s="46"/>
       <c r="C947" s="49">
@@ -14385,7 +14370,7 @@
     </row>
     <row r="948" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A948" s="46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B948" s="46">
         <v>4</v>
@@ -14401,7 +14386,7 @@
     </row>
     <row r="949" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A949" s="46" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B949" s="46"/>
       <c r="C949" s="49">
@@ -14427,7 +14412,7 @@
         <v>38</v>
       </c>
       <c r="E950" s="49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F950" s="49" t="s">
         <v>39</v>
@@ -14435,7 +14420,7 @@
     </row>
     <row r="951" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A951" s="46" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B951" s="46"/>
       <c r="C951" s="49">
@@ -14453,7 +14438,7 @@
     </row>
     <row r="952" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A952" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B952" s="46">
         <v>6</v>
@@ -14469,7 +14454,7 @@
     </row>
     <row r="953" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A953" s="46" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B953" s="46"/>
       <c r="C953" s="49">
@@ -14483,7 +14468,7 @@
     </row>
     <row r="954" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A954" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B954" s="46">
         <v>7</v>
@@ -14492,7 +14477,7 @@
         <v>39</v>
       </c>
       <c r="D954" s="49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E954" s="49" t="s">
         <v>43</v>
@@ -14501,7 +14486,7 @@
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A955" s="51" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B955" s="46"/>
       <c r="C955" s="49">
@@ -14517,7 +14502,7 @@
     </row>
     <row r="956" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A956" s="46" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B956" s="46"/>
       <c r="C956" s="49"/>
@@ -14527,7 +14512,7 @@
     </row>
     <row r="957" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A957" s="33" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B957" s="33"/>
       <c r="C957" s="34"/>
@@ -14549,7 +14534,7 @@
         <v>1</v>
       </c>
       <c r="C959" s="38" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D959" s="39"/>
       <c r="E959" s="39"/>
@@ -14564,7 +14549,7 @@
         <v>9</v>
       </c>
       <c r="D960" s="39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E960" s="39"/>
       <c r="F960" s="39"/>
@@ -14587,7 +14572,7 @@
         <v>2</v>
       </c>
       <c r="C962" s="39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D962" s="39" t="s">
         <v>48</v>
@@ -14642,7 +14627,7 @@
         <v>3</v>
       </c>
       <c r="D966" s="39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E966" s="39"/>
       <c r="F966" s="39"/>
@@ -14667,10 +14652,10 @@
         <v>5</v>
       </c>
       <c r="C968" s="39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D968" s="39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E968" s="39"/>
       <c r="F968" s="39"/>
@@ -14698,10 +14683,10 @@
     <row r="971" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A971" s="40"/>
       <c r="B971" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C971" s="42" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D971" s="43"/>
       <c r="E971" s="43"/>
@@ -14739,7 +14724,7 @@
         <v>2</v>
       </c>
       <c r="C974" s="43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D974" s="43" t="s">
         <v>12</v>
@@ -14813,7 +14798,7 @@
     </row>
     <row r="980" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A980" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B980" s="40">
         <v>5</v>
@@ -14822,7 +14807,7 @@
         <v>46</v>
       </c>
       <c r="D980" s="43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E980" s="43" t="s">
         <v>5</v>
@@ -14857,7 +14842,7 @@
         <v>1</v>
       </c>
       <c r="C983" s="38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D983" s="39"/>
       <c r="E983" s="39"/>
@@ -14865,7 +14850,7 @@
     </row>
     <row r="984" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A984" s="36" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B984" s="36">
         <v>1</v>
@@ -14874,7 +14859,7 @@
         <v>26</v>
       </c>
       <c r="D984" s="39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E984" s="39"/>
       <c r="F984" s="39"/>
@@ -14897,7 +14882,7 @@
         <v>2</v>
       </c>
       <c r="C986" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D986" s="39" t="s">
         <v>34</v>
@@ -14925,16 +14910,16 @@
         <v>3</v>
       </c>
       <c r="C988" s="39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D988" s="45" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E988" s="39" t="s">
         <v>54</v>
       </c>
       <c r="F988" s="39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="989" spans="1:6" x14ac:dyDescent="0.2">
@@ -14962,7 +14947,7 @@
         <v>41</v>
       </c>
       <c r="D990" s="39" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E990" s="39"/>
       <c r="F990" s="39"/>
@@ -14990,7 +14975,7 @@
         <v>8</v>
       </c>
       <c r="D992" s="39" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E992" s="39" t="s">
         <v>62</v>
@@ -15022,10 +15007,10 @@
     <row r="995" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A995" s="40"/>
       <c r="B995" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C995" s="42" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D995" s="43"/>
       <c r="E995" s="43"/>
@@ -15033,7 +15018,7 @@
     </row>
     <row r="996" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A996" s="40" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B996" s="40">
         <v>1</v>
@@ -15042,7 +15027,7 @@
         <v>33</v>
       </c>
       <c r="D996" s="43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E996" s="43"/>
       <c r="F996" s="43"/>
@@ -15065,10 +15050,10 @@
         <v>2</v>
       </c>
       <c r="C998" s="43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D998" s="43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E998" s="43"/>
       <c r="F998" s="43"/>
@@ -15113,16 +15098,16 @@
     </row>
     <row r="1002" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1002" s="40" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B1002" s="40">
         <v>4</v>
       </c>
       <c r="C1002" s="43" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D1002" s="43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E1002" s="43"/>
       <c r="F1002" s="43"/>
@@ -15150,7 +15135,7 @@
         <v>27</v>
       </c>
       <c r="D1004" s="43" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E1004" s="43"/>
       <c r="F1004" s="43"/>
@@ -15181,7 +15166,7 @@
         <v>1</v>
       </c>
       <c r="C1007" s="38" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D1007" s="39"/>
       <c r="E1007" s="39"/>
@@ -15196,7 +15181,7 @@
         <v>31</v>
       </c>
       <c r="D1008" s="39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E1008" s="39"/>
       <c r="F1008" s="39"/>
@@ -15222,7 +15207,7 @@
         <v>34</v>
       </c>
       <c r="D1010" s="39" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E1010" s="39"/>
       <c r="F1010" s="39"/>
@@ -15248,7 +15233,7 @@
         <v>56</v>
       </c>
       <c r="D1012" s="39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E1012" s="39"/>
       <c r="F1012" s="39"/>
@@ -15271,10 +15256,10 @@
         <v>4</v>
       </c>
       <c r="C1014" s="39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D1014" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E1014" s="39"/>
       <c r="F1014" s="39"/>
@@ -15302,7 +15287,7 @@
         <v>41</v>
       </c>
       <c r="D1016" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E1016" s="39"/>
       <c r="F1016" s="39"/>
@@ -15330,10 +15315,10 @@
     <row r="1019" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1019" s="40"/>
       <c r="B1019" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C1019" s="42" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D1019" s="43"/>
       <c r="E1019" s="43"/>
@@ -15341,13 +15326,13 @@
     </row>
     <row r="1020" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1020" s="40" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B1020" s="40">
         <v>1</v>
       </c>
       <c r="C1020" s="43" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D1020" s="43" t="s">
         <v>21</v>
@@ -15369,7 +15354,7 @@
     </row>
     <row r="1022" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1022" s="40" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B1022" s="40">
         <v>2</v>
@@ -15378,7 +15363,7 @@
         <v>56</v>
       </c>
       <c r="D1022" s="43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E1022" s="43"/>
       <c r="F1022" s="43"/>
@@ -15401,7 +15386,7 @@
         <v>3</v>
       </c>
       <c r="C1024" s="43" t="s">
-        <v>291</v>
+        <v>97</v>
       </c>
       <c r="D1024" s="43" t="s">
         <v>20</v>
@@ -15449,7 +15434,7 @@
     </row>
     <row r="1028" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1028" s="40" t="s">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="B1028" s="40">
         <v>5</v>
@@ -15486,10 +15471,10 @@
     <row r="1031" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1031" s="46"/>
       <c r="B1031" s="47" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C1031" s="48" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D1031" s="49"/>
       <c r="E1031" s="49"/>
@@ -15506,7 +15491,7 @@
         <v>12</v>
       </c>
       <c r="D1032" s="49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E1032" s="49"/>
       <c r="F1032" s="49"/>
@@ -15525,7 +15510,7 @@
     </row>
     <row r="1034" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1034" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1034" s="46">
         <v>2</v>
@@ -15553,7 +15538,7 @@
     </row>
     <row r="1036" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1036" s="46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1036" s="46">
         <v>3</v>
@@ -15562,14 +15547,14 @@
         <v>26</v>
       </c>
       <c r="D1036" s="49" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E1036" s="49"/>
       <c r="F1036" s="49"/>
     </row>
     <row r="1037" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1037" s="46" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B1037" s="46"/>
       <c r="C1037" s="49">
@@ -15583,7 +15568,7 @@
     </row>
     <row r="1038" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1038" s="46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B1038" s="46">
         <v>4</v>
@@ -15631,7 +15616,7 @@
     </row>
     <row r="1041" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1041" s="46" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B1041" s="46"/>
       <c r="C1041" s="49">
@@ -15649,7 +15634,7 @@
     </row>
     <row r="1042" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1042" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B1042" s="46">
         <v>6</v>
@@ -15677,7 +15662,7 @@
     </row>
     <row r="1044" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1044" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B1044" s="46">
         <v>7</v>
@@ -15686,14 +15671,14 @@
         <v>9</v>
       </c>
       <c r="D1044" s="49" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E1044" s="49"/>
       <c r="F1044" s="49"/>
     </row>
     <row r="1045" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1045" s="51" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B1045" s="46"/>
       <c r="C1045" s="49">
@@ -15707,7 +15692,7 @@
     </row>
     <row r="1046" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A1046" s="33" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B1046" s="33"/>
       <c r="C1046" s="34"/>
@@ -15729,7 +15714,7 @@
         <v>1</v>
       </c>
       <c r="C1048" s="38" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D1048" s="39"/>
       <c r="E1048" s="39"/>
@@ -15744,7 +15729,7 @@
         <v>48</v>
       </c>
       <c r="D1049" s="39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E1049" s="39"/>
       <c r="F1049" s="39"/>
@@ -15796,7 +15781,7 @@
         <v>56</v>
       </c>
       <c r="D1053" s="39" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E1053" s="39"/>
       <c r="F1053" s="39"/>
@@ -15815,16 +15800,16 @@
     </row>
     <row r="1055" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1055" s="36" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B1055" s="36">
         <v>4</v>
       </c>
       <c r="C1055" s="39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D1055" s="39" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E1055" s="39"/>
       <c r="F1055" s="39"/>
@@ -15843,13 +15828,13 @@
     </row>
     <row r="1057" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1057" s="36" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B1057" s="36">
         <v>5</v>
       </c>
       <c r="C1057" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1057" s="39" t="s">
         <v>10</v>
@@ -15880,10 +15865,10 @@
     <row r="1060" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1060" s="40"/>
       <c r="B1060" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C1060" s="42" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D1060" s="43"/>
       <c r="E1060" s="43"/>
@@ -15898,7 +15883,7 @@
         <v>64</v>
       </c>
       <c r="D1061" s="43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E1061" s="43"/>
       <c r="F1061" s="43"/>
@@ -15921,7 +15906,7 @@
         <v>2</v>
       </c>
       <c r="C1063" s="43" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D1063" s="43" t="s">
         <v>20</v>
@@ -15943,7 +15928,7 @@
     </row>
     <row r="1065" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1065" s="40" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B1065" s="40">
         <v>3</v>
@@ -15952,7 +15937,7 @@
         <v>19</v>
       </c>
       <c r="D1065" s="43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E1065" s="43"/>
       <c r="F1065" s="43"/>
@@ -15978,7 +15963,7 @@
         <v>27</v>
       </c>
       <c r="D1067" s="43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E1067" s="43"/>
       <c r="F1067" s="43"/>
@@ -15997,7 +15982,7 @@
     </row>
     <row r="1069" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1069" s="40" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B1069" s="40">
         <v>5</v>
@@ -16037,7 +16022,7 @@
         <v>1</v>
       </c>
       <c r="C1072" s="38" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D1072" s="39"/>
       <c r="E1072" s="39"/>
@@ -16075,7 +16060,7 @@
         <v>2</v>
       </c>
       <c r="C1075" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1075" s="39" t="s">
         <v>48</v>
@@ -16101,7 +16086,7 @@
         <v>3</v>
       </c>
       <c r="C1077" s="39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1077" s="39" t="s">
         <v>3</v>
@@ -16123,7 +16108,7 @@
     </row>
     <row r="1079" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1079" s="36" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B1079" s="36">
         <v>4</v>
@@ -16151,7 +16136,7 @@
     </row>
     <row r="1081" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1081" s="36" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B1081" s="36">
         <v>5</v>
@@ -16188,10 +16173,10 @@
     <row r="1084" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1084" s="40"/>
       <c r="B1084" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C1084" s="42" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D1084" s="43"/>
       <c r="E1084" s="43"/>
@@ -16199,13 +16184,13 @@
     </row>
     <row r="1085" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1085" s="40" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B1085" s="40">
         <v>1</v>
       </c>
       <c r="C1085" s="43" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D1085" s="43" t="s">
         <v>4</v>
@@ -16253,7 +16238,7 @@
     </row>
     <row r="1089" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1089" s="40" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B1089" s="40">
         <v>3</v>
@@ -16289,7 +16274,7 @@
     </row>
     <row r="1091" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1091" s="40" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B1091" s="40">
         <v>4</v>
@@ -16298,7 +16283,7 @@
         <v>40</v>
       </c>
       <c r="D1091" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E1091" s="43"/>
       <c r="F1091" s="43"/>
@@ -16317,7 +16302,7 @@
     </row>
     <row r="1093" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1093" s="40" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B1093" s="40">
         <v>5</v>
@@ -16357,7 +16342,7 @@
         <v>1</v>
       </c>
       <c r="C1096" s="38" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D1096" s="39"/>
       <c r="E1096" s="39"/>
@@ -16391,13 +16376,13 @@
     </row>
     <row r="1099" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1099" s="36" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B1099" s="36">
         <v>2</v>
       </c>
       <c r="C1099" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D1099" s="39" t="s">
         <v>8</v>
@@ -16419,7 +16404,7 @@
     </row>
     <row r="1101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1101" s="36" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B1101" s="36">
         <v>3</v>
@@ -16510,10 +16495,10 @@
     <row r="1108" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1108" s="40"/>
       <c r="B1108" s="41" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C1108" s="42" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="D1108" s="43"/>
       <c r="E1108" s="43"/>
@@ -16525,7 +16510,7 @@
         <v>1</v>
       </c>
       <c r="C1109" s="43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D1109" s="43" t="s">
         <v>12</v>
@@ -16573,13 +16558,13 @@
     </row>
     <row r="1113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1113" s="40" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B1113" s="40">
         <v>3</v>
       </c>
       <c r="C1113" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D1113" s="43" t="s">
         <v>4</v>
@@ -16589,7 +16574,7 @@
     </row>
     <row r="1114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1114" s="40" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B1114" s="40"/>
       <c r="C1114" s="43">
@@ -16603,13 +16588,13 @@
     </row>
     <row r="1115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1115" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B1115" s="40">
         <v>4</v>
       </c>
       <c r="C1115" s="43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D1115" s="43" t="s">
         <v>23</v>
@@ -16631,7 +16616,7 @@
     </row>
     <row r="1117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1117" s="40" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B1117" s="40">
         <v>5</v>
@@ -16668,10 +16653,10 @@
     <row r="1120" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1120" s="46"/>
       <c r="B1120" s="47" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C1120" s="48" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="D1120" s="49"/>
       <c r="E1120" s="49"/>
@@ -16679,7 +16664,7 @@
     </row>
     <row r="1121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1121" s="46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B1121" s="46">
         <v>1</v>
@@ -16695,7 +16680,7 @@
     </row>
     <row r="1122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1122" s="46" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B1122" s="46"/>
       <c r="C1122" s="49">
@@ -16709,23 +16694,23 @@
     </row>
     <row r="1123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1123" s="46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1123" s="46">
         <v>2</v>
       </c>
       <c r="C1123" s="49" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D1123" s="49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E1123" s="49"/>
       <c r="F1123" s="49"/>
     </row>
     <row r="1124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1124" s="46" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B1124" s="46"/>
       <c r="C1124" s="49">
@@ -16739,7 +16724,7 @@
     </row>
     <row r="1125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1125" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1125" s="46">
         <v>3</v>
@@ -16748,7 +16733,7 @@
         <v>37</v>
       </c>
       <c r="D1125" s="49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E1125" s="49" t="s">
         <v>62</v>
@@ -16811,10 +16796,10 @@
         <v>41</v>
       </c>
       <c r="E1129" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F1129" s="49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1130" spans="1:6" x14ac:dyDescent="0.2">
@@ -16835,23 +16820,23 @@
     </row>
     <row r="1131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1131" s="46" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B1131" s="46">
         <v>6</v>
       </c>
       <c r="C1131" s="49" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D1131" s="49" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E1131" s="49"/>
       <c r="F1131" s="49"/>
     </row>
     <row r="1132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1132" s="46" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B1132" s="46"/>
       <c r="C1132" s="49">
@@ -16865,16 +16850,16 @@
     </row>
     <row r="1133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1133" s="51" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B1133" s="46">
         <v>7</v>
       </c>
       <c r="C1133" s="49" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D1133" s="49" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E1133" s="49"/>
       <c r="F1133" s="49"/>
@@ -16893,13 +16878,13 @@
     </row>
     <row r="1135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1135" s="46" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B1135" s="46">
         <v>8</v>
       </c>
       <c r="C1135" s="49" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D1135" s="49" t="s">
         <v>41</v>
@@ -16921,13 +16906,13 @@
     </row>
     <row r="1137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1137" s="46" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B1137" s="46">
         <v>10</v>
       </c>
       <c r="C1137" s="49" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D1137" s="49" t="s">
         <v>33</v>
@@ -16949,13 +16934,13 @@
     </row>
     <row r="1139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1139" s="46" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B1139" s="46">
         <v>11</v>
       </c>
       <c r="C1139" s="49" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D1139" s="49" t="s">
         <v>17</v>
@@ -16965,7 +16950,7 @@
     </row>
     <row r="1140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1140" s="51" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="B1140" s="46"/>
       <c r="C1140" s="49">
@@ -16979,13 +16964,13 @@
     </row>
     <row r="1141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1141" s="46" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B1141" s="46">
         <v>12</v>
       </c>
       <c r="C1141" s="49" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D1141" s="49" t="s">
         <v>43</v>
@@ -17007,13 +16992,13 @@
     </row>
     <row r="1143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1143" s="46" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B1143" s="46">
         <v>13</v>
       </c>
       <c r="C1143" s="49" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D1143" s="49" t="s">
         <v>27</v>
@@ -17035,16 +17020,16 @@
     </row>
     <row r="1145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1145" s="46" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B1145" s="46">
         <v>14</v>
       </c>
       <c r="C1145" s="49" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D1145" s="49" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E1145" s="49"/>
       <c r="F1145" s="49"/>

--- a/FullSeason5.xlsx
+++ b/FullSeason5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ianjpeck/Documents/GitHub/sbparser/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E30657E-F07A-F84F-B900-3B8B4C3907C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67E1E26-AAEF-0846-9C94-8D0E73CBE9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16500" xr2:uid="{C96D0F46-2D53-AF4F-A06C-8FE540EC6340}"/>
   </bookViews>
@@ -466,9 +466,6 @@
     <t>Toon Link 100% Handicap</t>
   </si>
   <si>
-    <t xml:space="preserve">Smash Bros. Championship </t>
-  </si>
-  <si>
     <t>Month 4</t>
   </si>
   <si>
@@ -1165,6 +1162,9 @@
   </si>
   <si>
     <t>Guest appearance by DK</t>
+  </si>
+  <si>
+    <t>Smash Bros. Championship</t>
   </si>
 </sst>
 </file>
@@ -3892,7 +3892,7 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B162" s="7">
         <v>4</v>
@@ -5410,7 +5410,7 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275" s="12" t="s">
-        <v>137</v>
+        <v>322</v>
       </c>
       <c r="B275" s="12">
         <v>8</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="279" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B279" s="1"/>
       <c r="C279" s="2"/>
@@ -5482,7 +5482,7 @@
         <v>1</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D281" s="6"/>
       <c r="E281" s="6"/>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B282" s="3">
         <v>1</v>
@@ -5499,7 +5499,7 @@
         <v>18</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E282" s="6"/>
       <c r="F282" s="6"/>
@@ -5644,7 +5644,7 @@
         <v>14</v>
       </c>
       <c r="C293" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D293" s="10"/>
       <c r="E293" s="10"/>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B294" s="7">
         <v>1</v>
@@ -5732,7 +5732,7 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B300" s="7">
         <v>4</v>
@@ -5760,7 +5760,7 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A302" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B302" s="7">
         <v>5</v>
@@ -5798,7 +5798,7 @@
         <v>1</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D305" s="6"/>
       <c r="E305" s="6"/>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B306" s="3">
         <v>1</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B310" s="3">
         <v>3</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A312" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B312" s="3">
         <v>4</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B314" s="3">
         <v>5</v>
@@ -5956,7 +5956,7 @@
         <v>14</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D317" s="10"/>
       <c r="E317" s="10"/>
@@ -6070,7 +6070,7 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B326" s="7">
         <v>5</v>
@@ -6108,7 +6108,7 @@
         <v>1</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D329" s="6"/>
       <c r="E329" s="6"/>
@@ -6122,7 +6122,7 @@
         <v>1</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D330" s="6" t="s">
         <v>8</v>
@@ -6230,7 +6230,7 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B338" s="3">
         <v>5</v>
@@ -6268,7 +6268,7 @@
         <v>14</v>
       </c>
       <c r="C341" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D341" s="10"/>
       <c r="E341" s="10"/>
@@ -6356,7 +6356,7 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A348" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B348" s="7">
         <v>4</v>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A350" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B350" s="7">
         <v>5</v>
@@ -6419,10 +6419,10 @@
     <row r="353" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A353" s="12"/>
       <c r="B353" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C353" s="14" t="s">
         <v>151</v>
-      </c>
-      <c r="C353" s="14" t="s">
-        <v>152</v>
       </c>
       <c r="D353" s="15"/>
       <c r="E353" s="15"/>
@@ -6538,7 +6538,7 @@
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A361" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B361" s="12"/>
       <c r="C361" s="15">
@@ -6580,7 +6580,7 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B364" s="12">
         <v>6</v>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A365" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B365" s="12"/>
       <c r="C365" s="15">
@@ -6618,7 +6618,7 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A366" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B366" s="12">
         <v>7</v>
@@ -6638,7 +6638,7 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A367" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B367" s="12"/>
       <c r="C367" s="15">
@@ -6690,7 +6690,7 @@
         <v>9</v>
       </c>
       <c r="C370" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D370" s="15" t="s">
         <v>9</v>
@@ -6700,7 +6700,7 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A371" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B371" s="12"/>
       <c r="C371" s="15">
@@ -6714,7 +6714,7 @@
     </row>
     <row r="372" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B372" s="1"/>
       <c r="C372" s="2"/>
@@ -6734,7 +6734,7 @@
         <v>1</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D374" s="6"/>
       <c r="E374" s="6"/>
@@ -6820,7 +6820,7 @@
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A381" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B381" s="3">
         <v>4</v>
@@ -6836,7 +6836,7 @@
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A382" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B382" s="3"/>
       <c r="C382" s="6">
@@ -6850,7 +6850,7 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A383" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B383" s="3">
         <v>5</v>
@@ -6866,7 +6866,7 @@
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A384" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B384" s="3"/>
       <c r="C384" s="6">
@@ -6890,7 +6890,7 @@
         <v>14</v>
       </c>
       <c r="C386" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D386" s="10"/>
       <c r="E386" s="10"/>
@@ -6924,7 +6924,7 @@
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A389" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B389" s="7">
         <v>2</v>
@@ -6978,7 +6978,7 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A393" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B393" s="7">
         <v>4</v>
@@ -7034,7 +7034,7 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A396" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B396" s="7"/>
       <c r="C396" s="10">
@@ -7062,7 +7062,7 @@
         <v>1</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D398" s="6"/>
       <c r="E398" s="6"/>
@@ -7216,7 +7216,7 @@
         <v>14</v>
       </c>
       <c r="C410" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D410" s="10"/>
       <c r="E410" s="10"/>
@@ -7366,7 +7366,7 @@
         <v>1</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D422" s="6"/>
       <c r="E422" s="6"/>
@@ -7514,7 +7514,7 @@
         <v>14</v>
       </c>
       <c r="C434" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D434" s="10"/>
       <c r="E434" s="10"/>
@@ -7616,7 +7616,7 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A442" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B442" s="7"/>
       <c r="C442" s="10">
@@ -7630,7 +7630,7 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A443" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B443" s="7">
         <v>5</v>
@@ -7646,7 +7646,7 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A444" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B444" s="7"/>
       <c r="C444" s="10">
@@ -7667,10 +7667,10 @@
     <row r="446" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A446" s="12"/>
       <c r="B446" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C446" s="14" t="s">
         <v>175</v>
-      </c>
-      <c r="C446" s="14" t="s">
-        <v>176</v>
       </c>
       <c r="D446" s="15"/>
       <c r="E446" s="15"/>
@@ -7762,7 +7762,7 @@
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A452" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B452" s="12"/>
       <c r="C452" s="15">
@@ -7792,7 +7792,7 @@
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A454" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B454" s="12"/>
       <c r="C454" s="15">
@@ -7824,7 +7824,7 @@
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A456" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B456" s="12"/>
       <c r="C456" s="15">
@@ -7849,7 +7849,7 @@
         <v>9</v>
       </c>
       <c r="D457" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E457" s="15"/>
       <c r="F457" s="15"/>
@@ -7884,7 +7884,7 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A460" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B460" s="12"/>
       <c r="C460" s="15">
@@ -7914,7 +7914,7 @@
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A462" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B462" s="12"/>
       <c r="C462" s="15">
@@ -7928,7 +7928,7 @@
     </row>
     <row r="463" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B463" s="1"/>
       <c r="C463" s="2"/>
@@ -7948,7 +7948,7 @@
         <v>1</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D465" s="6"/>
       <c r="E465" s="6"/>
@@ -7963,7 +7963,7 @@
         <v>69</v>
       </c>
       <c r="D466" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E466" s="6"/>
       <c r="F466" s="6"/>
@@ -8076,7 +8076,7 @@
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A475" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B475" s="3"/>
       <c r="C475" s="6">
@@ -8100,7 +8100,7 @@
         <v>14</v>
       </c>
       <c r="C477" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D477" s="10"/>
       <c r="E477" s="10"/>
@@ -8134,7 +8134,7 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A480" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B480" s="7">
         <v>2</v>
@@ -8188,7 +8188,7 @@
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A484" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B484" s="7">
         <v>4</v>
@@ -8204,7 +8204,7 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A485" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B485" s="7"/>
       <c r="C485" s="10">
@@ -8218,7 +8218,7 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A486" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B486" s="7">
         <v>5</v>
@@ -8256,7 +8256,7 @@
         <v>1</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D489" s="6"/>
       <c r="E489" s="6"/>
@@ -8268,7 +8268,7 @@
         <v>1</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D490" s="6" t="s">
         <v>34</v>
@@ -8296,7 +8296,7 @@
         <v>2</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D492" s="6" t="s">
         <v>32</v>
@@ -8416,7 +8416,7 @@
         <v>14</v>
       </c>
       <c r="C501" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D501" s="10"/>
       <c r="E501" s="10"/>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A502" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B502" s="7">
         <v>1</v>
@@ -8568,7 +8568,7 @@
         <v>1</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D513" s="6"/>
       <c r="E513" s="6"/>
@@ -8602,7 +8602,7 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A516" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B516" s="3">
         <v>2</v>
@@ -8611,7 +8611,7 @@
         <v>32</v>
       </c>
       <c r="D516" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E516" s="6"/>
       <c r="F516" s="6"/>
@@ -8806,7 +8806,7 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A532" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B532" s="7">
         <v>4</v>
@@ -8822,7 +8822,7 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A533" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B533" s="7"/>
       <c r="C533" s="10">
@@ -8869,7 +8869,7 @@
     <row r="537" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A537" s="12"/>
       <c r="B537" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C537" s="14" t="s">
         <v>28</v>
@@ -8952,7 +8952,7 @@
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A543" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B543" s="12"/>
       <c r="C543" s="15">
@@ -9014,7 +9014,7 @@
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A547" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B547" s="12"/>
       <c r="C547" s="15">
@@ -9041,7 +9041,7 @@
         <v>9</v>
       </c>
       <c r="D548" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E548" s="15"/>
       <c r="F548" s="15"/>
@@ -9076,7 +9076,7 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A551" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B551" s="12"/>
       <c r="C551" s="15">
@@ -9090,7 +9090,7 @@
     </row>
     <row r="552" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B552" s="1"/>
       <c r="C552" s="2"/>
@@ -9118,13 +9118,13 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A555" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B555" s="3">
         <v>1</v>
       </c>
       <c r="C555" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D555" s="6" t="s">
         <v>48</v>
@@ -9146,7 +9146,7 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A557" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B557" s="3">
         <v>2</v>
@@ -9270,7 +9270,7 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A567" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B567" s="7">
         <v>1</v>
@@ -9298,7 +9298,7 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A569" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B569" s="7">
         <v>2</v>
@@ -9314,7 +9314,7 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A570" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B570" s="7"/>
       <c r="C570" s="10">
@@ -9328,7 +9328,7 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A571" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B571" s="7">
         <v>3</v>
@@ -9426,7 +9426,7 @@
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A579" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B579" s="3">
         <v>1</v>
@@ -9454,7 +9454,7 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A581" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B581" s="3">
         <v>2</v>
@@ -9482,7 +9482,7 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A583" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B583" s="3">
         <v>3</v>
@@ -9510,7 +9510,7 @@
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A585" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B585" s="3">
         <v>4</v>
@@ -9538,7 +9538,7 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A587" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B587" s="3">
         <v>5</v>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A593" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B593" s="7">
         <v>2</v>
@@ -9642,7 +9642,7 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A595" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B595" s="7">
         <v>3</v>
@@ -9670,7 +9670,7 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A597" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B597" s="7">
         <v>4</v>
@@ -9698,7 +9698,7 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A599" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B599" s="7">
         <v>5</v>
@@ -9716,7 +9716,7 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A600" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B600" s="7"/>
       <c r="C600" s="10">
@@ -9828,7 +9828,7 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A609" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B609" s="3">
         <v>4</v>
@@ -9856,7 +9856,7 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A611" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B611" s="3">
         <v>5</v>
@@ -9902,7 +9902,7 @@
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A615" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B615" s="7">
         <v>1</v>
@@ -9986,7 +9986,7 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A621" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B621" s="7">
         <v>4</v>
@@ -10014,7 +10014,7 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A623" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B623" s="7">
         <v>5</v>
@@ -10049,35 +10049,35 @@
     <row r="626" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A626" s="12"/>
       <c r="B626" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C626" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D626" s="15"/>
       <c r="E626" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="F626" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="F626" s="15" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A627" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B627" s="12">
         <v>1</v>
       </c>
       <c r="C627" s="15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D627" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E627" s="15"/>
       <c r="F627" s="24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.2">
@@ -10094,7 +10094,7 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A629" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B629" s="12">
         <v>2</v>
@@ -10122,7 +10122,7 @@
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A631" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B631" s="12">
         <v>3</v>
@@ -10150,7 +10150,7 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A633" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B633" s="12">
         <v>4</v>
@@ -10178,7 +10178,7 @@
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A635" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B635" s="12">
         <v>5</v>
@@ -10206,7 +10206,7 @@
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A637" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B637" s="12">
         <v>6</v>
@@ -10234,7 +10234,7 @@
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A639" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B639" s="12">
         <v>7</v>
@@ -10262,7 +10262,7 @@
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A641" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B641" s="12">
         <v>8</v>
@@ -10290,7 +10290,7 @@
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A643" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B643" s="12">
         <v>9</v>
@@ -10318,7 +10318,7 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A645" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B645" s="12">
         <v>10</v>
@@ -10346,7 +10346,7 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A647" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B647" s="12">
         <v>11</v>
@@ -10374,13 +10374,13 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A649" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B649" s="12">
         <v>12</v>
       </c>
       <c r="C649" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D649" s="15" t="s">
         <v>85</v>
@@ -10402,7 +10402,7 @@
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A651" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B651" s="12">
         <v>13</v>
@@ -10430,7 +10430,7 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A653" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B653" s="12">
         <v>14</v>
@@ -10458,7 +10458,7 @@
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A655" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B655" s="12">
         <v>15</v>
@@ -10486,20 +10486,20 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A657" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B657" s="27">
         <v>1</v>
       </c>
       <c r="C657" s="28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D657" s="28" t="s">
         <v>21</v>
       </c>
       <c r="E657" s="27"/>
       <c r="F657" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.2">
@@ -10516,7 +10516,7 @@
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A659" s="27" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B659" s="27">
         <v>2</v>
@@ -10544,7 +10544,7 @@
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A661" s="27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B661" s="27">
         <v>3</v>
@@ -10572,7 +10572,7 @@
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A663" s="27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B663" s="27">
         <v>4</v>
@@ -10600,7 +10600,7 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A665" s="27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B665" s="27">
         <v>5</v>
@@ -10628,7 +10628,7 @@
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A667" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B667" s="27">
         <v>6</v>
@@ -10656,7 +10656,7 @@
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A669" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B669" s="27">
         <v>7</v>
@@ -10684,7 +10684,7 @@
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A671" s="27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B671" s="27">
         <v>8</v>
@@ -10712,13 +10712,13 @@
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A673" s="27" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B673" s="27">
         <v>9</v>
       </c>
       <c r="C673" s="28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D673" s="28" t="s">
         <v>65</v>
@@ -10740,7 +10740,7 @@
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A675" s="27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B675" s="27">
         <v>10</v>
@@ -10768,7 +10768,7 @@
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A677" s="27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B677" s="27">
         <v>11</v>
@@ -10796,7 +10796,7 @@
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A679" s="31" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B679" s="31">
         <v>12</v>
@@ -10824,13 +10824,13 @@
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A681" s="27" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B681" s="27">
         <v>13</v>
       </c>
       <c r="C681" s="28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D681" s="28" t="s">
         <v>38</v>
@@ -10852,7 +10852,7 @@
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A683" s="27" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B683" s="27">
         <v>14</v>
@@ -10880,7 +10880,7 @@
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A685" s="27" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B685" s="27">
         <v>15</v>
@@ -10908,7 +10908,7 @@
     </row>
     <row r="687" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B687" s="1"/>
       <c r="C687" s="2"/>
@@ -10936,7 +10936,7 @@
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A690" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B690" s="3">
         <v>1</v>
@@ -11042,7 +11042,7 @@
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A698" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B698" s="3">
         <v>5</v>
@@ -11051,7 +11051,7 @@
         <v>31</v>
       </c>
       <c r="D698" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E698" s="6"/>
       <c r="F698" s="6"/>
@@ -11088,7 +11088,7 @@
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A702" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B702" s="7">
         <v>1</v>
@@ -11142,7 +11142,7 @@
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A706" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B706" s="7">
         <v>3</v>
@@ -11170,7 +11170,7 @@
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A708" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B708" s="7">
         <v>4</v>
@@ -11198,7 +11198,7 @@
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A710" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B710" s="7">
         <v>5</v>
@@ -11244,7 +11244,7 @@
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A714" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B714" s="3">
         <v>1</v>
@@ -11298,7 +11298,7 @@
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A718" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B718" s="3">
         <v>3</v>
@@ -11314,7 +11314,7 @@
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A719" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B719" s="3"/>
       <c r="C719" s="6">
@@ -11328,7 +11328,7 @@
     </row>
     <row r="720" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A720" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B720" s="3">
         <v>4</v>
@@ -11356,7 +11356,7 @@
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A722" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B722" s="3">
         <v>5</v>
@@ -11454,7 +11454,7 @@
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A730" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B730" s="7">
         <v>3</v>
@@ -11470,7 +11470,7 @@
     </row>
     <row r="731" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A731" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B731" s="7"/>
       <c r="C731" s="10">
@@ -11484,7 +11484,7 @@
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A732" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B732" s="7">
         <v>4</v>
@@ -11500,7 +11500,7 @@
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A733" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B733" s="7"/>
       <c r="C733" s="10">
@@ -11514,7 +11514,7 @@
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A734" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B734" s="7">
         <v>5</v>
@@ -11638,13 +11638,13 @@
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A744" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B744" s="3">
         <v>4</v>
       </c>
       <c r="C744" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D744" s="6" t="s">
         <v>30</v>
@@ -11666,7 +11666,7 @@
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A746" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B746" s="3">
         <v>5</v>
@@ -11748,7 +11748,7 @@
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A752" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B752" s="7">
         <v>2</v>
@@ -11802,7 +11802,7 @@
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A756" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B756" s="7">
         <v>4</v>
@@ -11830,7 +11830,7 @@
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A758" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B758" s="7">
         <v>5</v>
@@ -11848,7 +11848,7 @@
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A759" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B759" s="7"/>
       <c r="C759" s="10">
@@ -11871,7 +11871,7 @@
     <row r="761" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A761" s="12"/>
       <c r="B761" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C761" s="14" t="s">
         <v>123</v>
@@ -11968,7 +11968,7 @@
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A767" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B767" s="12"/>
       <c r="C767" s="15">
@@ -11999,12 +11999,12 @@
         <v>13</v>
       </c>
       <c r="F768" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A769" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B769" s="12"/>
       <c r="C769" s="15">
@@ -12072,7 +12072,7 @@
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A773" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B773" s="12"/>
       <c r="C773" s="15">
@@ -12108,7 +12108,7 @@
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A775" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B775" s="12"/>
       <c r="C775" s="15">
@@ -12126,7 +12126,7 @@
     </row>
     <row r="776" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A776" s="33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B776" s="33"/>
       <c r="C776" s="34"/>
@@ -12297,7 +12297,7 @@
     <row r="790" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A790" s="40"/>
       <c r="B790" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C790" s="42" t="s">
         <v>128</v>
@@ -12360,7 +12360,7 @@
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A795" s="40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B795" s="40">
         <v>3</v>
@@ -12549,7 +12549,7 @@
         <v>52</v>
       </c>
       <c r="D809" s="39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E809" s="39"/>
       <c r="F809" s="39"/>
@@ -12605,10 +12605,10 @@
     <row r="814" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A814" s="40"/>
       <c r="B814" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C814" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D814" s="43"/>
       <c r="E814" s="43"/>
@@ -12724,7 +12724,7 @@
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A823" s="40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B823" s="40">
         <v>5</v>
@@ -12778,7 +12778,7 @@
         <v>1</v>
       </c>
       <c r="C827" s="39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D827" s="45" t="s">
         <v>93</v>
@@ -12890,7 +12890,7 @@
         <v>5</v>
       </c>
       <c r="C835" s="39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D835" s="39" t="s">
         <v>7</v>
@@ -12921,10 +12921,10 @@
     <row r="838" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A838" s="40"/>
       <c r="B838" s="41" t="s">
+        <v>256</v>
+      </c>
+      <c r="C838" s="42" t="s">
         <v>257</v>
-      </c>
-      <c r="C838" s="42" t="s">
-        <v>258</v>
       </c>
       <c r="D838" s="43"/>
       <c r="E838" s="43"/>
@@ -12958,7 +12958,7 @@
     </row>
     <row r="841" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A841" s="40" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B841" s="40">
         <v>2</v>
@@ -13073,10 +13073,10 @@
     <row r="850" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A850" s="46"/>
       <c r="B850" s="47" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C850" s="48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D850" s="49"/>
       <c r="E850" s="49"/>
@@ -13250,7 +13250,7 @@
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A862" s="46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B862" s="46"/>
       <c r="C862" s="49">
@@ -13280,7 +13280,7 @@
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A864" s="51" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B864" s="46"/>
       <c r="C864" s="49">
@@ -13303,14 +13303,14 @@
         <v>85</v>
       </c>
       <c r="D865" s="53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E865" s="53"/>
       <c r="F865" s="53"/>
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A866" s="12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B866" s="12"/>
       <c r="C866" s="15">
@@ -13324,7 +13324,7 @@
     </row>
     <row r="867" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A867" s="33" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B867" s="33"/>
       <c r="C867" s="34"/>
@@ -13346,7 +13346,7 @@
         <v>1</v>
       </c>
       <c r="C869" s="38" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D869" s="39"/>
       <c r="E869" s="39"/>
@@ -13406,7 +13406,7 @@
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A874" s="36" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B874" s="36">
         <v>3</v>
@@ -13497,10 +13497,10 @@
     <row r="881" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A881" s="40"/>
       <c r="B881" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C881" s="42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D881" s="43"/>
       <c r="E881" s="43"/>
@@ -13662,7 +13662,7 @@
         <v>1</v>
       </c>
       <c r="C893" s="38" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D893" s="39"/>
       <c r="E893" s="39"/>
@@ -13722,7 +13722,7 @@
     </row>
     <row r="898" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A898" s="36" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B898" s="36">
         <v>3</v>
@@ -13813,10 +13813,10 @@
     <row r="905" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A905" s="40"/>
       <c r="B905" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C905" s="42" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D905" s="43"/>
       <c r="E905" s="43"/>
@@ -13876,7 +13876,7 @@
     </row>
     <row r="910" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A910" s="40" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B910" s="40">
         <v>3</v>
@@ -13892,7 +13892,7 @@
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A911" s="40" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B911" s="40"/>
       <c r="C911" s="43">
@@ -13910,7 +13910,7 @@
         <v>4</v>
       </c>
       <c r="C912" s="43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D912" s="43" t="s">
         <v>82</v>
@@ -13932,7 +13932,7 @@
     </row>
     <row r="914" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A914" s="40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B914" s="40">
         <v>5</v>
@@ -13972,7 +13972,7 @@
         <v>1</v>
       </c>
       <c r="C917" s="38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D917" s="39"/>
       <c r="E917" s="39"/>
@@ -13987,7 +13987,7 @@
         <v>34</v>
       </c>
       <c r="D918" s="39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E918" s="39"/>
       <c r="F918" s="39"/>
@@ -14119,10 +14119,10 @@
     <row r="929" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A929" s="40"/>
       <c r="B929" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C929" s="42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D929" s="43"/>
       <c r="E929" s="43"/>
@@ -14269,10 +14269,10 @@
     <row r="941" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A941" s="46"/>
       <c r="B941" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C941" s="48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D941" s="49"/>
       <c r="E941" s="49"/>
@@ -14296,7 +14296,7 @@
     </row>
     <row r="943" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A943" s="46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B943" s="46"/>
       <c r="C943" s="49">
@@ -14326,7 +14326,7 @@
     </row>
     <row r="945" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A945" s="46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B945" s="46"/>
       <c r="C945" s="49">
@@ -14356,7 +14356,7 @@
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A947" s="46" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B947" s="46"/>
       <c r="C947" s="49">
@@ -14386,7 +14386,7 @@
     </row>
     <row r="949" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A949" s="46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B949" s="46"/>
       <c r="C949" s="49">
@@ -14420,7 +14420,7 @@
     </row>
     <row r="951" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A951" s="46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B951" s="46"/>
       <c r="C951" s="49">
@@ -14454,7 +14454,7 @@
     </row>
     <row r="953" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A953" s="46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B953" s="46"/>
       <c r="C953" s="49">
@@ -14486,7 +14486,7 @@
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A955" s="51" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B955" s="46"/>
       <c r="C955" s="49">
@@ -14502,7 +14502,7 @@
     </row>
     <row r="956" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A956" s="46" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B956" s="46"/>
       <c r="C956" s="49"/>
@@ -14512,7 +14512,7 @@
     </row>
     <row r="957" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A957" s="33" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B957" s="33"/>
       <c r="C957" s="34"/>
@@ -14534,7 +14534,7 @@
         <v>1</v>
       </c>
       <c r="C959" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D959" s="39"/>
       <c r="E959" s="39"/>
@@ -14683,10 +14683,10 @@
     <row r="971" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A971" s="40"/>
       <c r="B971" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C971" s="42" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D971" s="43"/>
       <c r="E971" s="43"/>
@@ -14842,7 +14842,7 @@
         <v>1</v>
       </c>
       <c r="C983" s="38" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D983" s="39"/>
       <c r="E983" s="39"/>
@@ -14850,7 +14850,7 @@
     </row>
     <row r="984" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A984" s="36" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B984" s="36">
         <v>1</v>
@@ -14913,7 +14913,7 @@
         <v>93</v>
       </c>
       <c r="D988" s="45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E988" s="39" t="s">
         <v>54</v>
@@ -15007,10 +15007,10 @@
     <row r="995" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A995" s="40"/>
       <c r="B995" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C995" s="42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D995" s="43"/>
       <c r="E995" s="43"/>
@@ -15018,7 +15018,7 @@
     </row>
     <row r="996" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A996" s="40" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B996" s="40">
         <v>1</v>
@@ -15098,7 +15098,7 @@
     </row>
     <row r="1002" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1002" s="40" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B1002" s="40">
         <v>4</v>
@@ -15166,7 +15166,7 @@
         <v>1</v>
       </c>
       <c r="C1007" s="38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D1007" s="39"/>
       <c r="E1007" s="39"/>
@@ -15207,7 +15207,7 @@
         <v>34</v>
       </c>
       <c r="D1010" s="39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E1010" s="39"/>
       <c r="F1010" s="39"/>
@@ -15315,10 +15315,10 @@
     <row r="1019" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1019" s="40"/>
       <c r="B1019" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1019" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D1019" s="43"/>
       <c r="E1019" s="43"/>
@@ -15326,7 +15326,7 @@
     </row>
     <row r="1020" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1020" s="40" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B1020" s="40">
         <v>1</v>
@@ -15354,7 +15354,7 @@
     </row>
     <row r="1022" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1022" s="40" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B1022" s="40">
         <v>2</v>
@@ -15434,7 +15434,7 @@
     </row>
     <row r="1028" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1028" s="40" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B1028" s="40">
         <v>5</v>
@@ -15471,10 +15471,10 @@
     <row r="1031" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1031" s="46"/>
       <c r="B1031" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C1031" s="48" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D1031" s="49"/>
       <c r="E1031" s="49"/>
@@ -15554,7 +15554,7 @@
     </row>
     <row r="1037" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1037" s="46" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B1037" s="46"/>
       <c r="C1037" s="49">
@@ -15616,7 +15616,7 @@
     </row>
     <row r="1041" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1041" s="46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B1041" s="46"/>
       <c r="C1041" s="49">
@@ -15678,7 +15678,7 @@
     </row>
     <row r="1045" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1045" s="51" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B1045" s="46"/>
       <c r="C1045" s="49">
@@ -15692,7 +15692,7 @@
     </row>
     <row r="1046" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A1046" s="33" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B1046" s="33"/>
       <c r="C1046" s="34"/>
@@ -15714,7 +15714,7 @@
         <v>1</v>
       </c>
       <c r="C1048" s="38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D1048" s="39"/>
       <c r="E1048" s="39"/>
@@ -15800,7 +15800,7 @@
     </row>
     <row r="1055" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1055" s="36" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B1055" s="36">
         <v>4</v>
@@ -15828,7 +15828,7 @@
     </row>
     <row r="1057" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1057" s="36" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B1057" s="36">
         <v>5</v>
@@ -15865,10 +15865,10 @@
     <row r="1060" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1060" s="40"/>
       <c r="B1060" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1060" s="42" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D1060" s="43"/>
       <c r="E1060" s="43"/>
@@ -15928,7 +15928,7 @@
     </row>
     <row r="1065" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1065" s="40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B1065" s="40">
         <v>3</v>
@@ -15982,7 +15982,7 @@
     </row>
     <row r="1069" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1069" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B1069" s="40">
         <v>5</v>
@@ -16022,7 +16022,7 @@
         <v>1</v>
       </c>
       <c r="C1072" s="38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D1072" s="39"/>
       <c r="E1072" s="39"/>
@@ -16108,7 +16108,7 @@
     </row>
     <row r="1079" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1079" s="36" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B1079" s="36">
         <v>4</v>
@@ -16136,7 +16136,7 @@
     </row>
     <row r="1081" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1081" s="36" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B1081" s="36">
         <v>5</v>
@@ -16173,10 +16173,10 @@
     <row r="1084" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1084" s="40"/>
       <c r="B1084" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1084" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D1084" s="43"/>
       <c r="E1084" s="43"/>
@@ -16184,7 +16184,7 @@
     </row>
     <row r="1085" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1085" s="40" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B1085" s="40">
         <v>1</v>
@@ -16274,7 +16274,7 @@
     </row>
     <row r="1091" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1091" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B1091" s="40">
         <v>4</v>
@@ -16302,7 +16302,7 @@
     </row>
     <row r="1093" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1093" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B1093" s="40">
         <v>5</v>
@@ -16342,7 +16342,7 @@
         <v>1</v>
       </c>
       <c r="C1096" s="38" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D1096" s="39"/>
       <c r="E1096" s="39"/>
@@ -16376,7 +16376,7 @@
     </row>
     <row r="1099" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1099" s="36" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B1099" s="36">
         <v>2</v>
@@ -16404,7 +16404,7 @@
     </row>
     <row r="1101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1101" s="36" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B1101" s="36">
         <v>3</v>
@@ -16495,10 +16495,10 @@
     <row r="1108" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1108" s="40"/>
       <c r="B1108" s="41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1108" s="42" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D1108" s="43"/>
       <c r="E1108" s="43"/>
@@ -16574,7 +16574,7 @@
     </row>
     <row r="1114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1114" s="40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B1114" s="40"/>
       <c r="C1114" s="43">
@@ -16616,7 +16616,7 @@
     </row>
     <row r="1117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1117" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B1117" s="40">
         <v>5</v>
@@ -16653,10 +16653,10 @@
     <row r="1120" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="A1120" s="46"/>
       <c r="B1120" s="47" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1120" s="48" t="s">
         <v>294</v>
-      </c>
-      <c r="C1120" s="48" t="s">
-        <v>295</v>
       </c>
       <c r="D1120" s="49"/>
       <c r="E1120" s="49"/>
@@ -16680,7 +16680,7 @@
     </row>
     <row r="1122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1122" s="46" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B1122" s="46"/>
       <c r="C1122" s="49">
@@ -16710,7 +16710,7 @@
     </row>
     <row r="1124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1124" s="46" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B1124" s="46"/>
       <c r="C1124" s="49">
@@ -16820,7 +16820,7 @@
     </row>
     <row r="1131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1131" s="46" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B1131" s="46">
         <v>6</v>
@@ -16829,14 +16829,14 @@
         <v>119</v>
       </c>
       <c r="D1131" s="49" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E1131" s="49"/>
       <c r="F1131" s="49"/>
     </row>
     <row r="1132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1132" s="46" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B1132" s="46"/>
       <c r="C1132" s="49">
@@ -16850,16 +16850,16 @@
     </row>
     <row r="1133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1133" s="51" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1133" s="46">
         <v>7</v>
       </c>
       <c r="C1133" s="49" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D1133" s="49" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E1133" s="49"/>
       <c r="F1133" s="49"/>
@@ -16878,13 +16878,13 @@
     </row>
     <row r="1135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1135" s="46" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B1135" s="46">
         <v>8</v>
       </c>
       <c r="C1135" s="49" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D1135" s="49" t="s">
         <v>41</v>
@@ -16906,13 +16906,13 @@
     </row>
     <row r="1137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1137" s="46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B1137" s="46">
         <v>10</v>
       </c>
       <c r="C1137" s="49" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D1137" s="49" t="s">
         <v>33</v>
@@ -16934,13 +16934,13 @@
     </row>
     <row r="1139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1139" s="46" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B1139" s="46">
         <v>11</v>
       </c>
       <c r="C1139" s="49" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D1139" s="49" t="s">
         <v>17</v>
@@ -16950,7 +16950,7 @@
     </row>
     <row r="1140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1140" s="51" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B1140" s="46"/>
       <c r="C1140" s="49">
@@ -16964,13 +16964,13 @@
     </row>
     <row r="1141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1141" s="46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1141" s="46">
         <v>12</v>
       </c>
       <c r="C1141" s="49" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D1141" s="49" t="s">
         <v>43</v>
@@ -16992,13 +16992,13 @@
     </row>
     <row r="1143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1143" s="46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B1143" s="46">
         <v>13</v>
       </c>
       <c r="C1143" s="49" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D1143" s="49" t="s">
         <v>27</v>
@@ -17020,13 +17020,13 @@
     </row>
     <row r="1145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1145" s="46" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B1145" s="46">
         <v>14</v>
       </c>
       <c r="C1145" s="49" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D1145" s="49" t="s">
         <v>82</v>
